--- a/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
+++ b/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O493"/>
+  <dimension ref="A1:O554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28168,28 +28168,28 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C464" t="n">
         <v>1</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>[H]. R. Clar[k] Jr</t>
+          <t>Thomas Norton</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>H. R. Clark Jr.</t>
+          <t>Thomas Norton</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -28199,7 +28199,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>5101295</t>
+          <t>5101325</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28220,30 +28220,30 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C465" t="n">
         <v>2</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>[Wi]lliam Kingsmell</t>
+          <t>Rob[t] [Chase]</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>William Kingswell</t>
+          <t>Rob[t] [?]</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>5101298</t>
+          <t>5101328</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28279,30 +28279,30 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C466" t="n">
         <v>3</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Spencer [W]arner</t>
+          <t>[N] Chatham</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Spencer [?]</t>
+          <t>[?] Chatham</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -28317,7 +28317,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>5101299</t>
+          <t>5101329</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28338,35 +28338,35 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C467" t="n">
         <v>4</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>J. K. Bott[s]ford</t>
+          <t>[?] C. Tyer</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>J. K. Bottsford</t>
+          <t>[?] C. Tyer</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -28374,53 +28374,61 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H467" t="inlineStr">
-        <is>
-          <t>5101300</t>
-        </is>
-      </c>
+      <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J467" t="n">
         <v>26</v>
       </c>
-      <c r="K467" t="inlineStr"/>
-      <c r="L467" t="inlineStr"/>
-      <c r="M467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>5101330;5101521;5101855</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>5101330</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>lines 3 and 5 resolve uniquely to serials 5101329 and 5101331; of this line's 3 candidates exactly one, 5101330, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C468" t="n">
         <v>5</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>[R]euben Wha[t]ley</t>
+          <t>[?] Cunneh[e]tt</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Reuben [?]</t>
+          <t>[?] [?]</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -28435,7 +28443,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>5101301</t>
+          <t>5101331</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -28456,30 +28464,30 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C469" t="n">
         <v>6</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>[?]m[l]. D. Mason</t>
+          <t>[Alex] Cleveland</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>[?] D. Mason</t>
+          <t>[?] Cleveland</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -28494,7 +28502,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>5101302</t>
+          <t>5101332</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -28515,30 +28523,30 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C470" t="n">
         <v>7</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>J. H. Davis</t>
+          <t>R. B. Goodall</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>J. H. Davis</t>
+          <t>R. B. Goodall</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -28551,66 +28559,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr"/>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>5101333</t>
+        </is>
+      </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J470" t="n">
         <v>26</v>
       </c>
-      <c r="K470" t="inlineStr">
-        <is>
-          <t>5101303;5101699</t>
-        </is>
-      </c>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t>5101303</t>
-        </is>
-      </c>
-      <c r="M470" t="inlineStr">
-        <is>
-          <t>lines 6 and 9 resolve uniquely to serials 5101302 and 5101305; of this line's 2 candidates exactly one, 5101303, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr"/>
       <c r="N470" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C471" t="n">
         <v>8</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>J. G. [M]othe[r]</t>
+          <t>W[m] C. Covington</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>J. G. [?]</t>
+          <t>W[m] C. Covington</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -28618,10 +28618,14 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr"/>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>5101334</t>
+        </is>
+      </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J471" t="n">
@@ -28632,40 +28636,40 @@
       <c r="M471" t="inlineStr"/>
       <c r="N471" t="inlineStr">
         <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C472" t="n">
         <v>9</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>[Jo]hn Rhine[s]</t>
+          <t>Gerald Bigelow</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>John Rhines</t>
+          <t>Gerald Bigelow</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -28673,53 +28677,61 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr">
-        <is>
-          <t>5101305</t>
-        </is>
-      </c>
+      <c r="H472" t="inlineStr"/>
       <c r="I472" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J472" t="n">
         <v>26</v>
       </c>
-      <c r="K472" t="inlineStr"/>
-      <c r="L472" t="inlineStr"/>
-      <c r="M472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>5101335;5101888</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>5101335</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>lines 8 and 11 resolve uniquely to serials 5101334 and 5101336; of this line's 2 candidates exactly one, 5101335, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C473" t="n">
         <v>10</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Pat Fit[z] [G]ibbe[n]s</t>
+          <t>[?] Calhoun</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Patrick Fitzgibbons</t>
+          <t>[?] Calhoun</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -28732,53 +28744,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H473" t="inlineStr">
-        <is>
-          <t>5101306</t>
-        </is>
-      </c>
+      <c r="H473" t="inlineStr"/>
       <c r="I473" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(12)</t>
         </is>
       </c>
       <c r="J473" t="n">
         <v>26</v>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr"/>
       <c r="M473" t="inlineStr"/>
       <c r="N473" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C474" t="n">
         <v>11</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>[Jo]hn Kemo[n]y</t>
+          <t>[?] M. M[erri]ck</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>John [?]</t>
+          <t>[?] M. [?]</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -28791,66 +28803,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H474" t="inlineStr"/>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>5101336</t>
+        </is>
+      </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J474" t="n">
         <v>26</v>
       </c>
-      <c r="K474" t="inlineStr">
-        <is>
-          <t>5101307;5102137</t>
-        </is>
-      </c>
-      <c r="L474" t="inlineStr">
-        <is>
-          <t>5101307</t>
-        </is>
-      </c>
-      <c r="M474" t="inlineStr">
-        <is>
-          <t>lines 10 and 12 resolve uniquely to serials 5101306 and 5101308; of this line's 2 candidates exactly one, 5101307, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr"/>
       <c r="N474" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C475" t="n">
         <v>12</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>[Edw]ard M[a]graw</t>
+          <t>D. A. Long</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Edward Magraw</t>
+          <t>D. A. Long</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -28858,58 +28862,66 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H475" t="inlineStr">
-        <is>
-          <t>5101308</t>
-        </is>
-      </c>
+      <c r="H475" t="inlineStr"/>
       <c r="I475" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J475" t="n">
         <v>26</v>
       </c>
-      <c r="K475" t="inlineStr"/>
-      <c r="L475" t="inlineStr"/>
-      <c r="M475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>5101337</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>lines 11 and 13 resolve uniquely to serials 5101336 and 5101338; of this line's 43 candidates exactly one, 5101337, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C476" t="n">
         <v>13</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>[?]ard C. [E]niel</t>
+          <t>H. M. Merrill</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>[?] C. [?]</t>
+          <t>H. M. Merrill</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -28917,61 +28929,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H476" t="inlineStr"/>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>5101338</t>
+        </is>
+      </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>ambiguous(8)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J476" t="n">
         <v>26</v>
       </c>
-      <c r="K476" t="inlineStr">
-        <is>
-          <t>5101309;5101502;5101537;5101583;5101702;5101895;5102044;5102109</t>
-        </is>
-      </c>
-      <c r="L476" t="inlineStr">
-        <is>
-          <t>5101309</t>
-        </is>
-      </c>
-      <c r="M476" t="inlineStr">
-        <is>
-          <t>lines 12 and 14 resolve uniquely to serials 5101308 and 5101310; of this line's 8 candidates exactly one, 5101309, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr"/>
       <c r="N476" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C477" t="n">
         <v>14</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>[Hen]ry Killi[c]k</t>
+          <t>[F]. S. Dixon</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Henry Killick</t>
+          <t>[?] S. Dixon</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -28986,7 +28990,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>5101310</t>
+          <t>5101339</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29007,30 +29011,30 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C478" t="n">
         <v>15</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>[Ru]ben Ross</t>
+          <t>[Harlow] Kimball</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Reuben Ross</t>
+          <t>[?] Kimball</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -29043,61 +29047,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H478" t="inlineStr"/>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>5101340</t>
+        </is>
+      </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J478" t="n">
         <v>26</v>
       </c>
-      <c r="K478" t="inlineStr">
-        <is>
-          <t>5101264;5101311;5101644</t>
-        </is>
-      </c>
-      <c r="L478" t="inlineStr">
-        <is>
-          <t>5101311</t>
-        </is>
-      </c>
-      <c r="M478" t="inlineStr">
-        <is>
-          <t>lines 14 and 16 resolve uniquely to serials 5101310 and 5101312; of this line's 3 candidates exactly one, 5101311, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr"/>
       <c r="N478" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C479" t="n">
         <v>16</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>[Tho]mas Kenney</t>
+          <t>John Calhoun</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Thomas Kenney</t>
+          <t>John Calhoun</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -29112,7 +29108,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>5101312</t>
+          <t>5101341</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29133,30 +29129,30 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C480" t="n">
         <v>17</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>[Jo]hn Guthrie</t>
+          <t>E. B. Williams</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>John Guthrie</t>
+          <t>E. B. Williams</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -29169,53 +29165,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H480" t="inlineStr"/>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>5101342</t>
+        </is>
+      </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>ambiguous(6)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J480" t="n">
         <v>26</v>
       </c>
-      <c r="K480" t="inlineStr">
-        <is>
-          <t>5101283;5101392;5101445;5101559;5101696;5101863</t>
-        </is>
-      </c>
+      <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr"/>
       <c r="M480" t="inlineStr"/>
       <c r="N480" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C481" t="n">
         <v>18</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>[Mic]hael [G]alovan</t>
+          <t>[?] Strong</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Michael [?]</t>
+          <t>[?] [?]</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -29230,7 +29226,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>5101284</t>
+          <t>5101313</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29251,30 +29247,30 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C482" t="n">
         <v>19</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>[?] Sulivan</t>
+          <t>[Stillman] [Woods]</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>[?] Sullivan</t>
+          <t>[?] [?]</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -29289,7 +29285,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>5101285</t>
+          <t>5101314</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29310,35 +29306,35 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C483" t="n">
         <v>20</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>[Jo]hn Hancock</t>
+          <t>[C]. W. White</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>John Hancock</t>
+          <t>[?] W. White</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -29348,7 +29344,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>5101286</t>
+          <t>5101315</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29369,30 +29365,30 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C484" t="n">
         <v>21</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>[?]nard Dalton</t>
+          <t>Sam[l] C. B[a]rcom</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>[?] Dalton</t>
+          <t>Sam[l] C. [?]</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -29407,7 +29403,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>5101574</t>
+          <t>5101316</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -29428,35 +29424,35 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C485" t="n">
         <v>22</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>[Ja]mes Church</t>
+          <t>[Hanson] [S]hollowell</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>James Church</t>
+          <t>[?] [?]</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -29466,7 +29462,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>5101288</t>
+          <t>5101317</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -29487,30 +29483,30 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C486" t="n">
         <v>23</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>[W]m Burton</t>
+          <t>Cha[s] L. do</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>William Burton</t>
+          <t>Cha[s] L. [Hollowell]</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -29523,10 +29519,14 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr"/>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>5101318</t>
+        </is>
+      </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J486" t="n">
@@ -29537,35 +29537,35 @@
       <c r="M486" t="inlineStr"/>
       <c r="N486" t="inlineStr">
         <is>
-          <t>contested: serial 5101289 is the sole fingerprint match for 2 different lines (33S7-9YYJ-9WF line 6, 33SQ-GYYJ-992 line 23), and a serial may not be attached twice, so none of them keeps it</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C487" t="n">
         <v>24</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>[Willi]am Brown</t>
+          <t>[Chas] Petrice</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>William Brown</t>
+          <t>[?] Petrice</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -29578,61 +29578,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr"/>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>5101319</t>
+        </is>
+      </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J487" t="n">
         <v>26</v>
       </c>
-      <c r="K487" t="inlineStr">
-        <is>
-          <t>5101290;5101463;5102140</t>
-        </is>
-      </c>
-      <c r="L487" t="inlineStr">
-        <is>
-          <t>5101290</t>
-        </is>
-      </c>
-      <c r="M487" t="inlineStr">
-        <is>
-          <t>lines 23 and 29 resolve uniquely to serials 5101289 and 5101296; of this line's 3 candidates exactly one, 5101290, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr"/>
       <c r="N487" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C488" t="n">
         <v>25</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>[Wa]lter Bunney</t>
+          <t>[A]. Bardell</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Walter Bunney</t>
+          <t>[?] Bardell</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -29645,57 +29637,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr"/>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>5101320</t>
+        </is>
+      </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J488" t="n">
         <v>26</v>
       </c>
-      <c r="K488" t="inlineStr">
-        <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
+      <c r="K488" t="inlineStr"/>
       <c r="L488" t="inlineStr"/>
-      <c r="M488" t="inlineStr">
-        <is>
-          <t>lines 23 and 29 resolve uniquely to serials 5101289 and 5101296, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
-        </is>
-      </c>
+      <c r="M488" t="inlineStr"/>
       <c r="N488" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C489" t="n">
         <v>26</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>[?] Robertson</t>
+          <t>[Gordon] Moore Jun[r]</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>[?] Robertson</t>
+          <t>[?] Moore Jun[r]</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -29711,7 +29699,7 @@
       <c r="H489" t="inlineStr"/>
       <c r="I489" t="inlineStr">
         <is>
-          <t>ambiguous(4)</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J489" t="n">
@@ -29719,50 +29707,50 @@
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>5101292;5101471;5102025;5102134</t>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>5101292</t>
+          <t>5101321</t>
         </is>
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>lines 23 and 29 resolve uniquely to serials 5101289 and 5101296; of this line's 4 candidates exactly one, 5101292, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 25 and 27 resolve uniquely to serials 5101320 and 5101322; of this line's 43 candidates exactly one, 5101321, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C490" t="n">
         <v>27</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>[?] D. Taylor</t>
+          <t>[Solomon] Mill</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>[?] D. Taylor</t>
+          <t>[?] Mill</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -29775,10 +29763,14 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H490" t="inlineStr"/>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>5101322</t>
+        </is>
+      </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J490" t="n">
@@ -29789,35 +29781,35 @@
       <c r="M490" t="inlineStr"/>
       <c r="N490" t="inlineStr">
         <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C491" t="n">
         <v>28</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>[?] Burns</t>
+          <t>Eno[s] Plummer</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>[?] Burns</t>
+          <t>Eno[s] Plummer</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -29830,57 +29822,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H491" t="inlineStr"/>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>5101323</t>
+        </is>
+      </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J491" t="n">
         <v>26</v>
       </c>
-      <c r="K491" t="inlineStr">
-        <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
+      <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr"/>
-      <c r="M491" t="inlineStr">
-        <is>
-          <t>lines 23 and 29 resolve uniquely to serials 5101289 and 5101296, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
-        </is>
-      </c>
+      <c r="M491" t="inlineStr"/>
       <c r="N491" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C492" t="n">
         <v>29</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>[?] C. Ken[t]</t>
+          <t>[M]. Phinney</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>[?] C. Kent</t>
+          <t>[?] Phinney</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -29893,53 +29881,61 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr">
-        <is>
-          <t>5101296</t>
-        </is>
-      </c>
+      <c r="H492" t="inlineStr"/>
       <c r="I492" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J492" t="n">
         <v>26</v>
       </c>
-      <c r="K492" t="inlineStr"/>
-      <c r="L492" t="inlineStr"/>
-      <c r="M492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>5101324</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>lines 28 and 31 resolve uniquely to serials 5101323 and 5101327; of this line's 43 candidates exactly one, 5101324, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-992</t>
+          <t>33SQ-GYYJ-93Y</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C493" t="n">
         <v>30</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>[?] [R]. Bolle[s]</t>
+          <t>[A]. McCa[ff]rey</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>[?] R. Bolles</t>
+          <t>[?] McCa[ff]rey</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -29952,28 +29948,3727 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H493" t="inlineStr">
-        <is>
-          <t>5101297</t>
-        </is>
-      </c>
+      <c r="H493" t="inlineStr"/>
       <c r="I493" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J493" t="n">
         <v>26</v>
       </c>
-      <c r="K493" t="inlineStr"/>
-      <c r="L493" t="inlineStr"/>
-      <c r="M493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>5101326;5102171</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>5101326</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>lines 28 and 31 resolve uniquely to serials 5101323 and 5101327; of this line's 2 candidates exactly one, 5101326, lies in that run, and an unbroken run would put this line at 5101325</t>
+        </is>
+      </c>
       <c r="N493" t="inlineStr">
         <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-93Y</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>209</v>
+      </c>
+      <c r="C494" t="n">
+        <v>31</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>[N]uman Bond</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>[?] Bond</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>5101327</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J494" t="n">
+        <v>26</v>
+      </c>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr"/>
+      <c r="N494" t="inlineStr">
+        <is>
           <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
-      <c r="O493" t="inlineStr">
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-93Y.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>211</v>
+      </c>
+      <c r="C495" t="n">
+        <v>1</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>William C. [?]</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>William C. [?]</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr"/>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>ambiguous(27)</t>
+        </is>
+      </c>
+      <c r="J495" t="n">
+        <v>26</v>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>5101279;5101385;5101465;5101540;5101684;5101685;5101689;5101708;5101710;5101723;5101726;5101744;5101764;5101779;5101780;5101784;5101792;5101842;5101898;5101935;5101980;5101986;5101994;5102009;5102055;5102077;5102090</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr"/>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 27 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>211</v>
+      </c>
+      <c r="C496" t="n">
+        <v>2</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>[A]. Tupper</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>[?] Tupper</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>5101388</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J496" t="n">
+        <v>26</v>
+      </c>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr"/>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>211</v>
+      </c>
+      <c r="C497" t="n">
+        <v>3</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Ira Couch</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Ira Couch</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>5101389</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J497" t="n">
+        <v>26</v>
+      </c>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr"/>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>211</v>
+      </c>
+      <c r="C498" t="n">
+        <v>4</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Rich[d] Lewis</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Rich[d] Lewis</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>5101390</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J498" t="n">
+        <v>26</v>
+      </c>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr"/>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>211</v>
+      </c>
+      <c r="C499" t="n">
+        <v>5</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>S. D. Lewis</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>S. D. Lewis</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>5101391</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J499" t="n">
+        <v>26</v>
+      </c>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr"/>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>211</v>
+      </c>
+      <c r="C500" t="n">
+        <v>6</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>W[m] Berry</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>W[m] Berry</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr"/>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J500" t="n">
+        <v>26</v>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>5101283;5101392;5101445;5101559;5101696;5101863</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>5101392</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>lines 5 and 8 resolve uniquely to serials 5101391 and 5101394; of this line's 6 candidates exactly one, 5101392, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>211</v>
+      </c>
+      <c r="C501" t="n">
+        <v>7</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Stephen [F] Black</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Stephen [?] Black</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr"/>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J501" t="n">
+        <v>26</v>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>5101393</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>lines 5 and 8 resolve uniquely to serials 5101391 and 5101394; of this line's 10 candidates exactly one, 5101393, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>211</v>
+      </c>
+      <c r="C502" t="n">
+        <v>8</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Nichol[l]s Rossiter</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Nichol[l]s Rossiter</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>5101394</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J502" t="n">
+        <v>26</v>
+      </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr"/>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>211</v>
+      </c>
+      <c r="C503" t="n">
+        <v>9</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Sa[m]l Baxter</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Sa[m]l Baxter</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>5101395</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J503" t="n">
+        <v>26</v>
+      </c>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr"/>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>211</v>
+      </c>
+      <c r="C504" t="n">
+        <v>10</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Joseph L. Williams</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Joseph L. Williams</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr"/>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>ambiguous(12)</t>
+        </is>
+      </c>
+      <c r="J504" t="n">
+        <v>26</v>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>lines 9 and 13 resolve uniquely to serials 5101395 and 5101399, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>211</v>
+      </c>
+      <c r="C505" t="n">
+        <v>11</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Sam[l] Anderson</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Sam[l] Anderson</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr"/>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>ambiguous(12)</t>
+        </is>
+      </c>
+      <c r="J505" t="n">
+        <v>26</v>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>lines 9 and 13 resolve uniquely to serials 5101395 and 5101399, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>211</v>
+      </c>
+      <c r="C506" t="n">
+        <v>12</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>[?] Smith &amp; Doyle</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>[?] Smith &amp; Doyle</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr"/>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J506" t="n">
+        <v>26</v>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>5101398</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>lines 9 and 13 resolve uniquely to serials 5101395 and 5101399; of this line's 10 candidates exactly one, 5101398, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>211</v>
+      </c>
+      <c r="C507" t="n">
+        <v>13</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Adam Gale</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Adam Gale</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>5101399</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J507" t="n">
+        <v>26</v>
+      </c>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr"/>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>211</v>
+      </c>
+      <c r="C508" t="n">
+        <v>14</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>E. Taylor</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>E. Taylor</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>5101400</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J508" t="n">
+        <v>26</v>
+      </c>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr"/>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>211</v>
+      </c>
+      <c r="C509" t="n">
+        <v>15</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>N. B. Judd</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>N. B. Judd</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr"/>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J509" t="n">
+        <v>26</v>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr"/>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>211</v>
+      </c>
+      <c r="C510" t="n">
+        <v>16</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>[?] Wadsworth</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>[?] Wadsworth</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr"/>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J510" t="n">
+        <v>26</v>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr"/>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>211</v>
+      </c>
+      <c r="C511" t="n">
+        <v>17</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>S. H. [Foss]</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>S. H. [?]</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr"/>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J511" t="n">
+        <v>26</v>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr"/>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>211</v>
+      </c>
+      <c r="C512" t="n">
+        <v>18</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>O. W. Shepard</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>O. W. Shepard</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J512" t="n">
+        <v>26</v>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr"/>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>211</v>
+      </c>
+      <c r="C513" t="n">
+        <v>19</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>John Wentworth</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>John Wentworth</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J513" t="n">
+        <v>26</v>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>211</v>
+      </c>
+      <c r="C514" t="n">
+        <v>20</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>H. L. Whitman</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>H. L. Whitman</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr"/>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J514" t="n">
+        <v>26</v>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr"/>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>211</v>
+      </c>
+      <c r="C515" t="n">
+        <v>21</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Geo. W. Randolph &amp; Co</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Geo. W. Randolph &amp; Co</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>ambiguous(4)</t>
+        </is>
+      </c>
+      <c r="J515" t="n">
+        <v>26</v>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>5101377;5101407;5101520;5101592</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr"/>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>211</v>
+      </c>
+      <c r="C516" t="n">
+        <v>22</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>P. P. Smith</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>P. P. Smith</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr"/>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J516" t="n">
+        <v>26</v>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr"/>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>211</v>
+      </c>
+      <c r="C517" t="n">
+        <v>23</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>[R]. [J]. [?]man</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>[?] [?] [?]</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J517" t="n">
+        <v>26</v>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>5101354;5101370;5101379;5101732;5101757;5102016</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr"/>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>211</v>
+      </c>
+      <c r="C518" t="n">
+        <v>24</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>M. K. [Silly]</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>M. K. [?]</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>5101380</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J518" t="n">
+        <v>26</v>
+      </c>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr"/>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>211</v>
+      </c>
+      <c r="C519" t="n">
+        <v>25</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Maria Hatch</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>[?] Hatch</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J519" t="n">
+        <v>26</v>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>5101381</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>lines 24 and 26 resolve uniquely to serials 5101380 and 5101382; of this line's 10 candidates exactly one, 5101381, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>211</v>
+      </c>
+      <c r="C520" t="n">
+        <v>26</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>[?] Mills</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>[?] Mills</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>5101382</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J520" t="n">
+        <v>26</v>
+      </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>211</v>
+      </c>
+      <c r="C521" t="n">
+        <v>27</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>E. Dewey</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>E. Dewey</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J521" t="n">
+        <v>26</v>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>5101383;5101899</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>5101383</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>lines 26 and 28 resolve uniquely to serials 5101382 and 5101384; of this line's 2 candidates exactly one, 5101383, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>211</v>
+      </c>
+      <c r="C522" t="n">
+        <v>28</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>John Mandell</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>John Mandell</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>5101384</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J522" t="n">
+        <v>26</v>
+      </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr"/>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>211</v>
+      </c>
+      <c r="C523" t="n">
+        <v>29</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Theodo[tia] Doty</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>[?] Doty</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>5101386</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J523" t="n">
+        <v>26</v>
+      </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-97P</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>211</v>
+      </c>
+      <c r="C524" t="n">
+        <v>30</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>William [Wheeler]</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>William [?]</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>5101387</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J524" t="n">
+        <v>26</v>
+      </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-97P.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>208</v>
+      </c>
+      <c r="C525" t="n">
+        <v>1</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>[H]. R. Clar[k] Jr</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>H. R. Clark Jr.</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>5101295</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J525" t="n">
+        <v>26</v>
+      </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr"/>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>208</v>
+      </c>
+      <c r="C526" t="n">
+        <v>2</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>[Wi]lliam Kingsmell</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>William Kingswell</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>5101298</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J526" t="n">
+        <v>26</v>
+      </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr"/>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>208</v>
+      </c>
+      <c r="C527" t="n">
+        <v>3</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Spencer [W]arner</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Spencer [?]</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>5101299</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J527" t="n">
+        <v>26</v>
+      </c>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr"/>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>208</v>
+      </c>
+      <c r="C528" t="n">
+        <v>4</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>J. K. Bott[s]ford</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>J. K. Bottsford</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>5101300</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J528" t="n">
+        <v>26</v>
+      </c>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr"/>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>208</v>
+      </c>
+      <c r="C529" t="n">
+        <v>5</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>[R]euben Wha[t]ley</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Reuben [?]</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>5101301</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J529" t="n">
+        <v>26</v>
+      </c>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr"/>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>208</v>
+      </c>
+      <c r="C530" t="n">
+        <v>6</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>[?]m[l]. D. Mason</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>[?] D. Mason</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>5101302</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J530" t="n">
+        <v>26</v>
+      </c>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr"/>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>208</v>
+      </c>
+      <c r="C531" t="n">
+        <v>7</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>J. H. Davis</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>J. H. Davis</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J531" t="n">
+        <v>26</v>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>5101303;5101699</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>5101303</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>lines 6 and 9 resolve uniquely to serials 5101302 and 5101305; of this line's 2 candidates exactly one, 5101303, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>208</v>
+      </c>
+      <c r="C532" t="n">
+        <v>8</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>J. G. [M]othe[r]</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>J. G. [?]</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J532" t="n">
+        <v>26</v>
+      </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr"/>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>208</v>
+      </c>
+      <c r="C533" t="n">
+        <v>9</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>[Jo]hn Rhine[s]</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>John Rhines</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>5101305</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J533" t="n">
+        <v>26</v>
+      </c>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr"/>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>208</v>
+      </c>
+      <c r="C534" t="n">
+        <v>10</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Pat Fit[z] [G]ibbe[n]s</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Patrick Fitzgibbons</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>5101306</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J534" t="n">
+        <v>26</v>
+      </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr"/>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>208</v>
+      </c>
+      <c r="C535" t="n">
+        <v>11</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>[Jo]hn Kemo[n]y</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>John [?]</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J535" t="n">
+        <v>26</v>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>5101307;5102137</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>5101307</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>lines 10 and 12 resolve uniquely to serials 5101306 and 5101308; of this line's 2 candidates exactly one, 5101307, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>208</v>
+      </c>
+      <c r="C536" t="n">
+        <v>12</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>[Edw]ard M[a]graw</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Edward Magraw</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>5101308</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J536" t="n">
+        <v>26</v>
+      </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr"/>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>208</v>
+      </c>
+      <c r="C537" t="n">
+        <v>13</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>[?]ard C. [E]niel</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>[?] C. [?]</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>ambiguous(8)</t>
+        </is>
+      </c>
+      <c r="J537" t="n">
+        <v>26</v>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>5101309;5101502;5101537;5101583;5101702;5101895;5102044;5102109</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>5101309</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>lines 12 and 14 resolve uniquely to serials 5101308 and 5101310; of this line's 8 candidates exactly one, 5101309, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>208</v>
+      </c>
+      <c r="C538" t="n">
+        <v>14</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>[Hen]ry Killi[c]k</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Henry Killick</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>5101310</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J538" t="n">
+        <v>26</v>
+      </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr"/>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>208</v>
+      </c>
+      <c r="C539" t="n">
+        <v>15</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>[Ru]ben Ross</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Reuben Ross</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr"/>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J539" t="n">
+        <v>26</v>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>5101264;5101311;5101644</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>5101311</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>lines 14 and 16 resolve uniquely to serials 5101310 and 5101312; of this line's 3 candidates exactly one, 5101311, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>208</v>
+      </c>
+      <c r="C540" t="n">
+        <v>16</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>[Tho]mas Kenney</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Thomas Kenney</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>5101312</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J540" t="n">
+        <v>26</v>
+      </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr"/>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>208</v>
+      </c>
+      <c r="C541" t="n">
+        <v>17</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>[Jo]hn Guthrie</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>John Guthrie</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J541" t="n">
+        <v>26</v>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>5101283;5101392;5101445;5101559;5101696;5101863</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr"/>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>208</v>
+      </c>
+      <c r="C542" t="n">
+        <v>18</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>[Mic]hael [G]alovan</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Michael [?]</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>5101284</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J542" t="n">
+        <v>26</v>
+      </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr"/>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>208</v>
+      </c>
+      <c r="C543" t="n">
+        <v>19</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>[?] Sulivan</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>[?] Sullivan</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>5101285</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J543" t="n">
+        <v>26</v>
+      </c>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr"/>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>208</v>
+      </c>
+      <c r="C544" t="n">
+        <v>20</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>[Jo]hn Hancock</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>John Hancock</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>5101286</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J544" t="n">
+        <v>26</v>
+      </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr"/>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>208</v>
+      </c>
+      <c r="C545" t="n">
+        <v>21</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>[?]nard Dalton</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>[?] Dalton</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>5101574</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J545" t="n">
+        <v>26</v>
+      </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr"/>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>208</v>
+      </c>
+      <c r="C546" t="n">
+        <v>22</v>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>[Ja]mes Church</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>James Church</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>5101288</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J546" t="n">
+        <v>26</v>
+      </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr"/>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>208</v>
+      </c>
+      <c r="C547" t="n">
+        <v>23</v>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>[W]m Burton</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>William Burton</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J547" t="n">
+        <v>26</v>
+      </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr"/>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>contested: serial 5101289 is the sole fingerprint match for 2 different lines (33S7-9YYJ-9WF line 6, 33SQ-GYYJ-992 line 23), and a serial may not be attached twice, so none of them keeps it</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>208</v>
+      </c>
+      <c r="C548" t="n">
+        <v>24</v>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>[Willi]am Brown</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>William Brown</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J548" t="n">
+        <v>26</v>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>5101290;5101463;5102140</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>5101290</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>lines 23 and 29 resolve uniquely to serials 5101289 and 5101296; of this line's 3 candidates exactly one, 5101290, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>208</v>
+      </c>
+      <c r="C549" t="n">
+        <v>25</v>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>[Wa]lter Bunney</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Walter Bunney</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J549" t="n">
+        <v>26</v>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>lines 23 and 29 resolve uniquely to serials 5101289 and 5101296, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>208</v>
+      </c>
+      <c r="C550" t="n">
+        <v>26</v>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>[?] Robertson</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>[?] Robertson</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr"/>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>ambiguous(4)</t>
+        </is>
+      </c>
+      <c r="J550" t="n">
+        <v>26</v>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>5101292;5101471;5102025;5102134</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>5101292</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>lines 23 and 29 resolve uniquely to serials 5101289 and 5101296; of this line's 4 candidates exactly one, 5101292, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>208</v>
+      </c>
+      <c r="C551" t="n">
+        <v>27</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>[?] D. Taylor</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>[?] D. Taylor</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr"/>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J551" t="n">
+        <v>26</v>
+      </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr"/>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>208</v>
+      </c>
+      <c r="C552" t="n">
+        <v>28</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>[?] Burns</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>[?] Burns</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr"/>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J552" t="n">
+        <v>26</v>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>lines 23 and 29 resolve uniquely to serials 5101289 and 5101296, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>208</v>
+      </c>
+      <c r="C553" t="n">
+        <v>29</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>[?] C. Ken[t]</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>[?] C. Kent</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>5101296</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J553" t="n">
+        <v>26</v>
+      </c>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr"/>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-992</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>208</v>
+      </c>
+      <c r="C554" t="n">
+        <v>30</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>[?] [R]. Bolle[s]</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>[?] R. Bolles</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>5101297</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J554" t="n">
+        <v>26</v>
+      </c>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr"/>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
         <is>
           <t>chicago/reference/census1840/33SQ-GYYJ-992.jpg</t>
         </is>

--- a/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
+++ b/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
@@ -1395,14 +1395,10 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>5101709</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1413,7 +1409,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 24 of the schedule's 26 columns matches exactly one of the 964 IPUMS households; 2 columns masked because this page's reading does not close them against the enumerator's printed totals</t>
+          <t>contested: serial 5101709 is the sole fingerprint match for 2 different lines (33S7-9YYJ-2T line 15, 33S7-9YYJ-9M5 line 22), and a serial may not be attached twice, so none of them keeps it</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -11566,7 +11562,7 @@
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ambiguous(14)</t>
+          <t>ambiguous(8)</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -11574,14 +11570,14 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>5101354;5101370;5101379;5101712;5101732;5101757;5101821;5101896;5101924;5101941;5102016;5102149;5102154;5102164</t>
+          <t>5101712;5101821;5101896;5101924;5101941;5102149;5102154;5102164</t>
         </is>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 14 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -11625,7 +11621,7 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>ambiguous(24)</t>
+          <t>ambiguous(29)</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -11633,14 +11629,14 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>5101307;5101362;5101440;5101450;5101509;5101516;5101580;5101628;5101650;5101654;5101655;5101728;5101776;5101783;5101852;5101857;5101944;5101969;5101976;5102005;5102045;5102094;5102137;5102157</t>
+          <t>5101254;5101263;5101344;5101362;5101450;5101478;5101509;5101516;5101561;5101580;5101628;5101650;5101654;5101655;5101691;5101735;5101776;5101783;5101800;5101805;5101857;5101871;5101878;5101881;5101969;5102045;5102108;5102148;5102160</t>
         </is>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 24 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 29 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -11681,14 +11677,10 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>5101945</t>
-        </is>
-      </c>
+      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -11699,7 +11691,7 @@
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 24 of the schedule's 26 columns matches exactly one of the 964 IPUMS households; 2 columns masked because this page's reading does not close them against the enumerator's printed totals</t>
+          <t>no IPUMS household carries this pattern over the 24 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -11743,7 +11735,7 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>ambiguous(33)</t>
+          <t>ambiguous(76)</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -11751,22 +11743,14 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>5101309;5101427;5101502;5101537;5101555;5101557;5101583;5101648;5101653;5101682;5101702;5101722;5101813;5101827;5101864;5101869;5101890;5101895;5101905;5101909;5101937;5101939;5101946;5101973;5102000;5102011;5102038;5102044;5102052;5102105;5102109;5102144;5102187</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>5101946</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>lines 3 and 6 resolve uniquely to serials 5101945 and 5101948; of this line's 33 candidates exactly one, 5101946, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101273;5101283;5101291;5101294;5101321;5101324;5101337;5101392;5101427;5101432;5101434;5101443;5101445;5101464;5101476;5101479;5101485;5101551;5101552;5101555;5101557;5101559;5101589;5101606;5101609;5101631;5101648;5101653;5101656;5101663;5101678;5101682;5101696;5101722;5101739;5101743;5101759;5101765;5101794;5101812;5101813;5101820;5101822;5101827;5101853;5101863;5101864;5101869;5101880;5101882;5101883;5101890;5101905;5101906;5101918;5101928;5101939;5101946;5101947;5101954;5101956;5101973;5101985;5101990;5102000;5102011;5102050;5102052;5102105;5102113;5102144;5102155;5102156;5102159;5102168;5102187</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 33 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 76 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -11810,7 +11794,7 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>ambiguous(80)</t>
+          <t>ambiguous(76)</t>
         </is>
       </c>
       <c r="J192" t="n">
@@ -11818,22 +11802,14 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>5101273;5101279;5101291;5101294;5101321;5101324;5101337;5101385;5101432;5101434;5101443;5101464;5101465;5101476;5101479;5101485;5101540;5101551;5101552;5101589;5101606;5101609;5101631;5101656;5101663;5101669;5101678;5101684;5101685;5101689;5101708;5101710;5101723;5101726;5101739;5101743;5101744;5101759;5101764;5101765;5101779;5101780;5101784;5101792;5101794;5101807;5101808;5101812;5101820;5101822;5101842;5101853;5101873;5101880;5101882;5101883;5101898;5101906;5101918;5101928;5101935;5101947;5101954;5101956;5101980;5101985;5101986;5101990;5101994;5102009;5102050;5102055;5102056;5102077;5102090;5102113;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>5101947</t>
-        </is>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>lines 3 and 6 resolve uniquely to serials 5101945 and 5101948; of this line's 80 candidates exactly one, 5101947, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101273;5101283;5101291;5101294;5101321;5101324;5101337;5101392;5101427;5101432;5101434;5101443;5101445;5101464;5101476;5101479;5101485;5101551;5101552;5101555;5101557;5101559;5101589;5101606;5101609;5101631;5101648;5101653;5101656;5101663;5101678;5101682;5101696;5101722;5101739;5101743;5101759;5101765;5101794;5101812;5101813;5101820;5101822;5101827;5101853;5101863;5101864;5101869;5101880;5101882;5101883;5101890;5101905;5101906;5101918;5101928;5101939;5101946;5101947;5101954;5101956;5101973;5101985;5101990;5102000;5102011;5102050;5102052;5102105;5102113;5102144;5102155;5102156;5102159;5102168;5102187</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 80 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 76 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -11933,14 +11909,10 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>5101949</t>
-        </is>
-      </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J194" t="n">
@@ -11951,7 +11923,7 @@
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 24 of the schedule's 26 columns matches exactly one of the 964 IPUMS households; 2 columns masked because this page's reading does not close them against the enumerator's printed totals</t>
+          <t>no IPUMS household carries this pattern over the 24 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -12003,19 +11975,11 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>5101920;5101950</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>5101950</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>lines 7 and 9 resolve uniquely to serials 5101949 and 5101951; of this line's 2 candidates exactly one, 5101950, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101920;5102095</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
           <t>the fingerprint over 24 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
@@ -12059,14 +12023,10 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>5101951</t>
-        </is>
-      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J196" t="n">
@@ -12077,7 +12037,7 @@
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 24 of the schedule's 26 columns matches exactly one of the 964 IPUMS households; 2 columns masked because this page's reading does not close them against the enumerator's printed totals</t>
+          <t>no IPUMS household carries this pattern over the 24 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -12239,7 +12199,7 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>ambiguous(80)</t>
+          <t>ambiguous(76)</t>
         </is>
       </c>
       <c r="J199" t="n">
@@ -12247,7 +12207,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>5101273;5101279;5101291;5101294;5101321;5101324;5101337;5101385;5101432;5101434;5101443;5101464;5101465;5101476;5101479;5101485;5101540;5101551;5101552;5101589;5101606;5101609;5101631;5101656;5101663;5101669;5101678;5101684;5101685;5101689;5101708;5101710;5101723;5101726;5101739;5101743;5101744;5101759;5101764;5101765;5101779;5101780;5101784;5101792;5101794;5101807;5101808;5101812;5101820;5101822;5101842;5101853;5101873;5101880;5101882;5101883;5101898;5101906;5101918;5101928;5101935;5101947;5101954;5101956;5101980;5101985;5101986;5101990;5101994;5102009;5102050;5102055;5102056;5102077;5102090;5102113;5102155;5102156;5102159;5102168</t>
+          <t>5101273;5101283;5101291;5101294;5101321;5101324;5101337;5101392;5101427;5101432;5101434;5101443;5101445;5101464;5101476;5101479;5101485;5101551;5101552;5101555;5101557;5101559;5101589;5101606;5101609;5101631;5101648;5101653;5101656;5101663;5101678;5101682;5101696;5101722;5101739;5101743;5101759;5101765;5101794;5101812;5101813;5101820;5101822;5101827;5101853;5101863;5101864;5101869;5101880;5101882;5101883;5101890;5101905;5101906;5101918;5101928;5101939;5101946;5101947;5101954;5101956;5101973;5101985;5101990;5102000;5102011;5102050;5102052;5102105;5102113;5102144;5102155;5102156;5102159;5102168;5102187</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12257,12 +12217,12 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>lines 11 and 13 resolve uniquely to serials 5101953 and 5101955; of this line's 80 candidates exactly one, 5101954, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 11 and 13 resolve uniquely to serials 5101953 and 5101955; of this line's 76 candidates exactly one, 5101954, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 80 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 76 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -12365,7 +12325,7 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>ambiguous(80)</t>
+          <t>ambiguous(76)</t>
         </is>
       </c>
       <c r="J201" t="n">
@@ -12373,7 +12333,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>5101273;5101279;5101291;5101294;5101321;5101324;5101337;5101385;5101432;5101434;5101443;5101464;5101465;5101476;5101479;5101485;5101540;5101551;5101552;5101589;5101606;5101609;5101631;5101656;5101663;5101669;5101678;5101684;5101685;5101689;5101708;5101710;5101723;5101726;5101739;5101743;5101744;5101759;5101764;5101765;5101779;5101780;5101784;5101792;5101794;5101807;5101808;5101812;5101820;5101822;5101842;5101853;5101873;5101880;5101882;5101883;5101898;5101906;5101918;5101928;5101935;5101947;5101954;5101956;5101980;5101985;5101986;5101990;5101994;5102009;5102050;5102055;5102056;5102077;5102090;5102113;5102155;5102156;5102159;5102168</t>
+          <t>5101273;5101283;5101291;5101294;5101321;5101324;5101337;5101392;5101427;5101432;5101434;5101443;5101445;5101464;5101476;5101479;5101485;5101551;5101552;5101555;5101557;5101559;5101589;5101606;5101609;5101631;5101648;5101653;5101656;5101663;5101678;5101682;5101696;5101722;5101739;5101743;5101759;5101765;5101794;5101812;5101813;5101820;5101822;5101827;5101853;5101863;5101864;5101869;5101880;5101882;5101883;5101890;5101905;5101906;5101918;5101928;5101939;5101946;5101947;5101954;5101956;5101973;5101985;5101990;5102000;5102011;5102050;5102052;5102105;5102113;5102144;5102155;5102156;5102159;5102168;5102187</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -12383,12 +12343,12 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>lines 13 and 16 resolve uniquely to serials 5101955 and 5101958; of this line's 80 candidates exactly one, 5101956, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 13 and 16 resolve uniquely to serials 5101955 and 5101958; of this line's 76 candidates exactly one, 5101956, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 80 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 76 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -12432,7 +12392,7 @@
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J202" t="n">
@@ -12440,22 +12400,14 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>5101616;5101957</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>5101957</t>
-        </is>
-      </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>lines 13 and 16 resolve uniquely to serials 5101955 and 5101958; of this line's 2 candidates exactly one, 5101957, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101341;5101581;5101616</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -12614,14 +12566,10 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>5101930</t>
-        </is>
-      </c>
+      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -12632,7 +12580,7 @@
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 24 of the schedule's 26 columns matches exactly one of the 964 IPUMS households; 2 columns masked because this page's reading does not close them against the enumerator's printed totals</t>
+          <t>no IPUMS household carries this pattern over the 24 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -12673,25 +12621,33 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>5101931</t>
-        </is>
-      </c>
+      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J206" t="n">
         <v>24</v>
       </c>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>5101649;5101931</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>5101931</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>lines 17 and 21 resolve uniquely to serials 5101929 and 5101933; of this line's 2 candidates exactly one, 5101931, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 24 of the schedule's 26 columns matches exactly one of the 964 IPUMS households; 2 columns masked because this page's reading does not close them against the enumerator's printed totals</t>
+          <t>the fingerprint over 24 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -12732,14 +12688,10 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>5101932</t>
-        </is>
-      </c>
+      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -12750,7 +12702,7 @@
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 24 of the schedule's 26 columns matches exactly one of the 964 IPUMS households; 2 columns masked because this page's reading does not close them against the enumerator's printed totals</t>
+          <t>no IPUMS household carries this pattern over the 24 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -12853,30 +12805,18 @@
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J209" t="n">
         <v>24</v>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>5101709;5101934</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>5101934</t>
-        </is>
-      </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>lines 21 and 24 resolve uniquely to serials 5101933 and 5101936; of this line's 2 candidates exactly one, 5101934, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>contested: serial 5101709 is the sole fingerprint match for 2 different lines (33S7-9YYJ-2T line 15, 33S7-9YYJ-9M5 line 22), and a serial may not be attached twice, so none of them keeps it</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -12920,7 +12860,7 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>ambiguous(80)</t>
+          <t>ambiguous(76)</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -12928,22 +12868,18 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>5101273;5101279;5101291;5101294;5101321;5101324;5101337;5101385;5101432;5101434;5101443;5101464;5101465;5101476;5101479;5101485;5101540;5101551;5101552;5101589;5101606;5101609;5101631;5101656;5101663;5101669;5101678;5101684;5101685;5101689;5101708;5101710;5101723;5101726;5101739;5101743;5101744;5101759;5101764;5101765;5101779;5101780;5101784;5101792;5101794;5101807;5101808;5101812;5101820;5101822;5101842;5101853;5101873;5101880;5101882;5101883;5101898;5101906;5101918;5101928;5101935;5101947;5101954;5101956;5101980;5101985;5101986;5101990;5101994;5102009;5102050;5102055;5102056;5102077;5102090;5102113;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>5101935</t>
-        </is>
-      </c>
+          <t>5101273;5101283;5101291;5101294;5101321;5101324;5101337;5101392;5101427;5101432;5101434;5101443;5101445;5101464;5101476;5101479;5101485;5101551;5101552;5101555;5101557;5101559;5101589;5101606;5101609;5101631;5101648;5101653;5101656;5101663;5101678;5101682;5101696;5101722;5101739;5101743;5101759;5101765;5101794;5101812;5101813;5101820;5101822;5101827;5101853;5101863;5101864;5101869;5101880;5101882;5101883;5101890;5101905;5101906;5101918;5101928;5101939;5101946;5101947;5101954;5101956;5101973;5101985;5101990;5102000;5102011;5102050;5102052;5102105;5102113;5102144;5102155;5102156;5102159;5102168;5102187</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>lines 21 and 24 resolve uniquely to serials 5101933 and 5101936; of this line's 80 candidates exactly one, 5101935, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 22 and 30 resolve uniquely to serials 5101709 and 5101943, and 24 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 80 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 76 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -12984,14 +12920,10 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>5101936</t>
-        </is>
-      </c>
+      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J211" t="n">
@@ -13002,7 +12934,7 @@
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 24 of the schedule's 26 columns matches exactly one of the 964 IPUMS households; 2 columns masked because this page's reading does not close them against the enumerator's printed totals</t>
+          <t>no IPUMS household carries this pattern over the 24 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -13046,7 +12978,7 @@
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
-          <t>ambiguous(33)</t>
+          <t>ambiguous(76)</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -13054,18 +12986,18 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>5101309;5101427;5101502;5101537;5101555;5101557;5101583;5101648;5101653;5101682;5101702;5101722;5101813;5101827;5101864;5101869;5101890;5101895;5101905;5101909;5101937;5101939;5101946;5101973;5102000;5102011;5102038;5102044;5102052;5102105;5102109;5102144;5102187</t>
+          <t>5101273;5101283;5101291;5101294;5101321;5101324;5101337;5101392;5101427;5101432;5101434;5101443;5101445;5101464;5101476;5101479;5101485;5101551;5101552;5101555;5101557;5101559;5101589;5101606;5101609;5101631;5101648;5101653;5101656;5101663;5101678;5101682;5101696;5101722;5101739;5101743;5101759;5101765;5101794;5101812;5101813;5101820;5101822;5101827;5101853;5101863;5101864;5101869;5101880;5101882;5101883;5101890;5101905;5101906;5101918;5101928;5101939;5101946;5101947;5101954;5101956;5101973;5101985;5101990;5102000;5102011;5102050;5102052;5102105;5102113;5102144;5102155;5102156;5102159;5102168;5102187</t>
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>lines 24 and 30 resolve uniquely to serials 5101936 and 5101943, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+          <t>lines 22 and 30 resolve uniquely to serials 5101709 and 5101943, and 24 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 33 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 76 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -13164,7 +13096,7 @@
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
-          <t>ambiguous(33)</t>
+          <t>ambiguous(76)</t>
         </is>
       </c>
       <c r="J214" t="n">
@@ -13172,18 +13104,18 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>5101309;5101427;5101502;5101537;5101555;5101557;5101583;5101648;5101653;5101682;5101702;5101722;5101813;5101827;5101864;5101869;5101890;5101895;5101905;5101909;5101937;5101939;5101946;5101973;5102000;5102011;5102038;5102044;5102052;5102105;5102109;5102144;5102187</t>
+          <t>5101273;5101283;5101291;5101294;5101321;5101324;5101337;5101392;5101427;5101432;5101434;5101443;5101445;5101464;5101476;5101479;5101485;5101551;5101552;5101555;5101557;5101559;5101589;5101606;5101609;5101631;5101648;5101653;5101656;5101663;5101678;5101682;5101696;5101722;5101739;5101743;5101759;5101765;5101794;5101812;5101813;5101820;5101822;5101827;5101853;5101863;5101864;5101869;5101880;5101882;5101883;5101890;5101905;5101906;5101918;5101928;5101939;5101946;5101947;5101954;5101956;5101973;5101985;5101990;5102000;5102011;5102050;5102052;5102105;5102113;5102144;5102155;5102156;5102159;5102168;5102187</t>
         </is>
       </c>
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>lines 24 and 30 resolve uniquely to serials 5101936 and 5101943, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+          <t>lines 22 and 30 resolve uniquely to serials 5101709 and 5101943, and 24 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 33 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 76 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -13227,7 +13159,7 @@
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
-          <t>ambiguous(4)</t>
+          <t>ambiguous(9)</t>
         </is>
       </c>
       <c r="J215" t="n">
@@ -13235,22 +13167,18 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>5101927;5101940;5102018;5102019</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>5101940</t>
-        </is>
-      </c>
+          <t>5101292;5101334;5101471;5101927;5101940;5102018;5102019;5102025;5102134</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>lines 24 and 30 resolve uniquely to serials 5101936 and 5101943; of this line's 4 candidates exactly one, 5101940, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 22 and 30 resolve uniquely to serials 5101709 and 5101943, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 9 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -13294,7 +13222,7 @@
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
-          <t>ambiguous(7)</t>
+          <t>ambiguous(4)</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -13302,22 +13230,18 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>5101258;5101278;5101331;5101425;5101910;5101942;5101983</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>5101942</t>
-        </is>
-      </c>
+          <t>5101306;5101425;5101910;5101913</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>lines 24 and 30 resolve uniquely to serials 5101936 and 5101943; of this line's 7 candidates exactly one, 5101942, lies in that run, and an unbroken run would put this line at 5101941</t>
+          <t>lines 22 and 30 resolve uniquely to serials 5101709 and 5101943, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>the fingerprint over 24 columns matches 7 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 24 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">

--- a/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
+++ b/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O637"/>
+  <dimension ref="A1:O698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38687,6 +38687,3669 @@
         </is>
       </c>
     </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>213</v>
+      </c>
+      <c r="C638" t="n">
+        <v>1</v>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Casper [M]uller</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Casper Muller</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr"/>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J638" t="n">
+        <v>26</v>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr"/>
+      <c r="M638" t="inlineStr"/>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>213</v>
+      </c>
+      <c r="C639" t="n">
+        <v>2</v>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>W[m]. [?] Sh[e]n[e]r</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>William [?] Shener</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>5101449</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J639" t="n">
+        <v>26</v>
+      </c>
+      <c r="K639" t="inlineStr"/>
+      <c r="L639" t="inlineStr"/>
+      <c r="M639" t="inlineStr"/>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>213</v>
+      </c>
+      <c r="C640" t="n">
+        <v>3</v>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>[D]. [B]. [F]ischo[f]</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>D. B. Fischof</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr"/>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>ambiguous(11)</t>
+        </is>
+      </c>
+      <c r="J640" t="n">
+        <v>26</v>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr"/>
+      <c r="M640" t="inlineStr"/>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>213</v>
+      </c>
+      <c r="C641" t="n">
+        <v>4</v>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>E[ph]e[a]n [?] Sha[i]l[s]</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>[?] Shails</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr"/>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J641" t="n">
+        <v>26</v>
+      </c>
+      <c r="K641" t="inlineStr"/>
+      <c r="L641" t="inlineStr"/>
+      <c r="M641" t="inlineStr"/>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>213</v>
+      </c>
+      <c r="C642" t="n">
+        <v>5</v>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Ch[s]. Raymond</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Charles Raymond</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr"/>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>ambiguous(8)</t>
+        </is>
+      </c>
+      <c r="J642" t="n">
+        <v>26</v>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr"/>
+      <c r="M642" t="inlineStr"/>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>213</v>
+      </c>
+      <c r="C643" t="n">
+        <v>6</v>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>[N]. B. Ca[r]t[e]r</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>N. B. Carter</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr"/>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>ambiguous(8)</t>
+        </is>
+      </c>
+      <c r="J643" t="n">
+        <v>26</v>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr"/>
+      <c r="M643" t="inlineStr"/>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>213</v>
+      </c>
+      <c r="C644" t="n">
+        <v>7</v>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Nath[a]n [E]. King</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Nathan E. King</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr"/>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J644" t="n">
+        <v>26</v>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr"/>
+      <c r="M644" t="inlineStr"/>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>213</v>
+      </c>
+      <c r="C645" t="n">
+        <v>8</v>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>[Ch]ad[w]ell &amp; H. Vail</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Chadwell &amp; H. Vail</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr"/>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J645" t="n">
+        <v>26</v>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr"/>
+      <c r="M645" t="inlineStr"/>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>213</v>
+      </c>
+      <c r="C646" t="n">
+        <v>9</v>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>[S]. M. Wag[e]r</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>S. M. Wager</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr"/>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J646" t="n">
+        <v>26</v>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr"/>
+      <c r="M646" t="inlineStr"/>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>213</v>
+      </c>
+      <c r="C647" t="n">
+        <v>10</v>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>[?] W[m]. C[l]on[e]</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>[?] William Clone</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr"/>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J647" t="n">
+        <v>26</v>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>5101420;5101457;5101810</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr"/>
+      <c r="M647" t="inlineStr"/>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>213</v>
+      </c>
+      <c r="C648" t="n">
+        <v>11</v>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>[A]. [N]. Dea[r]d[e]n</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>A. N. Dearden</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr"/>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J648" t="n">
+        <v>26</v>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr"/>
+      <c r="M648" t="inlineStr"/>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>213</v>
+      </c>
+      <c r="C649" t="n">
+        <v>12</v>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>[E]. [K]. [?]</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr"/>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J649" t="n">
+        <v>26</v>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr"/>
+      <c r="M649" t="inlineStr"/>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>213</v>
+      </c>
+      <c r="C650" t="n">
+        <v>13</v>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>[H]. [H]. Ryan</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>H. H. Ryan</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr"/>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J650" t="n">
+        <v>26</v>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr"/>
+      <c r="M650" t="inlineStr"/>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>213</v>
+      </c>
+      <c r="C651" t="n">
+        <v>14</v>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Chaunc[y] [S]hell</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Chauncy Shell</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr"/>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J651" t="n">
+        <v>26</v>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>5101451;5101461</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr"/>
+      <c r="M651" t="inlineStr"/>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>213</v>
+      </c>
+      <c r="C652" t="n">
+        <v>15</v>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>[Jos]. Pat[h]</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Jos. Path</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr"/>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J652" t="n">
+        <v>26</v>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr"/>
+      <c r="M652" t="inlineStr"/>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>213</v>
+      </c>
+      <c r="C653" t="n">
+        <v>16</v>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>[?]. [B]. Ba[?]</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr"/>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J653" t="n">
+        <v>26</v>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>5101290;5101463;5102140</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr"/>
+      <c r="M653" t="inlineStr"/>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>213</v>
+      </c>
+      <c r="C654" t="n">
+        <v>17</v>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Robert [F]ol[g]an</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Robert Folgan</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr"/>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J654" t="n">
+        <v>26</v>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr"/>
+      <c r="M654" t="inlineStr"/>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>213</v>
+      </c>
+      <c r="C655" t="n">
+        <v>18</v>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>[W]m. Ra[n]kin</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>William Rankin</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>5101435</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J655" t="n">
+        <v>26</v>
+      </c>
+      <c r="K655" t="inlineStr"/>
+      <c r="L655" t="inlineStr"/>
+      <c r="M655" t="inlineStr"/>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>213</v>
+      </c>
+      <c r="C656" t="n">
+        <v>19</v>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>[?] A[b]e[l]e[s]</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>[?] Abeles</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>5101436</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J656" t="n">
+        <v>26</v>
+      </c>
+      <c r="K656" t="inlineStr"/>
+      <c r="L656" t="inlineStr"/>
+      <c r="M656" t="inlineStr"/>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>213</v>
+      </c>
+      <c r="C657" t="n">
+        <v>20</v>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>[W]. [H]o[d]son</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>W. Hodson</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>5101437</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J657" t="n">
+        <v>26</v>
+      </c>
+      <c r="K657" t="inlineStr"/>
+      <c r="L657" t="inlineStr"/>
+      <c r="M657" t="inlineStr"/>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>213</v>
+      </c>
+      <c r="C658" t="n">
+        <v>21</v>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>[H]. [Sp]a[rk]e[r]</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>H. Sparker</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>5101438</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J658" t="n">
+        <v>26</v>
+      </c>
+      <c r="K658" t="inlineStr"/>
+      <c r="L658" t="inlineStr"/>
+      <c r="M658" t="inlineStr"/>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>213</v>
+      </c>
+      <c r="C659" t="n">
+        <v>22</v>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>John H[e]in[i]ck</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>John Heinick</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>5101439</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J659" t="n">
+        <v>26</v>
+      </c>
+      <c r="K659" t="inlineStr"/>
+      <c r="L659" t="inlineStr"/>
+      <c r="M659" t="inlineStr"/>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>213</v>
+      </c>
+      <c r="C660" t="n">
+        <v>23</v>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>[Jos]. Whit[a]k[e]r</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Jos. Whitaker</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr"/>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J660" t="n">
+        <v>26</v>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>5101440;5101728;5101852;5102005;5102094;5102157</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>5101440</t>
+        </is>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>lines 22 and 24 resolve uniquely to serials 5101439 and 5101441; of this line's 6 candidates exactly one, 5101440, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>213</v>
+      </c>
+      <c r="C661" t="n">
+        <v>24</v>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>John Rogan</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>John Rogan</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>5101441</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J661" t="n">
+        <v>26</v>
+      </c>
+      <c r="K661" t="inlineStr"/>
+      <c r="L661" t="inlineStr"/>
+      <c r="M661" t="inlineStr"/>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>213</v>
+      </c>
+      <c r="C662" t="n">
+        <v>25</v>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>A. [S]. Benne[t]</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>A. S. Bennet</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr"/>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J662" t="n">
+        <v>26</v>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>5101442;5102092</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>5101442</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 2 candidates exactly one, 5101442, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>213</v>
+      </c>
+      <c r="C663" t="n">
+        <v>26</v>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Th[os]. P[ag]e</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Thomas Page</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr"/>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J663" t="n">
+        <v>26</v>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>5101443</t>
+        </is>
+      </c>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 43 candidates exactly one, 5101443, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>213</v>
+      </c>
+      <c r="C664" t="n">
+        <v>27</v>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>[Ja]s. M[c]Lea[n]</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>James McLean</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>5101444</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J664" t="n">
+        <v>26</v>
+      </c>
+      <c r="K664" t="inlineStr"/>
+      <c r="L664" t="inlineStr"/>
+      <c r="M664" t="inlineStr"/>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>213</v>
+      </c>
+      <c r="C665" t="n">
+        <v>28</v>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>[L]. [A]. [R]a[ll]s[t]one</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>L. A. Rallstone</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr"/>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J665" t="n">
+        <v>26</v>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>5101283;5101392;5101445;5101559;5101696;5101863</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>5101445</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>lines 27 and 30 resolve uniquely to serials 5101444 and 5101448; of this line's 6 candidates exactly one, 5101445, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>213</v>
+      </c>
+      <c r="C666" t="n">
+        <v>29</v>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>M. [H]. Magi[e]</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>M. H. Magie</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr"/>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J666" t="n">
+        <v>26</v>
+      </c>
+      <c r="K666" t="inlineStr"/>
+      <c r="L666" t="inlineStr"/>
+      <c r="M666" t="inlineStr"/>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>213</v>
+      </c>
+      <c r="C667" t="n">
+        <v>30</v>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>[F]. C. Sherman</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>F. C. Sherman</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>5101448</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J667" t="n">
+        <v>26</v>
+      </c>
+      <c r="K667" t="inlineStr"/>
+      <c r="L667" t="inlineStr"/>
+      <c r="M667" t="inlineStr"/>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>212</v>
+      </c>
+      <c r="C668" t="n">
+        <v>1</v>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>[?] Sawyer</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>[?] Sawyer</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr"/>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>ambiguous(8)</t>
+        </is>
+      </c>
+      <c r="J668" t="n">
+        <v>26</v>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr"/>
+      <c r="M668" t="inlineStr"/>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>212</v>
+      </c>
+      <c r="C669" t="n">
+        <v>2</v>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Joseph Shields</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Joseph Shields</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr"/>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J669" t="n">
+        <v>26</v>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>5101420;5101457;5101810</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="inlineStr"/>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>212</v>
+      </c>
+      <c r="C670" t="n">
+        <v>3</v>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>And[e]rson [L]. Co[x]</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Anderson L. Cox</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr"/>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J670" t="n">
+        <v>26</v>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr"/>
+      <c r="M670" t="inlineStr"/>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>212</v>
+      </c>
+      <c r="C671" t="n">
+        <v>4</v>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Robert Ba[d]y</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Robert Bady</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>5101422</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J671" t="n">
+        <v>26</v>
+      </c>
+      <c r="K671" t="inlineStr"/>
+      <c r="L671" t="inlineStr"/>
+      <c r="M671" t="inlineStr"/>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>212</v>
+      </c>
+      <c r="C672" t="n">
+        <v>5</v>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>D. H. [?]anda[c]k</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>D. H. [?]</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr"/>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J672" t="n">
+        <v>26</v>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>5101423</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>lines 4 and 6 resolve uniquely to serials 5101422 and 5101424; of this line's 10 candidates exactly one, 5101423, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>212</v>
+      </c>
+      <c r="C673" t="n">
+        <v>6</v>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Marg[u]erite M[e]rra[r]d</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Marguerite Merrard</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>5101424</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J673" t="n">
+        <v>26</v>
+      </c>
+      <c r="K673" t="inlineStr"/>
+      <c r="L673" t="inlineStr"/>
+      <c r="M673" t="inlineStr"/>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>212</v>
+      </c>
+      <c r="C674" t="n">
+        <v>7</v>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>David Bra[m]elin</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>David Bramelin</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr"/>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J674" t="n">
+        <v>26</v>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>5101425;5101910</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>5101425</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>lines 6 and 8 resolve uniquely to serials 5101424 and 5101426; of this line's 2 candidates exactly one, 5101425, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>212</v>
+      </c>
+      <c r="C675" t="n">
+        <v>8</v>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Robt. Watts</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Robert Watts</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>5101426</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J675" t="n">
+        <v>26</v>
+      </c>
+      <c r="K675" t="inlineStr"/>
+      <c r="L675" t="inlineStr"/>
+      <c r="M675" t="inlineStr"/>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>212</v>
+      </c>
+      <c r="C676" t="n">
+        <v>9</v>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Wm. Raymond</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>William Raymond</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr"/>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>ambiguous(18)</t>
+        </is>
+      </c>
+      <c r="J676" t="n">
+        <v>26</v>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>5101427;5101555;5101557;5101653;5101682;5101722;5101827;5101864;5101869;5101890;5101905;5101939;5101973;5102000;5102011;5102052;5102105;5102144</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>5101427</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>lines 8 and 10 resolve uniquely to serials 5101426 and 5101428; of this line's 18 candidates exactly one, 5101427, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 18 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>212</v>
+      </c>
+      <c r="C677" t="n">
+        <v>10</v>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>W[m]. [W]arner</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>William Warner</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>5101428</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J677" t="n">
+        <v>26</v>
+      </c>
+      <c r="K677" t="inlineStr"/>
+      <c r="L677" t="inlineStr"/>
+      <c r="M677" t="inlineStr"/>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>212</v>
+      </c>
+      <c r="C678" t="n">
+        <v>11</v>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Ja[s]. C. [?]</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Jas. C. [?]</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>5101429</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J678" t="n">
+        <v>26</v>
+      </c>
+      <c r="K678" t="inlineStr"/>
+      <c r="L678" t="inlineStr"/>
+      <c r="M678" t="inlineStr"/>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>212</v>
+      </c>
+      <c r="C679" t="n">
+        <v>12</v>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>[?] H. Sherm[an]</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>[?] H. Sherman</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>5101430</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J679" t="n">
+        <v>26</v>
+      </c>
+      <c r="K679" t="inlineStr"/>
+      <c r="L679" t="inlineStr"/>
+      <c r="M679" t="inlineStr"/>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>212</v>
+      </c>
+      <c r="C680" t="n">
+        <v>13</v>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>[?]. [K]. Bul[l]</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>[?] K. Bull</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr"/>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>ambiguous(12)</t>
+        </is>
+      </c>
+      <c r="J680" t="n">
+        <v>26</v>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr"/>
+      <c r="M680" t="inlineStr"/>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>212</v>
+      </c>
+      <c r="C681" t="n">
+        <v>14</v>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>John Davis</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>John Davis</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr"/>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J681" t="n">
+        <v>26</v>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr"/>
+      <c r="M681" t="inlineStr"/>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>212</v>
+      </c>
+      <c r="C682" t="n">
+        <v>15</v>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Isaac [?] W[il]mo[t]h</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Isaac [?] Wilmoth</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr"/>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J682" t="n">
+        <v>26</v>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr"/>
+      <c r="M682" t="inlineStr"/>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>212</v>
+      </c>
+      <c r="C683" t="n">
+        <v>16</v>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Mary Willard</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Mary Willard</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr"/>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J683" t="n">
+        <v>26</v>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr"/>
+      <c r="M683" t="inlineStr"/>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>212</v>
+      </c>
+      <c r="C684" t="n">
+        <v>17</v>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Martin Stewart</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Martin Stewart</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>5101404</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J684" t="n">
+        <v>26</v>
+      </c>
+      <c r="K684" t="inlineStr"/>
+      <c r="L684" t="inlineStr"/>
+      <c r="M684" t="inlineStr"/>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>212</v>
+      </c>
+      <c r="C685" t="n">
+        <v>18</v>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>F[r]. Ka[l]bfl[ei]sch</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>[?] Kalbfleisch</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>5101405</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J685" t="n">
+        <v>26</v>
+      </c>
+      <c r="K685" t="inlineStr"/>
+      <c r="L685" t="inlineStr"/>
+      <c r="M685" t="inlineStr"/>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>212</v>
+      </c>
+      <c r="C686" t="n">
+        <v>19</v>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Jam[e]s [?] Morrison</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>James Morrison</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr"/>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J686" t="n">
+        <v>26</v>
+      </c>
+      <c r="K686" t="inlineStr"/>
+      <c r="L686" t="inlineStr"/>
+      <c r="M686" t="inlineStr"/>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>212</v>
+      </c>
+      <c r="C687" t="n">
+        <v>20</v>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>L. Chr[is]t[ia]n[s]</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>L. Christians</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr"/>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>ambiguous(4)</t>
+        </is>
+      </c>
+      <c r="J687" t="n">
+        <v>26</v>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>5101377;5101407;5101520;5101592</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>5101407</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410; of this line's 4 candidates exactly one, 5101407, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>212</v>
+      </c>
+      <c r="C688" t="n">
+        <v>21</v>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Geo. C. Mo[r]e</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>George C. More</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr"/>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J688" t="n">
+        <v>26</v>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr"/>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>212</v>
+      </c>
+      <c r="C689" t="n">
+        <v>22</v>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>[J]. Kir[t]la[n]d</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>J. Kirtland</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr"/>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J689" t="n">
+        <v>26</v>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr"/>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>212</v>
+      </c>
+      <c r="C690" t="n">
+        <v>23</v>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Jas. Edmu[n]ds</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>James Edmunds</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>5101410</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J690" t="n">
+        <v>26</v>
+      </c>
+      <c r="K690" t="inlineStr"/>
+      <c r="L690" t="inlineStr"/>
+      <c r="M690" t="inlineStr"/>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>212</v>
+      </c>
+      <c r="C691" t="n">
+        <v>24</v>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>John P[e]irc[e]</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>John Peirce</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr"/>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J691" t="n">
+        <v>26</v>
+      </c>
+      <c r="K691" t="inlineStr"/>
+      <c r="L691" t="inlineStr"/>
+      <c r="M691" t="inlineStr"/>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>212</v>
+      </c>
+      <c r="C692" t="n">
+        <v>25</v>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>[P]. Lawrence</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>P. Lawrence</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>5101412</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J692" t="n">
+        <v>26</v>
+      </c>
+      <c r="K692" t="inlineStr"/>
+      <c r="L692" t="inlineStr"/>
+      <c r="M692" t="inlineStr"/>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>212</v>
+      </c>
+      <c r="C693" t="n">
+        <v>26</v>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>[J]. [C]. Walker</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>J. C. Walker</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr"/>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J693" t="n">
+        <v>26</v>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>5101413</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>lines 25 and 27 resolve uniquely to serials 5101412 and 5101414; of this line's 10 candidates exactly one, 5101413, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>212</v>
+      </c>
+      <c r="C694" t="n">
+        <v>27</v>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>[W]m. Williams</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>William Williams</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>5101414</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J694" t="n">
+        <v>26</v>
+      </c>
+      <c r="K694" t="inlineStr"/>
+      <c r="L694" t="inlineStr"/>
+      <c r="M694" t="inlineStr"/>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>212</v>
+      </c>
+      <c r="C695" t="n">
+        <v>28</v>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>W. Nelson</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>W. Nelson</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>5101415</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J695" t="n">
+        <v>26</v>
+      </c>
+      <c r="K695" t="inlineStr"/>
+      <c r="L695" t="inlineStr"/>
+      <c r="M695" t="inlineStr"/>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>212</v>
+      </c>
+      <c r="C696" t="n">
+        <v>29</v>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Geo. Merrill</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>George Merrill</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr"/>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J696" t="n">
+        <v>26</v>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr"/>
+      <c r="M696" t="inlineStr"/>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>212</v>
+      </c>
+      <c r="C697" t="n">
+        <v>30</v>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>J. W. Salisbury</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>J. W. Salisbury</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr"/>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J697" t="n">
+        <v>26</v>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr"/>
+      <c r="M697" t="inlineStr"/>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>212</v>
+      </c>
+      <c r="C698" t="n">
+        <v>31</v>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>John Parkin</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>John Parkin</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J698" t="n">
+        <v>26</v>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr"/>
+      <c r="M698" t="inlineStr"/>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
+++ b/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O698"/>
+  <dimension ref="A1:O759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38690,28 +38690,28 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B638" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C638" t="n">
         <v>1</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Casper [M]uller</t>
+          <t>E. C. Stowell</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Casper Muller</t>
+          <t>E. C. Stowell</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -38719,53 +38719,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H638" t="inlineStr"/>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>5101477</t>
+        </is>
+      </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J638" t="n">
         <v>26</v>
       </c>
-      <c r="K638" t="inlineStr">
-        <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
-        </is>
-      </c>
+      <c r="K638" t="inlineStr"/>
       <c r="L638" t="inlineStr"/>
       <c r="M638" t="inlineStr"/>
       <c r="N638" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O638" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B639" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C639" t="n">
         <v>2</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>W[m]. [?] Sh[e]n[e]r</t>
+          <t>Jno. Hodges</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>William [?] Shener</t>
+          <t>Jno. Hodges</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -38780,7 +38780,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>5101449</t>
+          <t>5101480</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -38801,30 +38801,30 @@
       </c>
       <c r="O639" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B640" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C640" t="n">
         <v>3</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>[D]. [B]. [F]ischo[f]</t>
+          <t>Samuel Cha[p]in</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>D. B. Fischof</t>
+          <t>Samuel Cha[p]in</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
@@ -38837,53 +38837,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H640" t="inlineStr"/>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>5101481</t>
+        </is>
+      </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>ambiguous(11)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J640" t="n">
         <v>26</v>
       </c>
-      <c r="K640" t="inlineStr">
-        <is>
-          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
-        </is>
-      </c>
+      <c r="K640" t="inlineStr"/>
       <c r="L640" t="inlineStr"/>
       <c r="M640" t="inlineStr"/>
       <c r="N640" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B641" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C641" t="n">
         <v>4</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>E[ph]e[a]n [?] Sha[i]l[s]</t>
+          <t>Chs. L. Drag[u]a</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>[?] Shails</t>
+          <t>Chs. L. Drag[u]a</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
@@ -38896,10 +38896,14 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H641" t="inlineStr"/>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>5101482</t>
+        </is>
+      </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J641" t="n">
@@ -38910,40 +38914,40 @@
       <c r="M641" t="inlineStr"/>
       <c r="N641" t="inlineStr">
         <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B642" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C642" t="n">
         <v>5</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Ch[s]. Raymond</t>
+          <t>[W]il[lia]m Ta[f]f</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Charles Raymond</t>
+          <t>[W]il[lia]m Ta[f]f</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -38954,7 +38958,7 @@
       <c r="H642" t="inlineStr"/>
       <c r="I642" t="inlineStr">
         <is>
-          <t>ambiguous(8)</t>
+          <t>ambiguous(11)</t>
         </is>
       </c>
       <c r="J642" t="n">
@@ -38962,47 +38966,55 @@
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
-        </is>
-      </c>
-      <c r="L642" t="inlineStr"/>
-      <c r="M642" t="inlineStr"/>
+          <t>5101363;5101483;5101491;5101519;5101721;5101748;5101819;5102023;5102132;5102194;5102211</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>5101483</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>lines 4 and 6 resolve uniquely to serials 5101482 and 5101484; of this line's 11 candidates exactly one, 5101483, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B643" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C643" t="n">
         <v>6</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>[N]. B. Ca[r]t[e]r</t>
+          <t>Chs. B. Benjamin</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>N. B. Carter</t>
+          <t>Chs. B. Benjamin</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -39010,58 +39022,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H643" t="inlineStr"/>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>5101484</t>
+        </is>
+      </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>ambiguous(8)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J643" t="n">
         <v>26</v>
       </c>
-      <c r="K643" t="inlineStr">
-        <is>
-          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
-        </is>
-      </c>
+      <c r="K643" t="inlineStr"/>
       <c r="L643" t="inlineStr"/>
       <c r="M643" t="inlineStr"/>
       <c r="N643" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O643" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B644" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C644" t="n">
         <v>7</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Nath[a]n [E]. King</t>
+          <t>Jno. C. Dunican</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Nathan E. King</t>
+          <t>Jno. C. Dunican</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -39080,11 +39092,19 @@
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L644" t="inlineStr"/>
-      <c r="M644" t="inlineStr"/>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>5101485</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>lines 6 and 8 resolve uniquely to serials 5101484 and 5101486; of this line's 43 candidates exactly one, 5101485, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N644" t="inlineStr">
         <is>
           <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
@@ -39092,30 +39112,30 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B645" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C645" t="n">
         <v>8</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>[Ch]ad[w]ell &amp; H. Vail</t>
+          <t>[?]</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Chadwell &amp; H. Vail</t>
+          <t>[?]</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
@@ -39128,53 +39148,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H645" t="inlineStr"/>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>5101486</t>
+        </is>
+      </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>ambiguous(6)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J645" t="n">
         <v>26</v>
       </c>
-      <c r="K645" t="inlineStr">
-        <is>
-          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
-        </is>
-      </c>
+      <c r="K645" t="inlineStr"/>
       <c r="L645" t="inlineStr"/>
       <c r="M645" t="inlineStr"/>
       <c r="N645" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B646" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C646" t="n">
         <v>9</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>[S]. M. Wag[e]r</t>
+          <t>[?]m. Morrison</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>S. M. Wager</t>
+          <t>[?]m. Morrison</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
@@ -39187,53 +39207,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H646" t="inlineStr"/>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>5101487</t>
+        </is>
+      </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J646" t="n">
         <v>26</v>
       </c>
-      <c r="K646" t="inlineStr">
-        <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
-        </is>
-      </c>
+      <c r="K646" t="inlineStr"/>
       <c r="L646" t="inlineStr"/>
       <c r="M646" t="inlineStr"/>
       <c r="N646" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B647" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C647" t="n">
         <v>10</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>[?] W[m]. C[l]on[e]</t>
+          <t>[Sam]l. J. Brown</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>[?] William Clone</t>
+          <t>[Sam]l. J. Brown</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
@@ -39246,53 +39266,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H647" t="inlineStr"/>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>5101488</t>
+        </is>
+      </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J647" t="n">
         <v>26</v>
       </c>
-      <c r="K647" t="inlineStr">
-        <is>
-          <t>5101420;5101457;5101810</t>
-        </is>
-      </c>
+      <c r="K647" t="inlineStr"/>
       <c r="L647" t="inlineStr"/>
       <c r="M647" t="inlineStr"/>
       <c r="N647" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B648" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C648" t="n">
         <v>11</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>[A]. [N]. Dea[r]d[e]n</t>
+          <t>[H]enry Morrison</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>A. N. Dearden</t>
+          <t>[H]enry Morrison</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
@@ -39305,53 +39325,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H648" t="inlineStr"/>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>5101489</t>
+        </is>
+      </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J648" t="n">
         <v>26</v>
       </c>
-      <c r="K648" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
+      <c r="K648" t="inlineStr"/>
       <c r="L648" t="inlineStr"/>
       <c r="M648" t="inlineStr"/>
       <c r="N648" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O648" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B649" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C649" t="n">
         <v>12</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>[E]. [K]. [?]</t>
+          <t>Jas. W. Bend[l]ey</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>Jas. W. Bend[l]ey</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
@@ -39367,7 +39387,7 @@
       <c r="H649" t="inlineStr"/>
       <c r="I649" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J649" t="n">
@@ -39375,42 +39395,50 @@
       </c>
       <c r="K649" t="inlineStr">
         <is>
-          <t>5101408;5101409;5101459</t>
-        </is>
-      </c>
-      <c r="L649" t="inlineStr"/>
-      <c r="M649" t="inlineStr"/>
+          <t>5101490;5101662</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>5101490</t>
+        </is>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>lines 11 and 15 resolve uniquely to serials 5101489 and 5101493; of this line's 2 candidates exactly one, 5101490, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N649" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O649" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B650" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C650" t="n">
         <v>13</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>[H]. [H]. Ryan</t>
+          <t>Ge[o]. M[u]nn</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>H. H. Ryan</t>
+          <t>Ge[o]. M[u]nn</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
@@ -39426,7 +39454,7 @@
       <c r="H650" t="inlineStr"/>
       <c r="I650" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(11)</t>
         </is>
       </c>
       <c r="J650" t="n">
@@ -39434,47 +39462,55 @@
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L650" t="inlineStr"/>
-      <c r="M650" t="inlineStr"/>
+          <t>5101363;5101483;5101491;5101519;5101721;5101748;5101819;5102023;5102132;5102194;5102211</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>5101491</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>lines 11 and 15 resolve uniquely to serials 5101489 and 5101493; of this line's 11 candidates exactly one, 5101491, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N650" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B651" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C651" t="n">
         <v>14</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Chaunc[y] [S]hell</t>
+          <t>Jno. B. Mitchell</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Chauncy Shell</t>
+          <t>Jno. B. Mitchell</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -39493,11 +39529,19 @@
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>5101451;5101461</t>
-        </is>
-      </c>
-      <c r="L651" t="inlineStr"/>
-      <c r="M651" t="inlineStr"/>
+          <t>5101358;5101492</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>5101492</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>lines 11 and 15 resolve uniquely to serials 5101489 and 5101493; of this line's 2 candidates exactly one, 5101492, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N651" t="inlineStr">
         <is>
           <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
@@ -39505,35 +39549,35 @@
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B652" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C652" t="n">
         <v>15</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>[Jos]. Pat[h]</t>
+          <t>[Th]os. Ladd</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Jos. Path</t>
+          <t>[Th]os. Ladd</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -39541,53 +39585,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H652" t="inlineStr"/>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>5101493</t>
+        </is>
+      </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J652" t="n">
         <v>26</v>
       </c>
-      <c r="K652" t="inlineStr">
-        <is>
-          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
-        </is>
-      </c>
+      <c r="K652" t="inlineStr"/>
       <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr"/>
       <c r="N652" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B653" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C653" t="n">
         <v>16</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>[?]. [B]. Ba[?]</t>
+          <t>Ja[s]. [K]ean</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>Ja[s]. [K]ean</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
@@ -39603,7 +39647,7 @@
       <c r="H653" t="inlineStr"/>
       <c r="I653" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J653" t="n">
@@ -39611,42 +39655,42 @@
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>5101290;5101463;5102140</t>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
         </is>
       </c>
       <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr"/>
       <c r="N653" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B654" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C654" t="n">
         <v>17</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>Robert [F]ol[g]an</t>
+          <t>W. H. Bra[i]nbridge</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>Robert Folgan</t>
+          <t>W. H. Bra[i]nbridge</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
@@ -39662,7 +39706,7 @@
       <c r="H654" t="inlineStr"/>
       <c r="I654" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(27)</t>
         </is>
       </c>
       <c r="J654" t="n">
@@ -39670,47 +39714,47 @@
       </c>
       <c r="K654" t="inlineStr">
         <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+          <t>5101279;5101385;5101465;5101540;5101684;5101685;5101689;5101708;5101710;5101723;5101726;5101744;5101764;5101779;5101780;5101784;5101792;5101842;5101898;5101935;5101980;5101986;5101994;5102009;5102055;5102077;5102090</t>
         </is>
       </c>
       <c r="L654" t="inlineStr"/>
       <c r="M654" t="inlineStr"/>
       <c r="N654" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 27 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O654" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B655" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C655" t="n">
         <v>18</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>[W]m. Ra[n]kin</t>
+          <t>[J]no. Mars[h] W. Cad[y]</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>William Rankin</t>
+          <t>[J]no. Mars[h] W. Cad[y]</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -39720,7 +39764,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>5101435</t>
+          <t>5101466</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -39741,30 +39785,30 @@
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B656" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C656" t="n">
         <v>19</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>[?] A[b]e[l]e[s]</t>
+          <t>[I]saac Stua[r]t</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>[?] Abeles</t>
+          <t>[I]saac Stua[r]t</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
@@ -39779,7 +39823,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>5101436</t>
+          <t>5101467</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -39800,30 +39844,30 @@
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B657" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C657" t="n">
         <v>20</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>[W]. [H]o[d]son</t>
+          <t>[J]os[eph] L. M[u]ll[i]n</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>W. Hodson</t>
+          <t>[J]os[eph] L. M[u]ll[i]n</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -39838,7 +39882,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>5101437</t>
+          <t>5101468</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -39859,35 +39903,35 @@
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B658" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C658" t="n">
         <v>21</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>[H]. [Sp]a[rk]e[r]</t>
+          <t>R. W. Patterson</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>H. Sparker</t>
+          <t>R. W. Patterson</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
@@ -39895,58 +39939,66 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H658" t="inlineStr">
-        <is>
-          <t>5101438</t>
-        </is>
-      </c>
+      <c r="H658" t="inlineStr"/>
       <c r="I658" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J658" t="n">
         <v>26</v>
       </c>
-      <c r="K658" t="inlineStr"/>
-      <c r="L658" t="inlineStr"/>
-      <c r="M658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>5101469</t>
+        </is>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>lines 20 and 22 resolve uniquely to serials 5101468 and 5101470; of this line's 43 candidates exactly one, 5101469, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N658" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B659" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C659" t="n">
         <v>22</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>John H[e]in[i]ck</t>
+          <t>[J]. [H]. Collins</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>John Heinick</t>
+          <t>[J]. [H]. Collins</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
@@ -39956,7 +40008,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>5101439</t>
+          <t>5101470</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -39977,30 +40029,30 @@
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B660" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C660" t="n">
         <v>23</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>[Jos]. Whit[a]k[e]r</t>
+          <t>Ethan Bu[t]ler</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Jos. Whitaker</t>
+          <t>Ethan Bu[t]ler</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
@@ -40016,7 +40068,7 @@
       <c r="H660" t="inlineStr"/>
       <c r="I660" t="inlineStr">
         <is>
-          <t>ambiguous(6)</t>
+          <t>ambiguous(4)</t>
         </is>
       </c>
       <c r="J660" t="n">
@@ -40024,55 +40076,55 @@
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>5101440;5101728;5101852;5102005;5102094;5102157</t>
+          <t>5101292;5101471;5102025;5102134</t>
         </is>
       </c>
       <c r="L660" t="inlineStr">
         <is>
-          <t>5101440</t>
+          <t>5101471</t>
         </is>
       </c>
       <c r="M660" t="inlineStr">
         <is>
-          <t>lines 22 and 24 resolve uniquely to serials 5101439 and 5101441; of this line's 6 candidates exactly one, 5101440, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 22 and 24 resolve uniquely to serials 5101470 and 5101472; of this line's 4 candidates exactly one, 5101471, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N660" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O660" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B661" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C661" t="n">
         <v>24</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>John Rogan</t>
+          <t>E[?]ra Wood[?]ur[y]</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>John Rogan</t>
+          <t>E[?]ra Wood[?]ur[y]</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -40082,7 +40134,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>5101441</t>
+          <t>5101472</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40103,35 +40155,35 @@
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B662" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C662" t="n">
         <v>25</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>A. [S]. Benne[t]</t>
+          <t>[J]no. Sammon[s]</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>A. S. Bennet</t>
+          <t>[J]no. Sammon[s]</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -40139,66 +40191,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H662" t="inlineStr"/>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>5101473</t>
+        </is>
+      </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J662" t="n">
         <v>26</v>
       </c>
-      <c r="K662" t="inlineStr">
-        <is>
-          <t>5101442;5102092</t>
-        </is>
-      </c>
-      <c r="L662" t="inlineStr">
-        <is>
-          <t>5101442</t>
-        </is>
-      </c>
-      <c r="M662" t="inlineStr">
-        <is>
-          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 2 candidates exactly one, 5101442, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K662" t="inlineStr"/>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="inlineStr"/>
       <c r="N662" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B663" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C663" t="n">
         <v>26</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Th[os]. P[ag]e</t>
+          <t>H. S. Cushing</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Thomas Page</t>
+          <t>H. S. Cushing</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -40209,7 +40253,7 @@
       <c r="H663" t="inlineStr"/>
       <c r="I663" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J663" t="n">
@@ -40217,55 +40261,55 @@
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+          <t>5101474;5101657</t>
         </is>
       </c>
       <c r="L663" t="inlineStr">
         <is>
-          <t>5101443</t>
+          <t>5101474</t>
         </is>
       </c>
       <c r="M663" t="inlineStr">
         <is>
-          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 43 candidates exactly one, 5101443, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 25 and 27 resolve uniquely to serials 5101473 and 5101475; of this line's 2 candidates exactly one, 5101474, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N663" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O663" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B664" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C664" t="n">
         <v>27</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>[Ja]s. M[c]Lea[n]</t>
+          <t>[W]m. Smith</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>James McLean</t>
+          <t>[W]m. Smith</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -40275,7 +40319,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>5101444</t>
+          <t>5101475</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40296,35 +40340,35 @@
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B665" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C665" t="n">
         <v>28</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>[L]. [A]. [R]a[ll]s[t]one</t>
+          <t>W. S. Lockrid[g]e</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>L. A. Rallstone</t>
+          <t>W. S. Lockrid[g]e</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -40335,7 +40379,7 @@
       <c r="H665" t="inlineStr"/>
       <c r="I665" t="inlineStr">
         <is>
-          <t>ambiguous(6)</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J665" t="n">
@@ -40343,55 +40387,47 @@
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>5101283;5101392;5101445;5101559;5101696;5101863</t>
-        </is>
-      </c>
-      <c r="L665" t="inlineStr">
-        <is>
-          <t>5101445</t>
-        </is>
-      </c>
-      <c r="M665" t="inlineStr">
-        <is>
-          <t>lines 27 and 30 resolve uniquely to serials 5101444 and 5101448; of this line's 6 candidates exactly one, 5101445, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr"/>
+      <c r="M665" t="inlineStr"/>
       <c r="N665" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O665" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C666" t="n">
         <v>29</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>M. [H]. Magi[e]</t>
+          <t>[M]. Worthingt[o]n</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>M. H. Magie</t>
+          <t>[M]. Worthingt[o]n</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -40402,51 +40438,55 @@
       <c r="H666" t="inlineStr"/>
       <c r="I666" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ambiguous(4)</t>
         </is>
       </c>
       <c r="J666" t="n">
         <v>26</v>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>5101478;5101871;5101878;5102108</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr"/>
       <c r="M666" t="inlineStr"/>
       <c r="N666" t="inlineStr">
         <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O666" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-BP</t>
         </is>
       </c>
       <c r="B667" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C667" t="n">
         <v>30</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>[F]. C. Sherman</t>
+          <t>[P]. [R]. F[ie]ld</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>F. C. Sherman</t>
+          <t>[P]. [R]. F[ie]ld</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -40454,58 +40494,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H667" t="inlineStr">
-        <is>
-          <t>5101448</t>
-        </is>
-      </c>
+      <c r="H667" t="inlineStr"/>
       <c r="I667" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J667" t="n">
         <v>26</v>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr"/>
       <c r="M667" t="inlineStr"/>
       <c r="N667" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B668" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C668" t="n">
         <v>1</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>[?] Sawyer</t>
+          <t>Jno. Beach</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>[?] Sawyer</t>
+          <t>Jno. Beach</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -40513,53 +40553,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H668" t="inlineStr"/>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>5101660</t>
+        </is>
+      </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>ambiguous(8)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J668" t="n">
         <v>26</v>
       </c>
-      <c r="K668" t="inlineStr">
-        <is>
-          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
-        </is>
-      </c>
+      <c r="K668" t="inlineStr"/>
       <c r="L668" t="inlineStr"/>
       <c r="M668" t="inlineStr"/>
       <c r="N668" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B669" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C669" t="n">
         <v>2</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Joseph Shields</t>
+          <t>Phill[i]p Dean</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>Joseph Shields</t>
+          <t>Phill[i]p Dean</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
@@ -40575,7 +40615,7 @@
       <c r="H669" t="inlineStr"/>
       <c r="I669" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>ambiguous(10)</t>
         </is>
       </c>
       <c r="J669" t="n">
@@ -40583,47 +40623,55 @@
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>5101420;5101457;5101810</t>
-        </is>
-      </c>
-      <c r="L669" t="inlineStr"/>
-      <c r="M669" t="inlineStr"/>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>5101664</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>lines 1 and 3 resolve uniquely to serials 5101660 and 5101665; of this line's 10 candidates exactly one, 5101664, lies in that run, and an unbroken run would put this line at 5101661</t>
+        </is>
+      </c>
       <c r="N669" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B670" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C670" t="n">
         <v>3</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>And[e]rson [L]. Co[x]</t>
+          <t>[J]. S. Roby</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>Anderson L. Cox</t>
+          <t>[J]. S. Roby</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -40631,58 +40679,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H670" t="inlineStr"/>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>5101665</t>
+        </is>
+      </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J670" t="n">
         <v>26</v>
       </c>
-      <c r="K670" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
+      <c r="K670" t="inlineStr"/>
       <c r="L670" t="inlineStr"/>
       <c r="M670" t="inlineStr"/>
       <c r="N670" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B671" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C671" t="n">
         <v>4</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Robert Ba[d]y</t>
+          <t>Salman Hyde</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Robert Bady</t>
+          <t>Salman Hyde</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -40692,7 +40740,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>5101422</t>
+          <t>5101666</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -40713,35 +40761,35 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B672" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C672" t="n">
         <v>5</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>D. H. [?]anda[c]k</t>
+          <t>Mrs. Mary Brown</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>D. H. [?]</t>
+          <t>Mrs. Mary Brown</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -40749,61 +40797,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H672" t="inlineStr"/>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>5101667</t>
+        </is>
+      </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J672" t="n">
         <v>26</v>
       </c>
-      <c r="K672" t="inlineStr">
-        <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
-        </is>
-      </c>
-      <c r="L672" t="inlineStr">
-        <is>
-          <t>5101423</t>
-        </is>
-      </c>
-      <c r="M672" t="inlineStr">
-        <is>
-          <t>lines 4 and 6 resolve uniquely to serials 5101422 and 5101424; of this line's 10 candidates exactly one, 5101423, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K672" t="inlineStr"/>
+      <c r="L672" t="inlineStr"/>
+      <c r="M672" t="inlineStr"/>
       <c r="N672" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B673" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C673" t="n">
         <v>6</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Marg[u]erite M[e]rra[r]d</t>
+          <t>Julius Ma[l]Kay</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Marguerite Merrard</t>
+          <t>Julius Ma[l]Kay</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
@@ -40816,58 +40856,66 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H673" t="inlineStr">
-        <is>
-          <t>5101424</t>
-        </is>
-      </c>
+      <c r="H673" t="inlineStr"/>
       <c r="I673" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J673" t="n">
         <v>26</v>
       </c>
-      <c r="K673" t="inlineStr"/>
-      <c r="L673" t="inlineStr"/>
-      <c r="M673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>5101668;5101790</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>5101668</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>lines 5 and 9 resolve uniquely to serials 5101667 and 5101671; of this line's 2 candidates exactly one, 5101668, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N673" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B674" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C674" t="n">
         <v>7</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>David Bra[m]elin</t>
+          <t>Levi Reynalds</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>David Bramelin</t>
+          <t>Levi Reynalds</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -40878,7 +40926,7 @@
       <c r="H674" t="inlineStr"/>
       <c r="I674" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>ambiguous(5)</t>
         </is>
       </c>
       <c r="J674" t="n">
@@ -40886,50 +40934,50 @@
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>5101425;5101910</t>
+          <t>5101669;5101807;5101808;5101873;5102056</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
         <is>
-          <t>5101425</t>
+          <t>5101669</t>
         </is>
       </c>
       <c r="M674" t="inlineStr">
         <is>
-          <t>lines 6 and 8 resolve uniquely to serials 5101424 and 5101426; of this line's 2 candidates exactly one, 5101425, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 5 and 9 resolve uniquely to serials 5101667 and 5101671; of this line's 5 candidates exactly one, 5101669, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N674" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 5 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B675" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C675" t="n">
         <v>8</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Robt. Watts</t>
+          <t>William Bell</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Robert Watts</t>
+          <t>William Bell</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
@@ -40942,53 +40990,61 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H675" t="inlineStr">
-        <is>
-          <t>5101426</t>
-        </is>
-      </c>
+      <c r="H675" t="inlineStr"/>
       <c r="I675" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J675" t="n">
         <v>26</v>
       </c>
-      <c r="K675" t="inlineStr"/>
-      <c r="L675" t="inlineStr"/>
-      <c r="M675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>5101670;5101965</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>5101670</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>lines 5 and 9 resolve uniquely to serials 5101667 and 5101671; of this line's 2 candidates exactly one, 5101670, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N675" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C676" t="n">
         <v>9</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Wm. Raymond</t>
+          <t>Benj[n]. Jacobs</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>William Raymond</t>
+          <t>Benj[n]. Jacobs</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
@@ -41001,61 +41057,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H676" t="inlineStr"/>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>5101671</t>
+        </is>
+      </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>ambiguous(18)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J676" t="n">
         <v>26</v>
       </c>
-      <c r="K676" t="inlineStr">
-        <is>
-          <t>5101427;5101555;5101557;5101653;5101682;5101722;5101827;5101864;5101869;5101890;5101905;5101939;5101973;5102000;5102011;5102052;5102105;5102144</t>
-        </is>
-      </c>
-      <c r="L676" t="inlineStr">
-        <is>
-          <t>5101427</t>
-        </is>
-      </c>
-      <c r="M676" t="inlineStr">
-        <is>
-          <t>lines 8 and 10 resolve uniquely to serials 5101426 and 5101428; of this line's 18 candidates exactly one, 5101427, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K676" t="inlineStr"/>
+      <c r="L676" t="inlineStr"/>
+      <c r="M676" t="inlineStr"/>
       <c r="N676" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 18 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O676" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B677" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C677" t="n">
         <v>10</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>W[m]. [W]arner</t>
+          <t>Sam[l]. J. W. Gilbert</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>William Warner</t>
+          <t>Sam[l]. J. W. Gilbert</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
@@ -41070,7 +41118,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>5101428</t>
+          <t>5101672</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41091,30 +41139,30 @@
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B678" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C678" t="n">
         <v>11</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Ja[s]. C. [?]</t>
+          <t>H. R. W[i]ll[i]s</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Jas. C. [?]</t>
+          <t>H. R. W[i]ll[i]s</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
@@ -41129,7 +41177,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>5101429</t>
+          <t>5101673</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41150,35 +41198,35 @@
       </c>
       <c r="O678" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B679" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C679" t="n">
         <v>12</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>[?] H. Sherm[an]</t>
+          <t>Alex[r]. Loyd</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>[?] H. Sherman</t>
+          <t>Alex[r]. Loyd</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -41188,7 +41236,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>5101430</t>
+          <t>5101674</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41209,35 +41257,35 @@
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B680" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C680" t="n">
         <v>13</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>[?]. [K]. Bul[l]</t>
+          <t>James Scott</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>[?] K. Bull</t>
+          <t>James Scott</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -41245,58 +41293,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H680" t="inlineStr"/>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>5101675</t>
+        </is>
+      </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>ambiguous(12)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J680" t="n">
         <v>26</v>
       </c>
-      <c r="K680" t="inlineStr">
-        <is>
-          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
-        </is>
-      </c>
+      <c r="K680" t="inlineStr"/>
       <c r="L680" t="inlineStr"/>
       <c r="M680" t="inlineStr"/>
       <c r="N680" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O680" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B681" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C681" t="n">
         <v>14</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>John Davis</t>
+          <t>[?]o. [D]esthalai[s]</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>John Davis</t>
+          <t>[?]o. [D]esthalai[s]</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
@@ -41315,11 +41363,19 @@
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
-      <c r="L681" t="inlineStr"/>
-      <c r="M681" t="inlineStr"/>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>5101676</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>lines 13 and 15 resolve uniquely to serials 5101675 and 5101677; of this line's 43 candidates exactly one, 5101676, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N681" t="inlineStr">
         <is>
           <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
@@ -41327,30 +41383,30 @@
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B682" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C682" t="n">
         <v>15</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Isaac [?] W[il]mo[t]h</t>
+          <t>B[a]rnihart [B]la[u]ey</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Isaac [?] Wilmoth</t>
+          <t>B[a]rnihart [B]la[u]ey</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
@@ -41363,58 +41419,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H682" t="inlineStr"/>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>5101677</t>
+        </is>
+      </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J682" t="n">
         <v>26</v>
       </c>
-      <c r="K682" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
+      <c r="K682" t="inlineStr"/>
       <c r="L682" t="inlineStr"/>
       <c r="M682" t="inlineStr"/>
       <c r="N682" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B683" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C683" t="n">
         <v>16</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Mary Willard</t>
+          <t>Adolp[h] Micha[e]l</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Mary Willard</t>
+          <t>Adolp[h] Micha[e]l</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -41433,7 +41489,7 @@
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
         </is>
       </c>
       <c r="L683" t="inlineStr"/>
@@ -41445,30 +41501,30 @@
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B684" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C684" t="n">
         <v>17</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Martin Stewart</t>
+          <t>Peter Case</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Martin Stewart</t>
+          <t>Peter Case</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
@@ -41483,7 +41539,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>5101404</t>
+          <t>5101648</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -41504,35 +41560,35 @@
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B685" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C685" t="n">
         <v>18</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>F[r]. Ka[l]bfl[ei]sch</t>
+          <t>Fred Goodman</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>[?] Kalbfleisch</t>
+          <t>Fred Goodman</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -41542,7 +41598,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>5101405</t>
+          <t>5101649</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -41563,35 +41619,35 @@
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B686" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C686" t="n">
         <v>19</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Jam[e]s [?] Morrison</t>
+          <t>[J]ohn Case</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>James Morrison</t>
+          <t>[J]ohn Case</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -41602,46 +41658,58 @@
       <c r="H686" t="inlineStr"/>
       <c r="I686" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ambiguous(11)</t>
         </is>
       </c>
       <c r="J686" t="n">
         <v>26</v>
       </c>
-      <c r="K686" t="inlineStr"/>
-      <c r="L686" t="inlineStr"/>
-      <c r="M686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>5101650</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>lines 18 and 20 resolve uniquely to serials 5101649 and 5101651; of this line's 11 candidates exactly one, 5101650, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N686" t="inlineStr">
         <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B687" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C687" t="n">
         <v>20</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>L. Chr[is]t[ia]n[s]</t>
+          <t>[G]. Shee</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>L. Christians</t>
+          <t>[G]. Shee</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
@@ -41654,66 +41722,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H687" t="inlineStr"/>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>5101651</t>
+        </is>
+      </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>ambiguous(4)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J687" t="n">
         <v>26</v>
       </c>
-      <c r="K687" t="inlineStr">
-        <is>
-          <t>5101377;5101407;5101520;5101592</t>
-        </is>
-      </c>
-      <c r="L687" t="inlineStr">
-        <is>
-          <t>5101407</t>
-        </is>
-      </c>
-      <c r="M687" t="inlineStr">
-        <is>
-          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410; of this line's 4 candidates exactly one, 5101407, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K687" t="inlineStr"/>
+      <c r="L687" t="inlineStr"/>
+      <c r="M687" t="inlineStr"/>
       <c r="N687" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B688" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C688" t="n">
         <v>21</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Geo. C. Mo[r]e</t>
+          <t>William Higgins</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>George C. More</t>
+          <t>William Higgins</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -41724,7 +41784,7 @@
       <c r="H688" t="inlineStr"/>
       <c r="I688" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J688" t="n">
@@ -41732,46 +41792,42 @@
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>5101408;5101409;5101459</t>
+          <t>5101652;5101738</t>
         </is>
       </c>
       <c r="L688" t="inlineStr"/>
-      <c r="M688" t="inlineStr">
-        <is>
-          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
-        </is>
-      </c>
+      <c r="M688" t="inlineStr"/>
       <c r="N688" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O688" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B689" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C689" t="n">
         <v>22</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>[J]. Kir[t]la[n]d</t>
+          <t>Sherman Ho[e]r</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>J. Kirtland</t>
+          <t>Sherman Ho[e]r</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
@@ -41787,7 +41843,7 @@
       <c r="H689" t="inlineStr"/>
       <c r="I689" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>ambiguous(18)</t>
         </is>
       </c>
       <c r="J689" t="n">
@@ -41795,46 +41851,42 @@
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>5101408;5101409;5101459</t>
+          <t>5101427;5101555;5101557;5101653;5101682;5101722;5101827;5101864;5101869;5101890;5101905;5101939;5101973;5102000;5102011;5102052;5102105;5102144</t>
         </is>
       </c>
       <c r="L689" t="inlineStr"/>
-      <c r="M689" t="inlineStr">
-        <is>
-          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
-        </is>
-      </c>
+      <c r="M689" t="inlineStr"/>
       <c r="N689" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 18 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B690" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C690" t="n">
         <v>23</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Jas. Edmu[n]ds</t>
+          <t>Cale[b] Lyman</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>James Edmunds</t>
+          <t>Cale[b] Lyman</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
@@ -41847,53 +41899,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H690" t="inlineStr">
-        <is>
-          <t>5101410</t>
-        </is>
-      </c>
+      <c r="H690" t="inlineStr"/>
       <c r="I690" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(11)</t>
         </is>
       </c>
       <c r="J690" t="n">
         <v>26</v>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr"/>
       <c r="M690" t="inlineStr"/>
       <c r="N690" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B691" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C691" t="n">
         <v>24</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>John P[e]irc[e]</t>
+          <t>Caleb Fairchild</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>John Peirce</t>
+          <t>Caleb Fairchild</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
@@ -41909,46 +41961,50 @@
       <c r="H691" t="inlineStr"/>
       <c r="I691" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ambiguous(11)</t>
         </is>
       </c>
       <c r="J691" t="n">
         <v>26</v>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr"/>
       <c r="M691" t="inlineStr"/>
       <c r="N691" t="inlineStr">
         <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B692" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C692" t="n">
         <v>25</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>[P]. Lawrence</t>
+          <t>Sam[ue]l Cook</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>P. Lawrence</t>
+          <t>Sam[ue]l Cook</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
@@ -41961,53 +42017,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H692" t="inlineStr">
-        <is>
-          <t>5101412</t>
-        </is>
-      </c>
+      <c r="H692" t="inlineStr"/>
       <c r="I692" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J692" t="n">
         <v>26</v>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr"/>
       <c r="M692" t="inlineStr"/>
       <c r="N692" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B693" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C693" t="n">
         <v>26</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>[J]. [C]. Walker</t>
+          <t>Thomas Ett[e]y</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>J. C. Walker</t>
+          <t>Thomas Ett[e]y</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
@@ -42023,7 +42079,7 @@
       <c r="H693" t="inlineStr"/>
       <c r="I693" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J693" t="n">
@@ -42031,50 +42087,42 @@
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
-        </is>
-      </c>
-      <c r="L693" t="inlineStr">
-        <is>
-          <t>5101413</t>
-        </is>
-      </c>
-      <c r="M693" t="inlineStr">
-        <is>
-          <t>lines 25 and 27 resolve uniquely to serials 5101412 and 5101414; of this line's 10 candidates exactly one, 5101413, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101474;5101657</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr"/>
+      <c r="M693" t="inlineStr"/>
       <c r="N693" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B694" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C694" t="n">
         <v>27</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>[W]m. Williams</t>
+          <t>[?]le[?] Ett[y]sen</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>William Williams</t>
+          <t>[?]le[?] Ett[y]sen</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
@@ -42087,53 +42135,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H694" t="inlineStr">
-        <is>
-          <t>5101414</t>
-        </is>
-      </c>
+      <c r="H694" t="inlineStr"/>
       <c r="I694" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J694" t="n">
         <v>26</v>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>5101658;5101661</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr"/>
       <c r="M694" t="inlineStr"/>
       <c r="N694" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B695" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C695" t="n">
         <v>28</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>W. Nelson</t>
+          <t>Andrew Duffy</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>W. Nelson</t>
+          <t>Andrew Duffy</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
@@ -42146,58 +42194,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H695" t="inlineStr">
-        <is>
-          <t>5101415</t>
-        </is>
-      </c>
+      <c r="H695" t="inlineStr"/>
       <c r="I695" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J695" t="n">
         <v>26</v>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>5101659;5102085</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr"/>
       <c r="M695" t="inlineStr"/>
       <c r="N695" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B696" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C696" t="n">
         <v>29</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Geo. Merrill</t>
+          <t>[J]ohn Ba[r]qu[ee]</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>George Merrill</t>
+          <t>[J]ohn Ba[r]qu[ee]</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -42208,7 +42256,7 @@
       <c r="H696" t="inlineStr"/>
       <c r="I696" t="inlineStr">
         <is>
-          <t>ambiguous(6)</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J696" t="n">
@@ -42216,47 +42264,47 @@
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
+          <t>5101658;5101661</t>
         </is>
       </c>
       <c r="L696" t="inlineStr"/>
       <c r="M696" t="inlineStr"/>
       <c r="N696" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B697" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C697" t="n">
         <v>30</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>J. W. Salisbury</t>
+          <t>Thomas Sh[i]r[d]</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>J. W. Salisbury</t>
+          <t>Thomas Sh[i]r[d]</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
@@ -42267,7 +42315,7 @@
       <c r="H697" t="inlineStr"/>
       <c r="I697" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J697" t="n">
@@ -42275,47 +42323,47 @@
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+          <t>5101490;5101662</t>
         </is>
       </c>
       <c r="L697" t="inlineStr"/>
       <c r="M697" t="inlineStr"/>
       <c r="N697" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-P5</t>
         </is>
       </c>
       <c r="B698" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C698" t="n">
         <v>31</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>John Parkin</t>
+          <t>[J]ohn Ellis</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>John Parkin</t>
+          <t>[J]ohn Ellis</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -42326,7 +42374,7 @@
       <c r="H698" t="inlineStr"/>
       <c r="I698" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(5)</t>
         </is>
       </c>
       <c r="J698" t="n">
@@ -42334,17 +42382,3680 @@
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+          <t>5101589;5101609;5101663;5101794;5102113</t>
         </is>
       </c>
       <c r="L698" t="inlineStr"/>
       <c r="M698" t="inlineStr"/>
       <c r="N698" t="inlineStr">
         <is>
+          <t>the fingerprint over 26 columns matches 5 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>213</v>
+      </c>
+      <c r="C699" t="n">
+        <v>1</v>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Casper [M]uller</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Casper Muller</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J699" t="n">
+        <v>26</v>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr"/>
+      <c r="M699" t="inlineStr"/>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>213</v>
+      </c>
+      <c r="C700" t="n">
+        <v>2</v>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>W[m]. [?] Sh[e]n[e]r</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>William [?] Shener</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>5101449</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J700" t="n">
+        <v>26</v>
+      </c>
+      <c r="K700" t="inlineStr"/>
+      <c r="L700" t="inlineStr"/>
+      <c r="M700" t="inlineStr"/>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>213</v>
+      </c>
+      <c r="C701" t="n">
+        <v>3</v>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>[D]. [B]. [F]ischo[f]</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>D. B. Fischof</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr"/>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>ambiguous(11)</t>
+        </is>
+      </c>
+      <c r="J701" t="n">
+        <v>26</v>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr"/>
+      <c r="M701" t="inlineStr"/>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>213</v>
+      </c>
+      <c r="C702" t="n">
+        <v>4</v>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>E[ph]e[a]n [?] Sha[i]l[s]</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>[?] Shails</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr"/>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J702" t="n">
+        <v>26</v>
+      </c>
+      <c r="K702" t="inlineStr"/>
+      <c r="L702" t="inlineStr"/>
+      <c r="M702" t="inlineStr"/>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>213</v>
+      </c>
+      <c r="C703" t="n">
+        <v>5</v>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Ch[s]. Raymond</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Charles Raymond</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr"/>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>ambiguous(8)</t>
+        </is>
+      </c>
+      <c r="J703" t="n">
+        <v>26</v>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr"/>
+      <c r="M703" t="inlineStr"/>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>213</v>
+      </c>
+      <c r="C704" t="n">
+        <v>6</v>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>[N]. B. Ca[r]t[e]r</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>N. B. Carter</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>ambiguous(8)</t>
+        </is>
+      </c>
+      <c r="J704" t="n">
+        <v>26</v>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr"/>
+      <c r="M704" t="inlineStr"/>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>213</v>
+      </c>
+      <c r="C705" t="n">
+        <v>7</v>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Nath[a]n [E]. King</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Nathan E. King</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr"/>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J705" t="n">
+        <v>26</v>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr"/>
+      <c r="M705" t="inlineStr"/>
+      <c r="N705" t="inlineStr">
+        <is>
           <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
-      <c r="O698" t="inlineStr">
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>213</v>
+      </c>
+      <c r="C706" t="n">
+        <v>8</v>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>[Ch]ad[w]ell &amp; H. Vail</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Chadwell &amp; H. Vail</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J706" t="n">
+        <v>26</v>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr"/>
+      <c r="M706" t="inlineStr"/>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>213</v>
+      </c>
+      <c r="C707" t="n">
+        <v>9</v>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>[S]. M. Wag[e]r</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>S. M. Wager</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J707" t="n">
+        <v>26</v>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr"/>
+      <c r="M707" t="inlineStr"/>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>213</v>
+      </c>
+      <c r="C708" t="n">
+        <v>10</v>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>[?] W[m]. C[l]on[e]</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>[?] William Clone</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr"/>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J708" t="n">
+        <v>26</v>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>5101420;5101457;5101810</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr"/>
+      <c r="M708" t="inlineStr"/>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>213</v>
+      </c>
+      <c r="C709" t="n">
+        <v>11</v>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>[A]. [N]. Dea[r]d[e]n</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>A. N. Dearden</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J709" t="n">
+        <v>26</v>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr"/>
+      <c r="M709" t="inlineStr"/>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>213</v>
+      </c>
+      <c r="C710" t="n">
+        <v>12</v>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>[E]. [K]. [?]</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J710" t="n">
+        <v>26</v>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr"/>
+      <c r="M710" t="inlineStr"/>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>213</v>
+      </c>
+      <c r="C711" t="n">
+        <v>13</v>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>[H]. [H]. Ryan</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>H. H. Ryan</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr"/>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J711" t="n">
+        <v>26</v>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr"/>
+      <c r="M711" t="inlineStr"/>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>213</v>
+      </c>
+      <c r="C712" t="n">
+        <v>14</v>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Chaunc[y] [S]hell</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Chauncy Shell</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr"/>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J712" t="n">
+        <v>26</v>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>5101451;5101461</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr"/>
+      <c r="M712" t="inlineStr"/>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>213</v>
+      </c>
+      <c r="C713" t="n">
+        <v>15</v>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>[Jos]. Pat[h]</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Jos. Path</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr"/>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J713" t="n">
+        <v>26</v>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr"/>
+      <c r="M713" t="inlineStr"/>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>213</v>
+      </c>
+      <c r="C714" t="n">
+        <v>16</v>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>[?]. [B]. Ba[?]</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr"/>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J714" t="n">
+        <v>26</v>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>5101290;5101463;5102140</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr"/>
+      <c r="M714" t="inlineStr"/>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>213</v>
+      </c>
+      <c r="C715" t="n">
+        <v>17</v>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Robert [F]ol[g]an</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Robert Folgan</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr"/>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J715" t="n">
+        <v>26</v>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr"/>
+      <c r="M715" t="inlineStr"/>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>213</v>
+      </c>
+      <c r="C716" t="n">
+        <v>18</v>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>[W]m. Ra[n]kin</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>William Rankin</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>5101435</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J716" t="n">
+        <v>26</v>
+      </c>
+      <c r="K716" t="inlineStr"/>
+      <c r="L716" t="inlineStr"/>
+      <c r="M716" t="inlineStr"/>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>213</v>
+      </c>
+      <c r="C717" t="n">
+        <v>19</v>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>[?] A[b]e[l]e[s]</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>[?] Abeles</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>5101436</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J717" t="n">
+        <v>26</v>
+      </c>
+      <c r="K717" t="inlineStr"/>
+      <c r="L717" t="inlineStr"/>
+      <c r="M717" t="inlineStr"/>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>213</v>
+      </c>
+      <c r="C718" t="n">
+        <v>20</v>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>[W]. [H]o[d]son</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>W. Hodson</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>5101437</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J718" t="n">
+        <v>26</v>
+      </c>
+      <c r="K718" t="inlineStr"/>
+      <c r="L718" t="inlineStr"/>
+      <c r="M718" t="inlineStr"/>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>213</v>
+      </c>
+      <c r="C719" t="n">
+        <v>21</v>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>[H]. [Sp]a[rk]e[r]</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>H. Sparker</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>5101438</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J719" t="n">
+        <v>26</v>
+      </c>
+      <c r="K719" t="inlineStr"/>
+      <c r="L719" t="inlineStr"/>
+      <c r="M719" t="inlineStr"/>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>213</v>
+      </c>
+      <c r="C720" t="n">
+        <v>22</v>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>John H[e]in[i]ck</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>John Heinick</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>5101439</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J720" t="n">
+        <v>26</v>
+      </c>
+      <c r="K720" t="inlineStr"/>
+      <c r="L720" t="inlineStr"/>
+      <c r="M720" t="inlineStr"/>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>213</v>
+      </c>
+      <c r="C721" t="n">
+        <v>23</v>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>[Jos]. Whit[a]k[e]r</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Jos. Whitaker</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J721" t="n">
+        <v>26</v>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>5101440;5101728;5101852;5102005;5102094;5102157</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>5101440</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>lines 22 and 24 resolve uniquely to serials 5101439 and 5101441; of this line's 6 candidates exactly one, 5101440, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>213</v>
+      </c>
+      <c r="C722" t="n">
+        <v>24</v>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>John Rogan</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>John Rogan</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>5101441</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J722" t="n">
+        <v>26</v>
+      </c>
+      <c r="K722" t="inlineStr"/>
+      <c r="L722" t="inlineStr"/>
+      <c r="M722" t="inlineStr"/>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>213</v>
+      </c>
+      <c r="C723" t="n">
+        <v>25</v>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>A. [S]. Benne[t]</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>A. S. Bennet</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J723" t="n">
+        <v>26</v>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>5101442;5102092</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>5101442</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 2 candidates exactly one, 5101442, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>213</v>
+      </c>
+      <c r="C724" t="n">
+        <v>26</v>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Th[os]. P[ag]e</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Thomas Page</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J724" t="n">
+        <v>26</v>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>5101443</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 43 candidates exactly one, 5101443, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>213</v>
+      </c>
+      <c r="C725" t="n">
+        <v>27</v>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>[Ja]s. M[c]Lea[n]</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>James McLean</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>5101444</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J725" t="n">
+        <v>26</v>
+      </c>
+      <c r="K725" t="inlineStr"/>
+      <c r="L725" t="inlineStr"/>
+      <c r="M725" t="inlineStr"/>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>213</v>
+      </c>
+      <c r="C726" t="n">
+        <v>28</v>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>[L]. [A]. [R]a[ll]s[t]one</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>L. A. Rallstone</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr"/>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J726" t="n">
+        <v>26</v>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>5101283;5101392;5101445;5101559;5101696;5101863</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>5101445</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>lines 27 and 30 resolve uniquely to serials 5101444 and 5101448; of this line's 6 candidates exactly one, 5101445, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>213</v>
+      </c>
+      <c r="C727" t="n">
+        <v>29</v>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>M. [H]. Magi[e]</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>M. H. Magie</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr"/>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J727" t="n">
+        <v>26</v>
+      </c>
+      <c r="K727" t="inlineStr"/>
+      <c r="L727" t="inlineStr"/>
+      <c r="M727" t="inlineStr"/>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>213</v>
+      </c>
+      <c r="C728" t="n">
+        <v>30</v>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>[F]. C. Sherman</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>F. C. Sherman</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>5101448</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J728" t="n">
+        <v>26</v>
+      </c>
+      <c r="K728" t="inlineStr"/>
+      <c r="L728" t="inlineStr"/>
+      <c r="M728" t="inlineStr"/>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>212</v>
+      </c>
+      <c r="C729" t="n">
+        <v>1</v>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>[?] Sawyer</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>[?] Sawyer</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>ambiguous(8)</t>
+        </is>
+      </c>
+      <c r="J729" t="n">
+        <v>26</v>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr"/>
+      <c r="M729" t="inlineStr"/>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>212</v>
+      </c>
+      <c r="C730" t="n">
+        <v>2</v>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Joseph Shields</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Joseph Shields</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J730" t="n">
+        <v>26</v>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>5101420;5101457;5101810</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr"/>
+      <c r="M730" t="inlineStr"/>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>212</v>
+      </c>
+      <c r="C731" t="n">
+        <v>3</v>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>And[e]rson [L]. Co[x]</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Anderson L. Cox</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J731" t="n">
+        <v>26</v>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr"/>
+      <c r="M731" t="inlineStr"/>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>212</v>
+      </c>
+      <c r="C732" t="n">
+        <v>4</v>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Robert Ba[d]y</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Robert Bady</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>5101422</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J732" t="n">
+        <v>26</v>
+      </c>
+      <c r="K732" t="inlineStr"/>
+      <c r="L732" t="inlineStr"/>
+      <c r="M732" t="inlineStr"/>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>212</v>
+      </c>
+      <c r="C733" t="n">
+        <v>5</v>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>D. H. [?]anda[c]k</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>D. H. [?]</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr"/>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J733" t="n">
+        <v>26</v>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>5101423</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>lines 4 and 6 resolve uniquely to serials 5101422 and 5101424; of this line's 10 candidates exactly one, 5101423, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>212</v>
+      </c>
+      <c r="C734" t="n">
+        <v>6</v>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Marg[u]erite M[e]rra[r]d</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Marguerite Merrard</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>5101424</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J734" t="n">
+        <v>26</v>
+      </c>
+      <c r="K734" t="inlineStr"/>
+      <c r="L734" t="inlineStr"/>
+      <c r="M734" t="inlineStr"/>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>212</v>
+      </c>
+      <c r="C735" t="n">
+        <v>7</v>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>David Bra[m]elin</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>David Bramelin</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J735" t="n">
+        <v>26</v>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>5101425;5101910</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>5101425</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>lines 6 and 8 resolve uniquely to serials 5101424 and 5101426; of this line's 2 candidates exactly one, 5101425, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>212</v>
+      </c>
+      <c r="C736" t="n">
+        <v>8</v>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Robt. Watts</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Robert Watts</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>5101426</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J736" t="n">
+        <v>26</v>
+      </c>
+      <c r="K736" t="inlineStr"/>
+      <c r="L736" t="inlineStr"/>
+      <c r="M736" t="inlineStr"/>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>212</v>
+      </c>
+      <c r="C737" t="n">
+        <v>9</v>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Wm. Raymond</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>William Raymond</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>ambiguous(18)</t>
+        </is>
+      </c>
+      <c r="J737" t="n">
+        <v>26</v>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>5101427;5101555;5101557;5101653;5101682;5101722;5101827;5101864;5101869;5101890;5101905;5101939;5101973;5102000;5102011;5102052;5102105;5102144</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>5101427</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>lines 8 and 10 resolve uniquely to serials 5101426 and 5101428; of this line's 18 candidates exactly one, 5101427, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 18 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>212</v>
+      </c>
+      <c r="C738" t="n">
+        <v>10</v>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>W[m]. [W]arner</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>William Warner</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>5101428</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J738" t="n">
+        <v>26</v>
+      </c>
+      <c r="K738" t="inlineStr"/>
+      <c r="L738" t="inlineStr"/>
+      <c r="M738" t="inlineStr"/>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>212</v>
+      </c>
+      <c r="C739" t="n">
+        <v>11</v>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Ja[s]. C. [?]</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Jas. C. [?]</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>5101429</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J739" t="n">
+        <v>26</v>
+      </c>
+      <c r="K739" t="inlineStr"/>
+      <c r="L739" t="inlineStr"/>
+      <c r="M739" t="inlineStr"/>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>212</v>
+      </c>
+      <c r="C740" t="n">
+        <v>12</v>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>[?] H. Sherm[an]</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>[?] H. Sherman</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>5101430</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J740" t="n">
+        <v>26</v>
+      </c>
+      <c r="K740" t="inlineStr"/>
+      <c r="L740" t="inlineStr"/>
+      <c r="M740" t="inlineStr"/>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>212</v>
+      </c>
+      <c r="C741" t="n">
+        <v>13</v>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>[?]. [K]. Bul[l]</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>[?] K. Bull</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>ambiguous(12)</t>
+        </is>
+      </c>
+      <c r="J741" t="n">
+        <v>26</v>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr"/>
+      <c r="M741" t="inlineStr"/>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>212</v>
+      </c>
+      <c r="C742" t="n">
+        <v>14</v>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>John Davis</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>John Davis</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J742" t="n">
+        <v>26</v>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr"/>
+      <c r="M742" t="inlineStr"/>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>212</v>
+      </c>
+      <c r="C743" t="n">
+        <v>15</v>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Isaac [?] W[il]mo[t]h</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Isaac [?] Wilmoth</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J743" t="n">
+        <v>26</v>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr"/>
+      <c r="M743" t="inlineStr"/>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>212</v>
+      </c>
+      <c r="C744" t="n">
+        <v>16</v>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Mary Willard</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Mary Willard</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J744" t="n">
+        <v>26</v>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr"/>
+      <c r="M744" t="inlineStr"/>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>212</v>
+      </c>
+      <c r="C745" t="n">
+        <v>17</v>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Martin Stewart</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Martin Stewart</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>5101404</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J745" t="n">
+        <v>26</v>
+      </c>
+      <c r="K745" t="inlineStr"/>
+      <c r="L745" t="inlineStr"/>
+      <c r="M745" t="inlineStr"/>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>212</v>
+      </c>
+      <c r="C746" t="n">
+        <v>18</v>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>F[r]. Ka[l]bfl[ei]sch</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>[?] Kalbfleisch</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>5101405</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J746" t="n">
+        <v>26</v>
+      </c>
+      <c r="K746" t="inlineStr"/>
+      <c r="L746" t="inlineStr"/>
+      <c r="M746" t="inlineStr"/>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>212</v>
+      </c>
+      <c r="C747" t="n">
+        <v>19</v>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Jam[e]s [?] Morrison</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>James Morrison</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J747" t="n">
+        <v>26</v>
+      </c>
+      <c r="K747" t="inlineStr"/>
+      <c r="L747" t="inlineStr"/>
+      <c r="M747" t="inlineStr"/>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>212</v>
+      </c>
+      <c r="C748" t="n">
+        <v>20</v>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>L. Chr[is]t[ia]n[s]</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>L. Christians</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>ambiguous(4)</t>
+        </is>
+      </c>
+      <c r="J748" t="n">
+        <v>26</v>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>5101377;5101407;5101520;5101592</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>5101407</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410; of this line's 4 candidates exactly one, 5101407, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>212</v>
+      </c>
+      <c r="C749" t="n">
+        <v>21</v>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Geo. C. Mo[r]e</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>George C. More</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J749" t="n">
+        <v>26</v>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr"/>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>212</v>
+      </c>
+      <c r="C750" t="n">
+        <v>22</v>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>[J]. Kir[t]la[n]d</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>J. Kirtland</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J750" t="n">
+        <v>26</v>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr"/>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>212</v>
+      </c>
+      <c r="C751" t="n">
+        <v>23</v>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Jas. Edmu[n]ds</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>James Edmunds</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>5101410</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J751" t="n">
+        <v>26</v>
+      </c>
+      <c r="K751" t="inlineStr"/>
+      <c r="L751" t="inlineStr"/>
+      <c r="M751" t="inlineStr"/>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>212</v>
+      </c>
+      <c r="C752" t="n">
+        <v>24</v>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>John P[e]irc[e]</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>John Peirce</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J752" t="n">
+        <v>26</v>
+      </c>
+      <c r="K752" t="inlineStr"/>
+      <c r="L752" t="inlineStr"/>
+      <c r="M752" t="inlineStr"/>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>212</v>
+      </c>
+      <c r="C753" t="n">
+        <v>25</v>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>[P]. Lawrence</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>P. Lawrence</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>5101412</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J753" t="n">
+        <v>26</v>
+      </c>
+      <c r="K753" t="inlineStr"/>
+      <c r="L753" t="inlineStr"/>
+      <c r="M753" t="inlineStr"/>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>212</v>
+      </c>
+      <c r="C754" t="n">
+        <v>26</v>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>[J]. [C]. Walker</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>J. C. Walker</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J754" t="n">
+        <v>26</v>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>5101413</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>lines 25 and 27 resolve uniquely to serials 5101412 and 5101414; of this line's 10 candidates exactly one, 5101413, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>212</v>
+      </c>
+      <c r="C755" t="n">
+        <v>27</v>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>[W]m. Williams</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>William Williams</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>5101414</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J755" t="n">
+        <v>26</v>
+      </c>
+      <c r="K755" t="inlineStr"/>
+      <c r="L755" t="inlineStr"/>
+      <c r="M755" t="inlineStr"/>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>212</v>
+      </c>
+      <c r="C756" t="n">
+        <v>28</v>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>W. Nelson</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>W. Nelson</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>5101415</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J756" t="n">
+        <v>26</v>
+      </c>
+      <c r="K756" t="inlineStr"/>
+      <c r="L756" t="inlineStr"/>
+      <c r="M756" t="inlineStr"/>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>212</v>
+      </c>
+      <c r="C757" t="n">
+        <v>29</v>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Geo. Merrill</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>George Merrill</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J757" t="n">
+        <v>26</v>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr"/>
+      <c r="M757" t="inlineStr"/>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>212</v>
+      </c>
+      <c r="C758" t="n">
+        <v>30</v>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>J. W. Salisbury</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>J. W. Salisbury</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J758" t="n">
+        <v>26</v>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr"/>
+      <c r="M758" t="inlineStr"/>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>212</v>
+      </c>
+      <c r="C759" t="n">
+        <v>31</v>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>John Parkin</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>John Parkin</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J759" t="n">
+        <v>26</v>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr"/>
+      <c r="M759" t="inlineStr"/>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
         <is>
           <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>

--- a/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
+++ b/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O759"/>
+  <dimension ref="A1:O698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38690,28 +38690,28 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B638" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C638" t="n">
         <v>1</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>E. C. Stowell</t>
+          <t>Casper [M]uller</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>E. C. Stowell</t>
+          <t>Casper Muller</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -38719,53 +38719,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H638" t="inlineStr">
-        <is>
-          <t>5101477</t>
-        </is>
-      </c>
+      <c r="H638" t="inlineStr"/>
       <c r="I638" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(10)</t>
         </is>
       </c>
       <c r="J638" t="n">
         <v>26</v>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr"/>
       <c r="M638" t="inlineStr"/>
       <c r="N638" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O638" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B639" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C639" t="n">
         <v>2</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Jno. Hodges</t>
+          <t>W[m]. [?] Sh[e]n[e]r</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Jno. Hodges</t>
+          <t>William [?] Shener</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -38780,7 +38780,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>5101480</t>
+          <t>5101449</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -38801,30 +38801,30 @@
       </c>
       <c r="O639" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B640" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C640" t="n">
         <v>3</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Samuel Cha[p]in</t>
+          <t>[D]. [B]. [F]ischo[f]</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Samuel Cha[p]in</t>
+          <t>D. B. Fischof</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
@@ -38837,53 +38837,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H640" t="inlineStr">
-        <is>
-          <t>5101481</t>
-        </is>
-      </c>
+      <c r="H640" t="inlineStr"/>
       <c r="I640" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(11)</t>
         </is>
       </c>
       <c r="J640" t="n">
         <v>26</v>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr"/>
       <c r="M640" t="inlineStr"/>
       <c r="N640" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B641" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C641" t="n">
         <v>4</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Chs. L. Drag[u]a</t>
+          <t>E[ph]e[a]n [?] Sha[i]l[s]</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Chs. L. Drag[u]a</t>
+          <t>[?] Shails</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
@@ -38896,14 +38896,10 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H641" t="inlineStr">
-        <is>
-          <t>5101482</t>
-        </is>
-      </c>
+      <c r="H641" t="inlineStr"/>
       <c r="I641" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J641" t="n">
@@ -38914,40 +38910,40 @@
       <c r="M641" t="inlineStr"/>
       <c r="N641" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B642" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C642" t="n">
         <v>5</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>[W]il[lia]m Ta[f]f</t>
+          <t>Ch[s]. Raymond</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>[W]il[lia]m Ta[f]f</t>
+          <t>Charles Raymond</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -38958,7 +38954,7 @@
       <c r="H642" t="inlineStr"/>
       <c r="I642" t="inlineStr">
         <is>
-          <t>ambiguous(11)</t>
+          <t>ambiguous(8)</t>
         </is>
       </c>
       <c r="J642" t="n">
@@ -38966,55 +38962,47 @@
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>5101363;5101483;5101491;5101519;5101721;5101748;5101819;5102023;5102132;5102194;5102211</t>
-        </is>
-      </c>
-      <c r="L642" t="inlineStr">
-        <is>
-          <t>5101483</t>
-        </is>
-      </c>
-      <c r="M642" t="inlineStr">
-        <is>
-          <t>lines 4 and 6 resolve uniquely to serials 5101482 and 5101484; of this line's 11 candidates exactly one, 5101483, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr"/>
+      <c r="M642" t="inlineStr"/>
       <c r="N642" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B643" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C643" t="n">
         <v>6</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Chs. B. Benjamin</t>
+          <t>[N]. B. Ca[r]t[e]r</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Chs. B. Benjamin</t>
+          <t>N. B. Carter</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -39022,58 +39010,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H643" t="inlineStr">
-        <is>
-          <t>5101484</t>
-        </is>
-      </c>
+      <c r="H643" t="inlineStr"/>
       <c r="I643" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(8)</t>
         </is>
       </c>
       <c r="J643" t="n">
         <v>26</v>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr"/>
       <c r="M643" t="inlineStr"/>
       <c r="N643" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O643" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B644" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C644" t="n">
         <v>7</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Jno. C. Dunican</t>
+          <t>Nath[a]n [E]. King</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Jno. C. Dunican</t>
+          <t>Nathan E. King</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -39092,19 +39080,11 @@
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
-      <c r="L644" t="inlineStr">
-        <is>
-          <t>5101485</t>
-        </is>
-      </c>
-      <c r="M644" t="inlineStr">
-        <is>
-          <t>lines 6 and 8 resolve uniquely to serials 5101484 and 5101486; of this line's 43 candidates exactly one, 5101485, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr"/>
+      <c r="M644" t="inlineStr"/>
       <c r="N644" t="inlineStr">
         <is>
           <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
@@ -39112,30 +39092,30 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B645" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C645" t="n">
         <v>8</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>[Ch]ad[w]ell &amp; H. Vail</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>Chadwell &amp; H. Vail</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
@@ -39148,53 +39128,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H645" t="inlineStr">
-        <is>
-          <t>5101486</t>
-        </is>
-      </c>
+      <c r="H645" t="inlineStr"/>
       <c r="I645" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(6)</t>
         </is>
       </c>
       <c r="J645" t="n">
         <v>26</v>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr"/>
       <c r="M645" t="inlineStr"/>
       <c r="N645" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B646" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C646" t="n">
         <v>9</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>[?]m. Morrison</t>
+          <t>[S]. M. Wag[e]r</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>[?]m. Morrison</t>
+          <t>S. M. Wager</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
@@ -39207,53 +39187,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H646" t="inlineStr">
-        <is>
-          <t>5101487</t>
-        </is>
-      </c>
+      <c r="H646" t="inlineStr"/>
       <c r="I646" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(10)</t>
         </is>
       </c>
       <c r="J646" t="n">
         <v>26</v>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr"/>
       <c r="M646" t="inlineStr"/>
       <c r="N646" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B647" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C647" t="n">
         <v>10</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>[Sam]l. J. Brown</t>
+          <t>[?] W[m]. C[l]on[e]</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>[Sam]l. J. Brown</t>
+          <t>[?] William Clone</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
@@ -39266,53 +39246,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H647" t="inlineStr">
-        <is>
-          <t>5101488</t>
-        </is>
-      </c>
+      <c r="H647" t="inlineStr"/>
       <c r="I647" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J647" t="n">
         <v>26</v>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>5101420;5101457;5101810</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr"/>
       <c r="M647" t="inlineStr"/>
       <c r="N647" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B648" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C648" t="n">
         <v>11</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>[H]enry Morrison</t>
+          <t>[A]. [N]. Dea[r]d[e]n</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>[H]enry Morrison</t>
+          <t>A. N. Dearden</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
@@ -39325,53 +39305,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H648" t="inlineStr">
-        <is>
-          <t>5101489</t>
-        </is>
-      </c>
+      <c r="H648" t="inlineStr"/>
       <c r="I648" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J648" t="n">
         <v>26</v>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr"/>
       <c r="M648" t="inlineStr"/>
       <c r="N648" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O648" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B649" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C649" t="n">
         <v>12</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Jas. W. Bend[l]ey</t>
+          <t>[E]. [K]. [?]</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Jas. W. Bend[l]ey</t>
+          <t>[?]</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
@@ -39387,7 +39367,7 @@
       <c r="H649" t="inlineStr"/>
       <c r="I649" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J649" t="n">
@@ -39395,50 +39375,42 @@
       </c>
       <c r="K649" t="inlineStr">
         <is>
-          <t>5101490;5101662</t>
-        </is>
-      </c>
-      <c r="L649" t="inlineStr">
-        <is>
-          <t>5101490</t>
-        </is>
-      </c>
-      <c r="M649" t="inlineStr">
-        <is>
-          <t>lines 11 and 15 resolve uniquely to serials 5101489 and 5101493; of this line's 2 candidates exactly one, 5101490, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr"/>
+      <c r="M649" t="inlineStr"/>
       <c r="N649" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O649" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B650" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C650" t="n">
         <v>13</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Ge[o]. M[u]nn</t>
+          <t>[H]. [H]. Ryan</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Ge[o]. M[u]nn</t>
+          <t>H. H. Ryan</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
@@ -39454,7 +39426,7 @@
       <c r="H650" t="inlineStr"/>
       <c r="I650" t="inlineStr">
         <is>
-          <t>ambiguous(11)</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J650" t="n">
@@ -39462,55 +39434,47 @@
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>5101363;5101483;5101491;5101519;5101721;5101748;5101819;5102023;5102132;5102194;5102211</t>
-        </is>
-      </c>
-      <c r="L650" t="inlineStr">
-        <is>
-          <t>5101491</t>
-        </is>
-      </c>
-      <c r="M650" t="inlineStr">
-        <is>
-          <t>lines 11 and 15 resolve uniquely to serials 5101489 and 5101493; of this line's 11 candidates exactly one, 5101491, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr"/>
+      <c r="M650" t="inlineStr"/>
       <c r="N650" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B651" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C651" t="n">
         <v>14</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Jno. B. Mitchell</t>
+          <t>Chaunc[y] [S]hell</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Jno. B. Mitchell</t>
+          <t>Chauncy Shell</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -39529,19 +39493,11 @@
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>5101358;5101492</t>
-        </is>
-      </c>
-      <c r="L651" t="inlineStr">
-        <is>
-          <t>5101492</t>
-        </is>
-      </c>
-      <c r="M651" t="inlineStr">
-        <is>
-          <t>lines 11 and 15 resolve uniquely to serials 5101489 and 5101493; of this line's 2 candidates exactly one, 5101492, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101451;5101461</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr"/>
+      <c r="M651" t="inlineStr"/>
       <c r="N651" t="inlineStr">
         <is>
           <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
@@ -39549,35 +39505,35 @@
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B652" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C652" t="n">
         <v>15</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>[Th]os. Ladd</t>
+          <t>[Jos]. Pat[h]</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>[Th]os. Ladd</t>
+          <t>Jos. Path</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -39585,53 +39541,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H652" t="inlineStr">
-        <is>
-          <t>5101493</t>
-        </is>
-      </c>
+      <c r="H652" t="inlineStr"/>
       <c r="I652" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(10)</t>
         </is>
       </c>
       <c r="J652" t="n">
         <v>26</v>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr"/>
       <c r="N652" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B653" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C653" t="n">
         <v>16</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>Ja[s]. [K]ean</t>
+          <t>[?]. [B]. Ba[?]</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Ja[s]. [K]ean</t>
+          <t>[?]</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
@@ -39647,7 +39603,7 @@
       <c r="H653" t="inlineStr"/>
       <c r="I653" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J653" t="n">
@@ -39655,42 +39611,42 @@
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+          <t>5101290;5101463;5102140</t>
         </is>
       </c>
       <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr"/>
       <c r="N653" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B654" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C654" t="n">
         <v>17</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>W. H. Bra[i]nbridge</t>
+          <t>Robert [F]ol[g]an</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>W. H. Bra[i]nbridge</t>
+          <t>Robert Folgan</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
@@ -39706,7 +39662,7 @@
       <c r="H654" t="inlineStr"/>
       <c r="I654" t="inlineStr">
         <is>
-          <t>ambiguous(27)</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J654" t="n">
@@ -39714,47 +39670,47 @@
       </c>
       <c r="K654" t="inlineStr">
         <is>
-          <t>5101279;5101385;5101465;5101540;5101684;5101685;5101689;5101708;5101710;5101723;5101726;5101744;5101764;5101779;5101780;5101784;5101792;5101842;5101898;5101935;5101980;5101986;5101994;5102009;5102055;5102077;5102090</t>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
         </is>
       </c>
       <c r="L654" t="inlineStr"/>
       <c r="M654" t="inlineStr"/>
       <c r="N654" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 27 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O654" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B655" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C655" t="n">
         <v>18</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>[J]no. Mars[h] W. Cad[y]</t>
+          <t>[W]m. Ra[n]kin</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>[J]no. Mars[h] W. Cad[y]</t>
+          <t>William Rankin</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -39764,7 +39720,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>5101466</t>
+          <t>5101435</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -39785,30 +39741,30 @@
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B656" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C656" t="n">
         <v>19</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>[I]saac Stua[r]t</t>
+          <t>[?] A[b]e[l]e[s]</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>[I]saac Stua[r]t</t>
+          <t>[?] Abeles</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
@@ -39823,7 +39779,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>5101467</t>
+          <t>5101436</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -39844,30 +39800,30 @@
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B657" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C657" t="n">
         <v>20</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>[J]os[eph] L. M[u]ll[i]n</t>
+          <t>[W]. [H]o[d]son</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>[J]os[eph] L. M[u]ll[i]n</t>
+          <t>W. Hodson</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -39882,7 +39838,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>5101468</t>
+          <t>5101437</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -39903,35 +39859,35 @@
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B658" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C658" t="n">
         <v>21</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>R. W. Patterson</t>
+          <t>[H]. [Sp]a[rk]e[r]</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>R. W. Patterson</t>
+          <t>H. Sparker</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
@@ -39939,66 +39895,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H658" t="inlineStr"/>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>5101438</t>
+        </is>
+      </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J658" t="n">
         <v>26</v>
       </c>
-      <c r="K658" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L658" t="inlineStr">
-        <is>
-          <t>5101469</t>
-        </is>
-      </c>
-      <c r="M658" t="inlineStr">
-        <is>
-          <t>lines 20 and 22 resolve uniquely to serials 5101468 and 5101470; of this line's 43 candidates exactly one, 5101469, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K658" t="inlineStr"/>
+      <c r="L658" t="inlineStr"/>
+      <c r="M658" t="inlineStr"/>
       <c r="N658" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B659" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C659" t="n">
         <v>22</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>[J]. [H]. Collins</t>
+          <t>John H[e]in[i]ck</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>[J]. [H]. Collins</t>
+          <t>John Heinick</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
@@ -40008,7 +39956,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>5101470</t>
+          <t>5101439</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40029,30 +39977,30 @@
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B660" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C660" t="n">
         <v>23</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Ethan Bu[t]ler</t>
+          <t>[Jos]. Whit[a]k[e]r</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Ethan Bu[t]ler</t>
+          <t>Jos. Whitaker</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
@@ -40068,7 +40016,7 @@
       <c r="H660" t="inlineStr"/>
       <c r="I660" t="inlineStr">
         <is>
-          <t>ambiguous(4)</t>
+          <t>ambiguous(6)</t>
         </is>
       </c>
       <c r="J660" t="n">
@@ -40076,55 +40024,55 @@
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>5101292;5101471;5102025;5102134</t>
+          <t>5101440;5101728;5101852;5102005;5102094;5102157</t>
         </is>
       </c>
       <c r="L660" t="inlineStr">
         <is>
-          <t>5101471</t>
+          <t>5101440</t>
         </is>
       </c>
       <c r="M660" t="inlineStr">
         <is>
-          <t>lines 22 and 24 resolve uniquely to serials 5101470 and 5101472; of this line's 4 candidates exactly one, 5101471, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 22 and 24 resolve uniquely to serials 5101439 and 5101441; of this line's 6 candidates exactly one, 5101440, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N660" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O660" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B661" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C661" t="n">
         <v>24</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>E[?]ra Wood[?]ur[y]</t>
+          <t>John Rogan</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>E[?]ra Wood[?]ur[y]</t>
+          <t>John Rogan</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -40134,7 +40082,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>5101472</t>
+          <t>5101441</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40155,35 +40103,35 @@
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B662" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C662" t="n">
         <v>25</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>[J]no. Sammon[s]</t>
+          <t>A. [S]. Benne[t]</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>[J]no. Sammon[s]</t>
+          <t>A. S. Bennet</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -40191,58 +40139,66 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H662" t="inlineStr">
-        <is>
-          <t>5101473</t>
-        </is>
-      </c>
+      <c r="H662" t="inlineStr"/>
       <c r="I662" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J662" t="n">
         <v>26</v>
       </c>
-      <c r="K662" t="inlineStr"/>
-      <c r="L662" t="inlineStr"/>
-      <c r="M662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>5101442;5102092</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>5101442</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 2 candidates exactly one, 5101442, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N662" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B663" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C663" t="n">
         <v>26</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>H. S. Cushing</t>
+          <t>Th[os]. P[ag]e</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>H. S. Cushing</t>
+          <t>Thomas Page</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -40253,7 +40209,7 @@
       <c r="H663" t="inlineStr"/>
       <c r="I663" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J663" t="n">
@@ -40261,55 +40217,55 @@
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>5101474;5101657</t>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
         </is>
       </c>
       <c r="L663" t="inlineStr">
         <is>
-          <t>5101474</t>
+          <t>5101443</t>
         </is>
       </c>
       <c r="M663" t="inlineStr">
         <is>
-          <t>lines 25 and 27 resolve uniquely to serials 5101473 and 5101475; of this line's 2 candidates exactly one, 5101474, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 43 candidates exactly one, 5101443, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N663" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O663" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B664" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C664" t="n">
         <v>27</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>[W]m. Smith</t>
+          <t>[Ja]s. M[c]Lea[n]</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>[W]m. Smith</t>
+          <t>James McLean</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -40319,7 +40275,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>5101475</t>
+          <t>5101444</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40340,35 +40296,35 @@
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B665" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C665" t="n">
         <v>28</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>W. S. Lockrid[g]e</t>
+          <t>[L]. [A]. [R]a[ll]s[t]one</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>W. S. Lockrid[g]e</t>
+          <t>L. A. Rallstone</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -40379,7 +40335,7 @@
       <c r="H665" t="inlineStr"/>
       <c r="I665" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(6)</t>
         </is>
       </c>
       <c r="J665" t="n">
@@ -40387,47 +40343,55 @@
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
-      <c r="L665" t="inlineStr"/>
-      <c r="M665" t="inlineStr"/>
+          <t>5101283;5101392;5101445;5101559;5101696;5101863</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>5101445</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>lines 27 and 30 resolve uniquely to serials 5101444 and 5101448; of this line's 6 candidates exactly one, 5101445, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N665" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O665" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C666" t="n">
         <v>29</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>[M]. Worthingt[o]n</t>
+          <t>M. [H]. Magi[e]</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>[M]. Worthingt[o]n</t>
+          <t>M. H. Magie</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -40438,55 +40402,51 @@
       <c r="H666" t="inlineStr"/>
       <c r="I666" t="inlineStr">
         <is>
-          <t>ambiguous(4)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J666" t="n">
         <v>26</v>
       </c>
-      <c r="K666" t="inlineStr">
-        <is>
-          <t>5101478;5101871;5101878;5102108</t>
-        </is>
-      </c>
+      <c r="K666" t="inlineStr"/>
       <c r="L666" t="inlineStr"/>
       <c r="M666" t="inlineStr"/>
       <c r="N666" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O666" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-BP</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B667" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C667" t="n">
         <v>30</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>[P]. [R]. F[ie]ld</t>
+          <t>[F]. C. Sherman</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>[P]. [R]. F[ie]ld</t>
+          <t>F. C. Sherman</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -40494,58 +40454,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H667" t="inlineStr"/>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>5101448</t>
+        </is>
+      </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J667" t="n">
         <v>26</v>
       </c>
-      <c r="K667" t="inlineStr">
-        <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
+      <c r="K667" t="inlineStr"/>
       <c r="L667" t="inlineStr"/>
       <c r="M667" t="inlineStr"/>
       <c r="N667" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-BP.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B668" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C668" t="n">
         <v>1</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Jno. Beach</t>
+          <t>[?] Sawyer</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Jno. Beach</t>
+          <t>[?] Sawyer</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -40553,53 +40513,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H668" t="inlineStr">
-        <is>
-          <t>5101660</t>
-        </is>
-      </c>
+      <c r="H668" t="inlineStr"/>
       <c r="I668" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(8)</t>
         </is>
       </c>
       <c r="J668" t="n">
         <v>26</v>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr"/>
       <c r="M668" t="inlineStr"/>
       <c r="N668" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B669" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C669" t="n">
         <v>2</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Phill[i]p Dean</t>
+          <t>Joseph Shields</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>Phill[i]p Dean</t>
+          <t>Joseph Shields</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
@@ -40615,7 +40575,7 @@
       <c r="H669" t="inlineStr"/>
       <c r="I669" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J669" t="n">
@@ -40623,55 +40583,47 @@
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
-        </is>
-      </c>
-      <c r="L669" t="inlineStr">
-        <is>
-          <t>5101664</t>
-        </is>
-      </c>
-      <c r="M669" t="inlineStr">
-        <is>
-          <t>lines 1 and 3 resolve uniquely to serials 5101660 and 5101665; of this line's 10 candidates exactly one, 5101664, lies in that run, and an unbroken run would put this line at 5101661</t>
-        </is>
-      </c>
+          <t>5101420;5101457;5101810</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="inlineStr"/>
       <c r="N669" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B670" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C670" t="n">
         <v>3</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>[J]. S. Roby</t>
+          <t>And[e]rson [L]. Co[x]</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>[J]. S. Roby</t>
+          <t>Anderson L. Cox</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -40679,58 +40631,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H670" t="inlineStr">
-        <is>
-          <t>5101665</t>
-        </is>
-      </c>
+      <c r="H670" t="inlineStr"/>
       <c r="I670" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J670" t="n">
         <v>26</v>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr"/>
       <c r="M670" t="inlineStr"/>
       <c r="N670" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B671" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C671" t="n">
         <v>4</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Salman Hyde</t>
+          <t>Robert Ba[d]y</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Salman Hyde</t>
+          <t>Robert Bady</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -40740,7 +40692,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>5101666</t>
+          <t>5101422</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -40761,35 +40713,35 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B672" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C672" t="n">
         <v>5</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Mrs. Mary Brown</t>
+          <t>D. H. [?]anda[c]k</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>Mrs. Mary Brown</t>
+          <t>D. H. [?]</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -40797,53 +40749,61 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H672" t="inlineStr">
-        <is>
-          <t>5101667</t>
-        </is>
-      </c>
+      <c r="H672" t="inlineStr"/>
       <c r="I672" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(10)</t>
         </is>
       </c>
       <c r="J672" t="n">
         <v>26</v>
       </c>
-      <c r="K672" t="inlineStr"/>
-      <c r="L672" t="inlineStr"/>
-      <c r="M672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>5101423</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>lines 4 and 6 resolve uniquely to serials 5101422 and 5101424; of this line's 10 candidates exactly one, 5101423, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N672" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B673" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C673" t="n">
         <v>6</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Julius Ma[l]Kay</t>
+          <t>Marg[u]erite M[e]rra[r]d</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Julius Ma[l]Kay</t>
+          <t>Marguerite Merrard</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
@@ -40856,66 +40816,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H673" t="inlineStr"/>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>5101424</t>
+        </is>
+      </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J673" t="n">
         <v>26</v>
       </c>
-      <c r="K673" t="inlineStr">
-        <is>
-          <t>5101668;5101790</t>
-        </is>
-      </c>
-      <c r="L673" t="inlineStr">
-        <is>
-          <t>5101668</t>
-        </is>
-      </c>
-      <c r="M673" t="inlineStr">
-        <is>
-          <t>lines 5 and 9 resolve uniquely to serials 5101667 and 5101671; of this line's 2 candidates exactly one, 5101668, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K673" t="inlineStr"/>
+      <c r="L673" t="inlineStr"/>
+      <c r="M673" t="inlineStr"/>
       <c r="N673" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B674" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C674" t="n">
         <v>7</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Levi Reynalds</t>
+          <t>David Bra[m]elin</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Levi Reynalds</t>
+          <t>David Bramelin</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -40926,7 +40878,7 @@
       <c r="H674" t="inlineStr"/>
       <c r="I674" t="inlineStr">
         <is>
-          <t>ambiguous(5)</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J674" t="n">
@@ -40934,50 +40886,50 @@
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>5101669;5101807;5101808;5101873;5102056</t>
+          <t>5101425;5101910</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
         <is>
-          <t>5101669</t>
+          <t>5101425</t>
         </is>
       </c>
       <c r="M674" t="inlineStr">
         <is>
-          <t>lines 5 and 9 resolve uniquely to serials 5101667 and 5101671; of this line's 5 candidates exactly one, 5101669, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 6 and 8 resolve uniquely to serials 5101424 and 5101426; of this line's 2 candidates exactly one, 5101425, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N674" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 5 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B675" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C675" t="n">
         <v>8</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>William Bell</t>
+          <t>Robt. Watts</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>William Bell</t>
+          <t>Robert Watts</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
@@ -40990,61 +40942,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H675" t="inlineStr"/>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>5101426</t>
+        </is>
+      </c>
       <c r="I675" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J675" t="n">
         <v>26</v>
       </c>
-      <c r="K675" t="inlineStr">
-        <is>
-          <t>5101670;5101965</t>
-        </is>
-      </c>
-      <c r="L675" t="inlineStr">
-        <is>
-          <t>5101670</t>
-        </is>
-      </c>
-      <c r="M675" t="inlineStr">
-        <is>
-          <t>lines 5 and 9 resolve uniquely to serials 5101667 and 5101671; of this line's 2 candidates exactly one, 5101670, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K675" t="inlineStr"/>
+      <c r="L675" t="inlineStr"/>
+      <c r="M675" t="inlineStr"/>
       <c r="N675" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C676" t="n">
         <v>9</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Benj[n]. Jacobs</t>
+          <t>Wm. Raymond</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Benj[n]. Jacobs</t>
+          <t>William Raymond</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
@@ -41057,53 +41001,61 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H676" t="inlineStr">
-        <is>
-          <t>5101671</t>
-        </is>
-      </c>
+      <c r="H676" t="inlineStr"/>
       <c r="I676" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(18)</t>
         </is>
       </c>
       <c r="J676" t="n">
         <v>26</v>
       </c>
-      <c r="K676" t="inlineStr"/>
-      <c r="L676" t="inlineStr"/>
-      <c r="M676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>5101427;5101555;5101557;5101653;5101682;5101722;5101827;5101864;5101869;5101890;5101905;5101939;5101973;5102000;5102011;5102052;5102105;5102144</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>5101427</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>lines 8 and 10 resolve uniquely to serials 5101426 and 5101428; of this line's 18 candidates exactly one, 5101427, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N676" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 18 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O676" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B677" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C677" t="n">
         <v>10</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Sam[l]. J. W. Gilbert</t>
+          <t>W[m]. [W]arner</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Sam[l]. J. W. Gilbert</t>
+          <t>William Warner</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
@@ -41118,7 +41070,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>5101672</t>
+          <t>5101428</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41139,30 +41091,30 @@
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B678" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C678" t="n">
         <v>11</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>H. R. W[i]ll[i]s</t>
+          <t>Ja[s]. C. [?]</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>H. R. W[i]ll[i]s</t>
+          <t>Jas. C. [?]</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
@@ -41177,7 +41129,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>5101673</t>
+          <t>5101429</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41198,35 +41150,35 @@
       </c>
       <c r="O678" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B679" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C679" t="n">
         <v>12</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Alex[r]. Loyd</t>
+          <t>[?] H. Sherm[an]</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>Alex[r]. Loyd</t>
+          <t>[?] H. Sherman</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -41236,7 +41188,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>5101674</t>
+          <t>5101430</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41257,35 +41209,35 @@
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B680" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C680" t="n">
         <v>13</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>James Scott</t>
+          <t>[?]. [K]. Bul[l]</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>James Scott</t>
+          <t>[?] K. Bull</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -41293,58 +41245,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H680" t="inlineStr">
-        <is>
-          <t>5101675</t>
-        </is>
-      </c>
+      <c r="H680" t="inlineStr"/>
       <c r="I680" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(12)</t>
         </is>
       </c>
       <c r="J680" t="n">
         <v>26</v>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr"/>
       <c r="M680" t="inlineStr"/>
       <c r="N680" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O680" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B681" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C681" t="n">
         <v>14</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>[?]o. [D]esthalai[s]</t>
+          <t>John Davis</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>[?]o. [D]esthalai[s]</t>
+          <t>John Davis</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
@@ -41363,19 +41315,11 @@
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L681" t="inlineStr">
-        <is>
-          <t>5101676</t>
-        </is>
-      </c>
-      <c r="M681" t="inlineStr">
-        <is>
-          <t>lines 13 and 15 resolve uniquely to serials 5101675 and 5101677; of this line's 43 candidates exactly one, 5101676, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr"/>
+      <c r="M681" t="inlineStr"/>
       <c r="N681" t="inlineStr">
         <is>
           <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
@@ -41383,30 +41327,30 @@
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B682" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C682" t="n">
         <v>15</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>B[a]rnihart [B]la[u]ey</t>
+          <t>Isaac [?] W[il]mo[t]h</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>B[a]rnihart [B]la[u]ey</t>
+          <t>Isaac [?] Wilmoth</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
@@ -41419,58 +41363,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H682" t="inlineStr">
-        <is>
-          <t>5101677</t>
-        </is>
-      </c>
+      <c r="H682" t="inlineStr"/>
       <c r="I682" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J682" t="n">
         <v>26</v>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr"/>
       <c r="M682" t="inlineStr"/>
       <c r="N682" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B683" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C683" t="n">
         <v>16</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Adolp[h] Micha[e]l</t>
+          <t>Mary Willard</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Adolp[h] Micha[e]l</t>
+          <t>Mary Willard</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -41489,7 +41433,7 @@
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
         </is>
       </c>
       <c r="L683" t="inlineStr"/>
@@ -41501,30 +41445,30 @@
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B684" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C684" t="n">
         <v>17</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Peter Case</t>
+          <t>Martin Stewart</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Peter Case</t>
+          <t>Martin Stewart</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
@@ -41539,7 +41483,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>5101648</t>
+          <t>5101404</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -41560,35 +41504,35 @@
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B685" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C685" t="n">
         <v>18</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Fred Goodman</t>
+          <t>F[r]. Ka[l]bfl[ei]sch</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Fred Goodman</t>
+          <t>[?] Kalbfleisch</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -41598,7 +41542,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>5101649</t>
+          <t>5101405</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -41619,35 +41563,35 @@
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B686" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C686" t="n">
         <v>19</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>[J]ohn Case</t>
+          <t>Jam[e]s [?] Morrison</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>[J]ohn Case</t>
+          <t>James Morrison</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -41658,58 +41602,46 @@
       <c r="H686" t="inlineStr"/>
       <c r="I686" t="inlineStr">
         <is>
-          <t>ambiguous(11)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J686" t="n">
         <v>26</v>
       </c>
-      <c r="K686" t="inlineStr">
-        <is>
-          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
-        </is>
-      </c>
-      <c r="L686" t="inlineStr">
-        <is>
-          <t>5101650</t>
-        </is>
-      </c>
-      <c r="M686" t="inlineStr">
-        <is>
-          <t>lines 18 and 20 resolve uniquely to serials 5101649 and 5101651; of this line's 11 candidates exactly one, 5101650, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K686" t="inlineStr"/>
+      <c r="L686" t="inlineStr"/>
+      <c r="M686" t="inlineStr"/>
       <c r="N686" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B687" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C687" t="n">
         <v>20</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>[G]. Shee</t>
+          <t>L. Chr[is]t[ia]n[s]</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>[G]. Shee</t>
+          <t>L. Christians</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
@@ -41722,58 +41654,66 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H687" t="inlineStr">
-        <is>
-          <t>5101651</t>
-        </is>
-      </c>
+      <c r="H687" t="inlineStr"/>
       <c r="I687" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(4)</t>
         </is>
       </c>
       <c r="J687" t="n">
         <v>26</v>
       </c>
-      <c r="K687" t="inlineStr"/>
-      <c r="L687" t="inlineStr"/>
-      <c r="M687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>5101377;5101407;5101520;5101592</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>5101407</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410; of this line's 4 candidates exactly one, 5101407, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B688" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C688" t="n">
         <v>21</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>William Higgins</t>
+          <t>Geo. C. Mo[r]e</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>William Higgins</t>
+          <t>George C. More</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -41784,7 +41724,7 @@
       <c r="H688" t="inlineStr"/>
       <c r="I688" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J688" t="n">
@@ -41792,42 +41732,46 @@
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>5101652;5101738</t>
+          <t>5101408;5101409;5101459</t>
         </is>
       </c>
       <c r="L688" t="inlineStr"/>
-      <c r="M688" t="inlineStr"/>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
       <c r="N688" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O688" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B689" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C689" t="n">
         <v>22</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Sherman Ho[e]r</t>
+          <t>[J]. Kir[t]la[n]d</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Sherman Ho[e]r</t>
+          <t>J. Kirtland</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
@@ -41843,7 +41787,7 @@
       <c r="H689" t="inlineStr"/>
       <c r="I689" t="inlineStr">
         <is>
-          <t>ambiguous(18)</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J689" t="n">
@@ -41851,42 +41795,46 @@
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>5101427;5101555;5101557;5101653;5101682;5101722;5101827;5101864;5101869;5101890;5101905;5101939;5101973;5102000;5102011;5102052;5102105;5102144</t>
+          <t>5101408;5101409;5101459</t>
         </is>
       </c>
       <c r="L689" t="inlineStr"/>
-      <c r="M689" t="inlineStr"/>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
       <c r="N689" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 18 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B690" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C690" t="n">
         <v>23</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Cale[b] Lyman</t>
+          <t>Jas. Edmu[n]ds</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Cale[b] Lyman</t>
+          <t>James Edmunds</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
@@ -41899,53 +41847,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H690" t="inlineStr"/>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>5101410</t>
+        </is>
+      </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>ambiguous(11)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J690" t="n">
         <v>26</v>
       </c>
-      <c r="K690" t="inlineStr">
-        <is>
-          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
-        </is>
-      </c>
+      <c r="K690" t="inlineStr"/>
       <c r="L690" t="inlineStr"/>
       <c r="M690" t="inlineStr"/>
       <c r="N690" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B691" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C691" t="n">
         <v>24</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Caleb Fairchild</t>
+          <t>John P[e]irc[e]</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>Caleb Fairchild</t>
+          <t>John Peirce</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
@@ -41961,50 +41909,46 @@
       <c r="H691" t="inlineStr"/>
       <c r="I691" t="inlineStr">
         <is>
-          <t>ambiguous(11)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J691" t="n">
         <v>26</v>
       </c>
-      <c r="K691" t="inlineStr">
-        <is>
-          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
-        </is>
-      </c>
+      <c r="K691" t="inlineStr"/>
       <c r="L691" t="inlineStr"/>
       <c r="M691" t="inlineStr"/>
       <c r="N691" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B692" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C692" t="n">
         <v>25</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Sam[ue]l Cook</t>
+          <t>[P]. Lawrence</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>Sam[ue]l Cook</t>
+          <t>P. Lawrence</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
@@ -42017,53 +41961,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H692" t="inlineStr"/>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>5101412</t>
+        </is>
+      </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J692" t="n">
         <v>26</v>
       </c>
-      <c r="K692" t="inlineStr">
-        <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
+      <c r="K692" t="inlineStr"/>
       <c r="L692" t="inlineStr"/>
       <c r="M692" t="inlineStr"/>
       <c r="N692" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B693" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C693" t="n">
         <v>26</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Thomas Ett[e]y</t>
+          <t>[J]. [C]. Walker</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Thomas Ett[e]y</t>
+          <t>J. C. Walker</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
@@ -42079,7 +42023,7 @@
       <c r="H693" t="inlineStr"/>
       <c r="I693" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>ambiguous(10)</t>
         </is>
       </c>
       <c r="J693" t="n">
@@ -42087,42 +42031,50 @@
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>5101474;5101657</t>
-        </is>
-      </c>
-      <c r="L693" t="inlineStr"/>
-      <c r="M693" t="inlineStr"/>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>5101413</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>lines 25 and 27 resolve uniquely to serials 5101412 and 5101414; of this line's 10 candidates exactly one, 5101413, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N693" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B694" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C694" t="n">
         <v>27</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>[?]le[?] Ett[y]sen</t>
+          <t>[W]m. Williams</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>[?]le[?] Ett[y]sen</t>
+          <t>William Williams</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
@@ -42135,53 +42087,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H694" t="inlineStr"/>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>5101414</t>
+        </is>
+      </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J694" t="n">
         <v>26</v>
       </c>
-      <c r="K694" t="inlineStr">
-        <is>
-          <t>5101658;5101661</t>
-        </is>
-      </c>
+      <c r="K694" t="inlineStr"/>
       <c r="L694" t="inlineStr"/>
       <c r="M694" t="inlineStr"/>
       <c r="N694" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B695" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C695" t="n">
         <v>28</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Andrew Duffy</t>
+          <t>W. Nelson</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Andrew Duffy</t>
+          <t>W. Nelson</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
@@ -42194,58 +42146,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H695" t="inlineStr"/>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>5101415</t>
+        </is>
+      </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J695" t="n">
         <v>26</v>
       </c>
-      <c r="K695" t="inlineStr">
-        <is>
-          <t>5101659;5102085</t>
-        </is>
-      </c>
+      <c r="K695" t="inlineStr"/>
       <c r="L695" t="inlineStr"/>
       <c r="M695" t="inlineStr"/>
       <c r="N695" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B696" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C696" t="n">
         <v>29</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>[J]ohn Ba[r]qu[ee]</t>
+          <t>Geo. Merrill</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>[J]ohn Ba[r]qu[ee]</t>
+          <t>George Merrill</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -42256,7 +42208,7 @@
       <c r="H696" t="inlineStr"/>
       <c r="I696" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>ambiguous(6)</t>
         </is>
       </c>
       <c r="J696" t="n">
@@ -42264,47 +42216,47 @@
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>5101658;5101661</t>
+          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
         </is>
       </c>
       <c r="L696" t="inlineStr"/>
       <c r="M696" t="inlineStr"/>
       <c r="N696" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B697" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C697" t="n">
         <v>30</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Thomas Sh[i]r[d]</t>
+          <t>J. W. Salisbury</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>Thomas Sh[i]r[d]</t>
+          <t>J. W. Salisbury</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
@@ -42315,7 +42267,7 @@
       <c r="H697" t="inlineStr"/>
       <c r="I697" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>ambiguous(10)</t>
         </is>
       </c>
       <c r="J697" t="n">
@@ -42323,47 +42275,47 @@
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>5101490;5101662</t>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
         </is>
       </c>
       <c r="L697" t="inlineStr"/>
       <c r="M697" t="inlineStr"/>
       <c r="N697" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-P5</t>
+          <t>33SQ-GYYJ-RY</t>
         </is>
       </c>
       <c r="B698" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C698" t="n">
         <v>31</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>[J]ohn Ellis</t>
+          <t>John Parkin</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>[J]ohn Ellis</t>
+          <t>John Parkin</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -42374,7 +42326,7 @@
       <c r="H698" t="inlineStr"/>
       <c r="I698" t="inlineStr">
         <is>
-          <t>ambiguous(5)</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J698" t="n">
@@ -42382,3680 +42334,17 @@
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>5101589;5101609;5101663;5101794;5102113</t>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
         </is>
       </c>
       <c r="L698" t="inlineStr"/>
       <c r="M698" t="inlineStr"/>
       <c r="N698" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 5 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O698" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-P5.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B699" t="n">
-        <v>213</v>
-      </c>
-      <c r="C699" t="n">
-        <v>1</v>
-      </c>
-      <c r="D699" t="inlineStr">
-        <is>
-          <t>Casper [M]uller</t>
-        </is>
-      </c>
-      <c r="E699" t="inlineStr">
-        <is>
-          <t>Casper Muller</t>
-        </is>
-      </c>
-      <c r="F699" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G699" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H699" t="inlineStr"/>
-      <c r="I699" t="inlineStr">
-        <is>
-          <t>ambiguous(10)</t>
-        </is>
-      </c>
-      <c r="J699" t="n">
-        <v>26</v>
-      </c>
-      <c r="K699" t="inlineStr">
-        <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
-        </is>
-      </c>
-      <c r="L699" t="inlineStr"/>
-      <c r="M699" t="inlineStr"/>
-      <c r="N699" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O699" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B700" t="n">
-        <v>213</v>
-      </c>
-      <c r="C700" t="n">
-        <v>2</v>
-      </c>
-      <c r="D700" t="inlineStr">
-        <is>
-          <t>W[m]. [?] Sh[e]n[e]r</t>
-        </is>
-      </c>
-      <c r="E700" t="inlineStr">
-        <is>
-          <t>William [?] Shener</t>
-        </is>
-      </c>
-      <c r="F700" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G700" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H700" t="inlineStr">
-        <is>
-          <t>5101449</t>
-        </is>
-      </c>
-      <c r="I700" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J700" t="n">
-        <v>26</v>
-      </c>
-      <c r="K700" t="inlineStr"/>
-      <c r="L700" t="inlineStr"/>
-      <c r="M700" t="inlineStr"/>
-      <c r="N700" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O700" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B701" t="n">
-        <v>213</v>
-      </c>
-      <c r="C701" t="n">
-        <v>3</v>
-      </c>
-      <c r="D701" t="inlineStr">
-        <is>
-          <t>[D]. [B]. [F]ischo[f]</t>
-        </is>
-      </c>
-      <c r="E701" t="inlineStr">
-        <is>
-          <t>D. B. Fischof</t>
-        </is>
-      </c>
-      <c r="F701" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G701" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H701" t="inlineStr"/>
-      <c r="I701" t="inlineStr">
-        <is>
-          <t>ambiguous(11)</t>
-        </is>
-      </c>
-      <c r="J701" t="n">
-        <v>26</v>
-      </c>
-      <c r="K701" t="inlineStr">
-        <is>
-          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
-        </is>
-      </c>
-      <c r="L701" t="inlineStr"/>
-      <c r="M701" t="inlineStr"/>
-      <c r="N701" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O701" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B702" t="n">
-        <v>213</v>
-      </c>
-      <c r="C702" t="n">
-        <v>4</v>
-      </c>
-      <c r="D702" t="inlineStr">
-        <is>
-          <t>E[ph]e[a]n [?] Sha[i]l[s]</t>
-        </is>
-      </c>
-      <c r="E702" t="inlineStr">
-        <is>
-          <t>[?] Shails</t>
-        </is>
-      </c>
-      <c r="F702" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G702" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H702" t="inlineStr"/>
-      <c r="I702" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="J702" t="n">
-        <v>26</v>
-      </c>
-      <c r="K702" t="inlineStr"/>
-      <c r="L702" t="inlineStr"/>
-      <c r="M702" t="inlineStr"/>
-      <c r="N702" t="inlineStr">
-        <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
-        </is>
-      </c>
-      <c r="O702" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B703" t="n">
-        <v>213</v>
-      </c>
-      <c r="C703" t="n">
-        <v>5</v>
-      </c>
-      <c r="D703" t="inlineStr">
-        <is>
-          <t>Ch[s]. Raymond</t>
-        </is>
-      </c>
-      <c r="E703" t="inlineStr">
-        <is>
-          <t>Charles Raymond</t>
-        </is>
-      </c>
-      <c r="F703" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G703" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H703" t="inlineStr"/>
-      <c r="I703" t="inlineStr">
-        <is>
-          <t>ambiguous(8)</t>
-        </is>
-      </c>
-      <c r="J703" t="n">
-        <v>26</v>
-      </c>
-      <c r="K703" t="inlineStr">
-        <is>
-          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
-        </is>
-      </c>
-      <c r="L703" t="inlineStr"/>
-      <c r="M703" t="inlineStr"/>
-      <c r="N703" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O703" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B704" t="n">
-        <v>213</v>
-      </c>
-      <c r="C704" t="n">
-        <v>6</v>
-      </c>
-      <c r="D704" t="inlineStr">
-        <is>
-          <t>[N]. B. Ca[r]t[e]r</t>
-        </is>
-      </c>
-      <c r="E704" t="inlineStr">
-        <is>
-          <t>N. B. Carter</t>
-        </is>
-      </c>
-      <c r="F704" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G704" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H704" t="inlineStr"/>
-      <c r="I704" t="inlineStr">
-        <is>
-          <t>ambiguous(8)</t>
-        </is>
-      </c>
-      <c r="J704" t="n">
-        <v>26</v>
-      </c>
-      <c r="K704" t="inlineStr">
-        <is>
-          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
-        </is>
-      </c>
-      <c r="L704" t="inlineStr"/>
-      <c r="M704" t="inlineStr"/>
-      <c r="N704" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O704" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B705" t="n">
-        <v>213</v>
-      </c>
-      <c r="C705" t="n">
-        <v>7</v>
-      </c>
-      <c r="D705" t="inlineStr">
-        <is>
-          <t>Nath[a]n [E]. King</t>
-        </is>
-      </c>
-      <c r="E705" t="inlineStr">
-        <is>
-          <t>Nathan E. King</t>
-        </is>
-      </c>
-      <c r="F705" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G705" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H705" t="inlineStr"/>
-      <c r="I705" t="inlineStr">
-        <is>
-          <t>ambiguous(43)</t>
-        </is>
-      </c>
-      <c r="J705" t="n">
-        <v>26</v>
-      </c>
-      <c r="K705" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L705" t="inlineStr"/>
-      <c r="M705" t="inlineStr"/>
-      <c r="N705" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O705" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B706" t="n">
-        <v>213</v>
-      </c>
-      <c r="C706" t="n">
-        <v>8</v>
-      </c>
-      <c r="D706" t="inlineStr">
-        <is>
-          <t>[Ch]ad[w]ell &amp; H. Vail</t>
-        </is>
-      </c>
-      <c r="E706" t="inlineStr">
-        <is>
-          <t>Chadwell &amp; H. Vail</t>
-        </is>
-      </c>
-      <c r="F706" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G706" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H706" t="inlineStr"/>
-      <c r="I706" t="inlineStr">
-        <is>
-          <t>ambiguous(6)</t>
-        </is>
-      </c>
-      <c r="J706" t="n">
-        <v>26</v>
-      </c>
-      <c r="K706" t="inlineStr">
-        <is>
-          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
-        </is>
-      </c>
-      <c r="L706" t="inlineStr"/>
-      <c r="M706" t="inlineStr"/>
-      <c r="N706" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O706" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B707" t="n">
-        <v>213</v>
-      </c>
-      <c r="C707" t="n">
-        <v>9</v>
-      </c>
-      <c r="D707" t="inlineStr">
-        <is>
-          <t>[S]. M. Wag[e]r</t>
-        </is>
-      </c>
-      <c r="E707" t="inlineStr">
-        <is>
-          <t>S. M. Wager</t>
-        </is>
-      </c>
-      <c r="F707" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G707" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H707" t="inlineStr"/>
-      <c r="I707" t="inlineStr">
-        <is>
-          <t>ambiguous(10)</t>
-        </is>
-      </c>
-      <c r="J707" t="n">
-        <v>26</v>
-      </c>
-      <c r="K707" t="inlineStr">
-        <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
-        </is>
-      </c>
-      <c r="L707" t="inlineStr"/>
-      <c r="M707" t="inlineStr"/>
-      <c r="N707" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O707" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B708" t="n">
-        <v>213</v>
-      </c>
-      <c r="C708" t="n">
-        <v>10</v>
-      </c>
-      <c r="D708" t="inlineStr">
-        <is>
-          <t>[?] W[m]. C[l]on[e]</t>
-        </is>
-      </c>
-      <c r="E708" t="inlineStr">
-        <is>
-          <t>[?] William Clone</t>
-        </is>
-      </c>
-      <c r="F708" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G708" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H708" t="inlineStr"/>
-      <c r="I708" t="inlineStr">
-        <is>
-          <t>ambiguous(3)</t>
-        </is>
-      </c>
-      <c r="J708" t="n">
-        <v>26</v>
-      </c>
-      <c r="K708" t="inlineStr">
-        <is>
-          <t>5101420;5101457;5101810</t>
-        </is>
-      </c>
-      <c r="L708" t="inlineStr"/>
-      <c r="M708" t="inlineStr"/>
-      <c r="N708" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O708" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B709" t="n">
-        <v>213</v>
-      </c>
-      <c r="C709" t="n">
-        <v>11</v>
-      </c>
-      <c r="D709" t="inlineStr">
-        <is>
-          <t>[A]. [N]. Dea[r]d[e]n</t>
-        </is>
-      </c>
-      <c r="E709" t="inlineStr">
-        <is>
-          <t>A. N. Dearden</t>
-        </is>
-      </c>
-      <c r="F709" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G709" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H709" t="inlineStr"/>
-      <c r="I709" t="inlineStr">
-        <is>
-          <t>ambiguous(43)</t>
-        </is>
-      </c>
-      <c r="J709" t="n">
-        <v>26</v>
-      </c>
-      <c r="K709" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L709" t="inlineStr"/>
-      <c r="M709" t="inlineStr"/>
-      <c r="N709" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O709" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B710" t="n">
-        <v>213</v>
-      </c>
-      <c r="C710" t="n">
-        <v>12</v>
-      </c>
-      <c r="D710" t="inlineStr">
-        <is>
-          <t>[E]. [K]. [?]</t>
-        </is>
-      </c>
-      <c r="E710" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="F710" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G710" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H710" t="inlineStr"/>
-      <c r="I710" t="inlineStr">
-        <is>
-          <t>ambiguous(3)</t>
-        </is>
-      </c>
-      <c r="J710" t="n">
-        <v>26</v>
-      </c>
-      <c r="K710" t="inlineStr">
-        <is>
-          <t>5101408;5101409;5101459</t>
-        </is>
-      </c>
-      <c r="L710" t="inlineStr"/>
-      <c r="M710" t="inlineStr"/>
-      <c r="N710" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O710" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B711" t="n">
-        <v>213</v>
-      </c>
-      <c r="C711" t="n">
-        <v>13</v>
-      </c>
-      <c r="D711" t="inlineStr">
-        <is>
-          <t>[H]. [H]. Ryan</t>
-        </is>
-      </c>
-      <c r="E711" t="inlineStr">
-        <is>
-          <t>H. H. Ryan</t>
-        </is>
-      </c>
-      <c r="F711" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G711" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H711" t="inlineStr"/>
-      <c r="I711" t="inlineStr">
-        <is>
-          <t>ambiguous(43)</t>
-        </is>
-      </c>
-      <c r="J711" t="n">
-        <v>26</v>
-      </c>
-      <c r="K711" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L711" t="inlineStr"/>
-      <c r="M711" t="inlineStr"/>
-      <c r="N711" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O711" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B712" t="n">
-        <v>213</v>
-      </c>
-      <c r="C712" t="n">
-        <v>14</v>
-      </c>
-      <c r="D712" t="inlineStr">
-        <is>
-          <t>Chaunc[y] [S]hell</t>
-        </is>
-      </c>
-      <c r="E712" t="inlineStr">
-        <is>
-          <t>Chauncy Shell</t>
-        </is>
-      </c>
-      <c r="F712" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G712" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H712" t="inlineStr"/>
-      <c r="I712" t="inlineStr">
-        <is>
-          <t>ambiguous(2)</t>
-        </is>
-      </c>
-      <c r="J712" t="n">
-        <v>26</v>
-      </c>
-      <c r="K712" t="inlineStr">
-        <is>
-          <t>5101451;5101461</t>
-        </is>
-      </c>
-      <c r="L712" t="inlineStr"/>
-      <c r="M712" t="inlineStr"/>
-      <c r="N712" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O712" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B713" t="n">
-        <v>213</v>
-      </c>
-      <c r="C713" t="n">
-        <v>15</v>
-      </c>
-      <c r="D713" t="inlineStr">
-        <is>
-          <t>[Jos]. Pat[h]</t>
-        </is>
-      </c>
-      <c r="E713" t="inlineStr">
-        <is>
-          <t>Jos. Path</t>
-        </is>
-      </c>
-      <c r="F713" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G713" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H713" t="inlineStr"/>
-      <c r="I713" t="inlineStr">
-        <is>
-          <t>ambiguous(10)</t>
-        </is>
-      </c>
-      <c r="J713" t="n">
-        <v>26</v>
-      </c>
-      <c r="K713" t="inlineStr">
-        <is>
-          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
-        </is>
-      </c>
-      <c r="L713" t="inlineStr"/>
-      <c r="M713" t="inlineStr"/>
-      <c r="N713" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O713" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B714" t="n">
-        <v>213</v>
-      </c>
-      <c r="C714" t="n">
-        <v>16</v>
-      </c>
-      <c r="D714" t="inlineStr">
-        <is>
-          <t>[?]. [B]. Ba[?]</t>
-        </is>
-      </c>
-      <c r="E714" t="inlineStr">
-        <is>
-          <t>[?]</t>
-        </is>
-      </c>
-      <c r="F714" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G714" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H714" t="inlineStr"/>
-      <c r="I714" t="inlineStr">
-        <is>
-          <t>ambiguous(3)</t>
-        </is>
-      </c>
-      <c r="J714" t="n">
-        <v>26</v>
-      </c>
-      <c r="K714" t="inlineStr">
-        <is>
-          <t>5101290;5101463;5102140</t>
-        </is>
-      </c>
-      <c r="L714" t="inlineStr"/>
-      <c r="M714" t="inlineStr"/>
-      <c r="N714" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O714" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B715" t="n">
-        <v>213</v>
-      </c>
-      <c r="C715" t="n">
-        <v>17</v>
-      </c>
-      <c r="D715" t="inlineStr">
-        <is>
-          <t>Robert [F]ol[g]an</t>
-        </is>
-      </c>
-      <c r="E715" t="inlineStr">
-        <is>
-          <t>Robert Folgan</t>
-        </is>
-      </c>
-      <c r="F715" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G715" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H715" t="inlineStr"/>
-      <c r="I715" t="inlineStr">
-        <is>
-          <t>ambiguous(43)</t>
-        </is>
-      </c>
-      <c r="J715" t="n">
-        <v>26</v>
-      </c>
-      <c r="K715" t="inlineStr">
-        <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
-      <c r="L715" t="inlineStr"/>
-      <c r="M715" t="inlineStr"/>
-      <c r="N715" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O715" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B716" t="n">
-        <v>213</v>
-      </c>
-      <c r="C716" t="n">
-        <v>18</v>
-      </c>
-      <c r="D716" t="inlineStr">
-        <is>
-          <t>[W]m. Ra[n]kin</t>
-        </is>
-      </c>
-      <c r="E716" t="inlineStr">
-        <is>
-          <t>William Rankin</t>
-        </is>
-      </c>
-      <c r="F716" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G716" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H716" t="inlineStr">
-        <is>
-          <t>5101435</t>
-        </is>
-      </c>
-      <c r="I716" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J716" t="n">
-        <v>26</v>
-      </c>
-      <c r="K716" t="inlineStr"/>
-      <c r="L716" t="inlineStr"/>
-      <c r="M716" t="inlineStr"/>
-      <c r="N716" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O716" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B717" t="n">
-        <v>213</v>
-      </c>
-      <c r="C717" t="n">
-        <v>19</v>
-      </c>
-      <c r="D717" t="inlineStr">
-        <is>
-          <t>[?] A[b]e[l]e[s]</t>
-        </is>
-      </c>
-      <c r="E717" t="inlineStr">
-        <is>
-          <t>[?] Abeles</t>
-        </is>
-      </c>
-      <c r="F717" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G717" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H717" t="inlineStr">
-        <is>
-          <t>5101436</t>
-        </is>
-      </c>
-      <c r="I717" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J717" t="n">
-        <v>26</v>
-      </c>
-      <c r="K717" t="inlineStr"/>
-      <c r="L717" t="inlineStr"/>
-      <c r="M717" t="inlineStr"/>
-      <c r="N717" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O717" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B718" t="n">
-        <v>213</v>
-      </c>
-      <c r="C718" t="n">
-        <v>20</v>
-      </c>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>[W]. [H]o[d]son</t>
-        </is>
-      </c>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>W. Hodson</t>
-        </is>
-      </c>
-      <c r="F718" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G718" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H718" t="inlineStr">
-        <is>
-          <t>5101437</t>
-        </is>
-      </c>
-      <c r="I718" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J718" t="n">
-        <v>26</v>
-      </c>
-      <c r="K718" t="inlineStr"/>
-      <c r="L718" t="inlineStr"/>
-      <c r="M718" t="inlineStr"/>
-      <c r="N718" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O718" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B719" t="n">
-        <v>213</v>
-      </c>
-      <c r="C719" t="n">
-        <v>21</v>
-      </c>
-      <c r="D719" t="inlineStr">
-        <is>
-          <t>[H]. [Sp]a[rk]e[r]</t>
-        </is>
-      </c>
-      <c r="E719" t="inlineStr">
-        <is>
-          <t>H. Sparker</t>
-        </is>
-      </c>
-      <c r="F719" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G719" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H719" t="inlineStr">
-        <is>
-          <t>5101438</t>
-        </is>
-      </c>
-      <c r="I719" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J719" t="n">
-        <v>26</v>
-      </c>
-      <c r="K719" t="inlineStr"/>
-      <c r="L719" t="inlineStr"/>
-      <c r="M719" t="inlineStr"/>
-      <c r="N719" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O719" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B720" t="n">
-        <v>213</v>
-      </c>
-      <c r="C720" t="n">
-        <v>22</v>
-      </c>
-      <c r="D720" t="inlineStr">
-        <is>
-          <t>John H[e]in[i]ck</t>
-        </is>
-      </c>
-      <c r="E720" t="inlineStr">
-        <is>
-          <t>John Heinick</t>
-        </is>
-      </c>
-      <c r="F720" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G720" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H720" t="inlineStr">
-        <is>
-          <t>5101439</t>
-        </is>
-      </c>
-      <c r="I720" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J720" t="n">
-        <v>26</v>
-      </c>
-      <c r="K720" t="inlineStr"/>
-      <c r="L720" t="inlineStr"/>
-      <c r="M720" t="inlineStr"/>
-      <c r="N720" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O720" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B721" t="n">
-        <v>213</v>
-      </c>
-      <c r="C721" t="n">
-        <v>23</v>
-      </c>
-      <c r="D721" t="inlineStr">
-        <is>
-          <t>[Jos]. Whit[a]k[e]r</t>
-        </is>
-      </c>
-      <c r="E721" t="inlineStr">
-        <is>
-          <t>Jos. Whitaker</t>
-        </is>
-      </c>
-      <c r="F721" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G721" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H721" t="inlineStr"/>
-      <c r="I721" t="inlineStr">
-        <is>
-          <t>ambiguous(6)</t>
-        </is>
-      </c>
-      <c r="J721" t="n">
-        <v>26</v>
-      </c>
-      <c r="K721" t="inlineStr">
-        <is>
-          <t>5101440;5101728;5101852;5102005;5102094;5102157</t>
-        </is>
-      </c>
-      <c r="L721" t="inlineStr">
-        <is>
-          <t>5101440</t>
-        </is>
-      </c>
-      <c r="M721" t="inlineStr">
-        <is>
-          <t>lines 22 and 24 resolve uniquely to serials 5101439 and 5101441; of this line's 6 candidates exactly one, 5101440, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
-      <c r="N721" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O721" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B722" t="n">
-        <v>213</v>
-      </c>
-      <c r="C722" t="n">
-        <v>24</v>
-      </c>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>John Rogan</t>
-        </is>
-      </c>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>John Rogan</t>
-        </is>
-      </c>
-      <c r="F722" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G722" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H722" t="inlineStr">
-        <is>
-          <t>5101441</t>
-        </is>
-      </c>
-      <c r="I722" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J722" t="n">
-        <v>26</v>
-      </c>
-      <c r="K722" t="inlineStr"/>
-      <c r="L722" t="inlineStr"/>
-      <c r="M722" t="inlineStr"/>
-      <c r="N722" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O722" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B723" t="n">
-        <v>213</v>
-      </c>
-      <c r="C723" t="n">
-        <v>25</v>
-      </c>
-      <c r="D723" t="inlineStr">
-        <is>
-          <t>A. [S]. Benne[t]</t>
-        </is>
-      </c>
-      <c r="E723" t="inlineStr">
-        <is>
-          <t>A. S. Bennet</t>
-        </is>
-      </c>
-      <c r="F723" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G723" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H723" t="inlineStr"/>
-      <c r="I723" t="inlineStr">
-        <is>
-          <t>ambiguous(2)</t>
-        </is>
-      </c>
-      <c r="J723" t="n">
-        <v>26</v>
-      </c>
-      <c r="K723" t="inlineStr">
-        <is>
-          <t>5101442;5102092</t>
-        </is>
-      </c>
-      <c r="L723" t="inlineStr">
-        <is>
-          <t>5101442</t>
-        </is>
-      </c>
-      <c r="M723" t="inlineStr">
-        <is>
-          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 2 candidates exactly one, 5101442, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
-      <c r="N723" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O723" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B724" t="n">
-        <v>213</v>
-      </c>
-      <c r="C724" t="n">
-        <v>26</v>
-      </c>
-      <c r="D724" t="inlineStr">
-        <is>
-          <t>Th[os]. P[ag]e</t>
-        </is>
-      </c>
-      <c r="E724" t="inlineStr">
-        <is>
-          <t>Thomas Page</t>
-        </is>
-      </c>
-      <c r="F724" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G724" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H724" t="inlineStr"/>
-      <c r="I724" t="inlineStr">
-        <is>
-          <t>ambiguous(43)</t>
-        </is>
-      </c>
-      <c r="J724" t="n">
-        <v>26</v>
-      </c>
-      <c r="K724" t="inlineStr">
-        <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
-      <c r="L724" t="inlineStr">
-        <is>
-          <t>5101443</t>
-        </is>
-      </c>
-      <c r="M724" t="inlineStr">
-        <is>
-          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 43 candidates exactly one, 5101443, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
-      <c r="N724" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O724" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B725" t="n">
-        <v>213</v>
-      </c>
-      <c r="C725" t="n">
-        <v>27</v>
-      </c>
-      <c r="D725" t="inlineStr">
-        <is>
-          <t>[Ja]s. M[c]Lea[n]</t>
-        </is>
-      </c>
-      <c r="E725" t="inlineStr">
-        <is>
-          <t>James McLean</t>
-        </is>
-      </c>
-      <c r="F725" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G725" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H725" t="inlineStr">
-        <is>
-          <t>5101444</t>
-        </is>
-      </c>
-      <c r="I725" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J725" t="n">
-        <v>26</v>
-      </c>
-      <c r="K725" t="inlineStr"/>
-      <c r="L725" t="inlineStr"/>
-      <c r="M725" t="inlineStr"/>
-      <c r="N725" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O725" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B726" t="n">
-        <v>213</v>
-      </c>
-      <c r="C726" t="n">
-        <v>28</v>
-      </c>
-      <c r="D726" t="inlineStr">
-        <is>
-          <t>[L]. [A]. [R]a[ll]s[t]one</t>
-        </is>
-      </c>
-      <c r="E726" t="inlineStr">
-        <is>
-          <t>L. A. Rallstone</t>
-        </is>
-      </c>
-      <c r="F726" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G726" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H726" t="inlineStr"/>
-      <c r="I726" t="inlineStr">
-        <is>
-          <t>ambiguous(6)</t>
-        </is>
-      </c>
-      <c r="J726" t="n">
-        <v>26</v>
-      </c>
-      <c r="K726" t="inlineStr">
-        <is>
-          <t>5101283;5101392;5101445;5101559;5101696;5101863</t>
-        </is>
-      </c>
-      <c r="L726" t="inlineStr">
-        <is>
-          <t>5101445</t>
-        </is>
-      </c>
-      <c r="M726" t="inlineStr">
-        <is>
-          <t>lines 27 and 30 resolve uniquely to serials 5101444 and 5101448; of this line's 6 candidates exactly one, 5101445, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
-      <c r="N726" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O726" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B727" t="n">
-        <v>213</v>
-      </c>
-      <c r="C727" t="n">
-        <v>29</v>
-      </c>
-      <c r="D727" t="inlineStr">
-        <is>
-          <t>M. [H]. Magi[e]</t>
-        </is>
-      </c>
-      <c r="E727" t="inlineStr">
-        <is>
-          <t>M. H. Magie</t>
-        </is>
-      </c>
-      <c r="F727" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G727" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H727" t="inlineStr"/>
-      <c r="I727" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="J727" t="n">
-        <v>26</v>
-      </c>
-      <c r="K727" t="inlineStr"/>
-      <c r="L727" t="inlineStr"/>
-      <c r="M727" t="inlineStr"/>
-      <c r="N727" t="inlineStr">
-        <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
-        </is>
-      </c>
-      <c r="O727" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RK</t>
-        </is>
-      </c>
-      <c r="B728" t="n">
-        <v>213</v>
-      </c>
-      <c r="C728" t="n">
-        <v>30</v>
-      </c>
-      <c r="D728" t="inlineStr">
-        <is>
-          <t>[F]. C. Sherman</t>
-        </is>
-      </c>
-      <c r="E728" t="inlineStr">
-        <is>
-          <t>F. C. Sherman</t>
-        </is>
-      </c>
-      <c r="F728" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G728" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H728" t="inlineStr">
-        <is>
-          <t>5101448</t>
-        </is>
-      </c>
-      <c r="I728" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J728" t="n">
-        <v>26</v>
-      </c>
-      <c r="K728" t="inlineStr"/>
-      <c r="L728" t="inlineStr"/>
-      <c r="M728" t="inlineStr"/>
-      <c r="N728" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O728" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B729" t="n">
-        <v>212</v>
-      </c>
-      <c r="C729" t="n">
-        <v>1</v>
-      </c>
-      <c r="D729" t="inlineStr">
-        <is>
-          <t>[?] Sawyer</t>
-        </is>
-      </c>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>[?] Sawyer</t>
-        </is>
-      </c>
-      <c r="F729" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G729" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H729" t="inlineStr"/>
-      <c r="I729" t="inlineStr">
-        <is>
-          <t>ambiguous(8)</t>
-        </is>
-      </c>
-      <c r="J729" t="n">
-        <v>26</v>
-      </c>
-      <c r="K729" t="inlineStr">
-        <is>
-          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
-        </is>
-      </c>
-      <c r="L729" t="inlineStr"/>
-      <c r="M729" t="inlineStr"/>
-      <c r="N729" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O729" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B730" t="n">
-        <v>212</v>
-      </c>
-      <c r="C730" t="n">
-        <v>2</v>
-      </c>
-      <c r="D730" t="inlineStr">
-        <is>
-          <t>Joseph Shields</t>
-        </is>
-      </c>
-      <c r="E730" t="inlineStr">
-        <is>
-          <t>Joseph Shields</t>
-        </is>
-      </c>
-      <c r="F730" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G730" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H730" t="inlineStr"/>
-      <c r="I730" t="inlineStr">
-        <is>
-          <t>ambiguous(3)</t>
-        </is>
-      </c>
-      <c r="J730" t="n">
-        <v>26</v>
-      </c>
-      <c r="K730" t="inlineStr">
-        <is>
-          <t>5101420;5101457;5101810</t>
-        </is>
-      </c>
-      <c r="L730" t="inlineStr"/>
-      <c r="M730" t="inlineStr"/>
-      <c r="N730" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O730" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B731" t="n">
-        <v>212</v>
-      </c>
-      <c r="C731" t="n">
-        <v>3</v>
-      </c>
-      <c r="D731" t="inlineStr">
-        <is>
-          <t>And[e]rson [L]. Co[x]</t>
-        </is>
-      </c>
-      <c r="E731" t="inlineStr">
-        <is>
-          <t>Anderson L. Cox</t>
-        </is>
-      </c>
-      <c r="F731" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G731" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H731" t="inlineStr"/>
-      <c r="I731" t="inlineStr">
-        <is>
-          <t>ambiguous(43)</t>
-        </is>
-      </c>
-      <c r="J731" t="n">
-        <v>26</v>
-      </c>
-      <c r="K731" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L731" t="inlineStr"/>
-      <c r="M731" t="inlineStr"/>
-      <c r="N731" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O731" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B732" t="n">
-        <v>212</v>
-      </c>
-      <c r="C732" t="n">
-        <v>4</v>
-      </c>
-      <c r="D732" t="inlineStr">
-        <is>
-          <t>Robert Ba[d]y</t>
-        </is>
-      </c>
-      <c r="E732" t="inlineStr">
-        <is>
-          <t>Robert Bady</t>
-        </is>
-      </c>
-      <c r="F732" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G732" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H732" t="inlineStr">
-        <is>
-          <t>5101422</t>
-        </is>
-      </c>
-      <c r="I732" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J732" t="n">
-        <v>26</v>
-      </c>
-      <c r="K732" t="inlineStr"/>
-      <c r="L732" t="inlineStr"/>
-      <c r="M732" t="inlineStr"/>
-      <c r="N732" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O732" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B733" t="n">
-        <v>212</v>
-      </c>
-      <c r="C733" t="n">
-        <v>5</v>
-      </c>
-      <c r="D733" t="inlineStr">
-        <is>
-          <t>D. H. [?]anda[c]k</t>
-        </is>
-      </c>
-      <c r="E733" t="inlineStr">
-        <is>
-          <t>D. H. [?]</t>
-        </is>
-      </c>
-      <c r="F733" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G733" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H733" t="inlineStr"/>
-      <c r="I733" t="inlineStr">
-        <is>
-          <t>ambiguous(10)</t>
-        </is>
-      </c>
-      <c r="J733" t="n">
-        <v>26</v>
-      </c>
-      <c r="K733" t="inlineStr">
-        <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
-        </is>
-      </c>
-      <c r="L733" t="inlineStr">
-        <is>
-          <t>5101423</t>
-        </is>
-      </c>
-      <c r="M733" t="inlineStr">
-        <is>
-          <t>lines 4 and 6 resolve uniquely to serials 5101422 and 5101424; of this line's 10 candidates exactly one, 5101423, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
-      <c r="N733" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O733" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B734" t="n">
-        <v>212</v>
-      </c>
-      <c r="C734" t="n">
-        <v>6</v>
-      </c>
-      <c r="D734" t="inlineStr">
-        <is>
-          <t>Marg[u]erite M[e]rra[r]d</t>
-        </is>
-      </c>
-      <c r="E734" t="inlineStr">
-        <is>
-          <t>Marguerite Merrard</t>
-        </is>
-      </c>
-      <c r="F734" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G734" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H734" t="inlineStr">
-        <is>
-          <t>5101424</t>
-        </is>
-      </c>
-      <c r="I734" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J734" t="n">
-        <v>26</v>
-      </c>
-      <c r="K734" t="inlineStr"/>
-      <c r="L734" t="inlineStr"/>
-      <c r="M734" t="inlineStr"/>
-      <c r="N734" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O734" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B735" t="n">
-        <v>212</v>
-      </c>
-      <c r="C735" t="n">
-        <v>7</v>
-      </c>
-      <c r="D735" t="inlineStr">
-        <is>
-          <t>David Bra[m]elin</t>
-        </is>
-      </c>
-      <c r="E735" t="inlineStr">
-        <is>
-          <t>David Bramelin</t>
-        </is>
-      </c>
-      <c r="F735" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G735" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H735" t="inlineStr"/>
-      <c r="I735" t="inlineStr">
-        <is>
-          <t>ambiguous(2)</t>
-        </is>
-      </c>
-      <c r="J735" t="n">
-        <v>26</v>
-      </c>
-      <c r="K735" t="inlineStr">
-        <is>
-          <t>5101425;5101910</t>
-        </is>
-      </c>
-      <c r="L735" t="inlineStr">
-        <is>
-          <t>5101425</t>
-        </is>
-      </c>
-      <c r="M735" t="inlineStr">
-        <is>
-          <t>lines 6 and 8 resolve uniquely to serials 5101424 and 5101426; of this line's 2 candidates exactly one, 5101425, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
-      <c r="N735" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O735" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B736" t="n">
-        <v>212</v>
-      </c>
-      <c r="C736" t="n">
-        <v>8</v>
-      </c>
-      <c r="D736" t="inlineStr">
-        <is>
-          <t>Robt. Watts</t>
-        </is>
-      </c>
-      <c r="E736" t="inlineStr">
-        <is>
-          <t>Robert Watts</t>
-        </is>
-      </c>
-      <c r="F736" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G736" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H736" t="inlineStr">
-        <is>
-          <t>5101426</t>
-        </is>
-      </c>
-      <c r="I736" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J736" t="n">
-        <v>26</v>
-      </c>
-      <c r="K736" t="inlineStr"/>
-      <c r="L736" t="inlineStr"/>
-      <c r="M736" t="inlineStr"/>
-      <c r="N736" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O736" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B737" t="n">
-        <v>212</v>
-      </c>
-      <c r="C737" t="n">
-        <v>9</v>
-      </c>
-      <c r="D737" t="inlineStr">
-        <is>
-          <t>Wm. Raymond</t>
-        </is>
-      </c>
-      <c r="E737" t="inlineStr">
-        <is>
-          <t>William Raymond</t>
-        </is>
-      </c>
-      <c r="F737" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G737" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H737" t="inlineStr"/>
-      <c r="I737" t="inlineStr">
-        <is>
-          <t>ambiguous(18)</t>
-        </is>
-      </c>
-      <c r="J737" t="n">
-        <v>26</v>
-      </c>
-      <c r="K737" t="inlineStr">
-        <is>
-          <t>5101427;5101555;5101557;5101653;5101682;5101722;5101827;5101864;5101869;5101890;5101905;5101939;5101973;5102000;5102011;5102052;5102105;5102144</t>
-        </is>
-      </c>
-      <c r="L737" t="inlineStr">
-        <is>
-          <t>5101427</t>
-        </is>
-      </c>
-      <c r="M737" t="inlineStr">
-        <is>
-          <t>lines 8 and 10 resolve uniquely to serials 5101426 and 5101428; of this line's 18 candidates exactly one, 5101427, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
-      <c r="N737" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 18 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O737" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B738" t="n">
-        <v>212</v>
-      </c>
-      <c r="C738" t="n">
-        <v>10</v>
-      </c>
-      <c r="D738" t="inlineStr">
-        <is>
-          <t>W[m]. [W]arner</t>
-        </is>
-      </c>
-      <c r="E738" t="inlineStr">
-        <is>
-          <t>William Warner</t>
-        </is>
-      </c>
-      <c r="F738" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G738" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H738" t="inlineStr">
-        <is>
-          <t>5101428</t>
-        </is>
-      </c>
-      <c r="I738" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J738" t="n">
-        <v>26</v>
-      </c>
-      <c r="K738" t="inlineStr"/>
-      <c r="L738" t="inlineStr"/>
-      <c r="M738" t="inlineStr"/>
-      <c r="N738" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O738" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B739" t="n">
-        <v>212</v>
-      </c>
-      <c r="C739" t="n">
-        <v>11</v>
-      </c>
-      <c r="D739" t="inlineStr">
-        <is>
-          <t>Ja[s]. C. [?]</t>
-        </is>
-      </c>
-      <c r="E739" t="inlineStr">
-        <is>
-          <t>Jas. C. [?]</t>
-        </is>
-      </c>
-      <c r="F739" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G739" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H739" t="inlineStr">
-        <is>
-          <t>5101429</t>
-        </is>
-      </c>
-      <c r="I739" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J739" t="n">
-        <v>26</v>
-      </c>
-      <c r="K739" t="inlineStr"/>
-      <c r="L739" t="inlineStr"/>
-      <c r="M739" t="inlineStr"/>
-      <c r="N739" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O739" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B740" t="n">
-        <v>212</v>
-      </c>
-      <c r="C740" t="n">
-        <v>12</v>
-      </c>
-      <c r="D740" t="inlineStr">
-        <is>
-          <t>[?] H. Sherm[an]</t>
-        </is>
-      </c>
-      <c r="E740" t="inlineStr">
-        <is>
-          <t>[?] H. Sherman</t>
-        </is>
-      </c>
-      <c r="F740" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G740" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H740" t="inlineStr">
-        <is>
-          <t>5101430</t>
-        </is>
-      </c>
-      <c r="I740" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J740" t="n">
-        <v>26</v>
-      </c>
-      <c r="K740" t="inlineStr"/>
-      <c r="L740" t="inlineStr"/>
-      <c r="M740" t="inlineStr"/>
-      <c r="N740" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O740" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B741" t="n">
-        <v>212</v>
-      </c>
-      <c r="C741" t="n">
-        <v>13</v>
-      </c>
-      <c r="D741" t="inlineStr">
-        <is>
-          <t>[?]. [K]. Bul[l]</t>
-        </is>
-      </c>
-      <c r="E741" t="inlineStr">
-        <is>
-          <t>[?] K. Bull</t>
-        </is>
-      </c>
-      <c r="F741" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G741" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H741" t="inlineStr"/>
-      <c r="I741" t="inlineStr">
-        <is>
-          <t>ambiguous(12)</t>
-        </is>
-      </c>
-      <c r="J741" t="n">
-        <v>26</v>
-      </c>
-      <c r="K741" t="inlineStr">
-        <is>
-          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
-        </is>
-      </c>
-      <c r="L741" t="inlineStr"/>
-      <c r="M741" t="inlineStr"/>
-      <c r="N741" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O741" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B742" t="n">
-        <v>212</v>
-      </c>
-      <c r="C742" t="n">
-        <v>14</v>
-      </c>
-      <c r="D742" t="inlineStr">
-        <is>
-          <t>John Davis</t>
-        </is>
-      </c>
-      <c r="E742" t="inlineStr">
-        <is>
-          <t>John Davis</t>
-        </is>
-      </c>
-      <c r="F742" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G742" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H742" t="inlineStr"/>
-      <c r="I742" t="inlineStr">
-        <is>
-          <t>ambiguous(43)</t>
-        </is>
-      </c>
-      <c r="J742" t="n">
-        <v>26</v>
-      </c>
-      <c r="K742" t="inlineStr">
-        <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
-      <c r="L742" t="inlineStr"/>
-      <c r="M742" t="inlineStr"/>
-      <c r="N742" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O742" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B743" t="n">
-        <v>212</v>
-      </c>
-      <c r="C743" t="n">
-        <v>15</v>
-      </c>
-      <c r="D743" t="inlineStr">
-        <is>
-          <t>Isaac [?] W[il]mo[t]h</t>
-        </is>
-      </c>
-      <c r="E743" t="inlineStr">
-        <is>
-          <t>Isaac [?] Wilmoth</t>
-        </is>
-      </c>
-      <c r="F743" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G743" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H743" t="inlineStr"/>
-      <c r="I743" t="inlineStr">
-        <is>
-          <t>ambiguous(43)</t>
-        </is>
-      </c>
-      <c r="J743" t="n">
-        <v>26</v>
-      </c>
-      <c r="K743" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L743" t="inlineStr"/>
-      <c r="M743" t="inlineStr"/>
-      <c r="N743" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O743" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B744" t="n">
-        <v>212</v>
-      </c>
-      <c r="C744" t="n">
-        <v>16</v>
-      </c>
-      <c r="D744" t="inlineStr">
-        <is>
-          <t>Mary Willard</t>
-        </is>
-      </c>
-      <c r="E744" t="inlineStr">
-        <is>
-          <t>Mary Willard</t>
-        </is>
-      </c>
-      <c r="F744" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G744" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H744" t="inlineStr"/>
-      <c r="I744" t="inlineStr">
-        <is>
-          <t>ambiguous(43)</t>
-        </is>
-      </c>
-      <c r="J744" t="n">
-        <v>26</v>
-      </c>
-      <c r="K744" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L744" t="inlineStr"/>
-      <c r="M744" t="inlineStr"/>
-      <c r="N744" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O744" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B745" t="n">
-        <v>212</v>
-      </c>
-      <c r="C745" t="n">
-        <v>17</v>
-      </c>
-      <c r="D745" t="inlineStr">
-        <is>
-          <t>Martin Stewart</t>
-        </is>
-      </c>
-      <c r="E745" t="inlineStr">
-        <is>
-          <t>Martin Stewart</t>
-        </is>
-      </c>
-      <c r="F745" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G745" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H745" t="inlineStr">
-        <is>
-          <t>5101404</t>
-        </is>
-      </c>
-      <c r="I745" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J745" t="n">
-        <v>26</v>
-      </c>
-      <c r="K745" t="inlineStr"/>
-      <c r="L745" t="inlineStr"/>
-      <c r="M745" t="inlineStr"/>
-      <c r="N745" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O745" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B746" t="n">
-        <v>212</v>
-      </c>
-      <c r="C746" t="n">
-        <v>18</v>
-      </c>
-      <c r="D746" t="inlineStr">
-        <is>
-          <t>F[r]. Ka[l]bfl[ei]sch</t>
-        </is>
-      </c>
-      <c r="E746" t="inlineStr">
-        <is>
-          <t>[?] Kalbfleisch</t>
-        </is>
-      </c>
-      <c r="F746" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G746" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H746" t="inlineStr">
-        <is>
-          <t>5101405</t>
-        </is>
-      </c>
-      <c r="I746" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J746" t="n">
-        <v>26</v>
-      </c>
-      <c r="K746" t="inlineStr"/>
-      <c r="L746" t="inlineStr"/>
-      <c r="M746" t="inlineStr"/>
-      <c r="N746" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O746" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B747" t="n">
-        <v>212</v>
-      </c>
-      <c r="C747" t="n">
-        <v>19</v>
-      </c>
-      <c r="D747" t="inlineStr">
-        <is>
-          <t>Jam[e]s [?] Morrison</t>
-        </is>
-      </c>
-      <c r="E747" t="inlineStr">
-        <is>
-          <t>James Morrison</t>
-        </is>
-      </c>
-      <c r="F747" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G747" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H747" t="inlineStr"/>
-      <c r="I747" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="J747" t="n">
-        <v>26</v>
-      </c>
-      <c r="K747" t="inlineStr"/>
-      <c r="L747" t="inlineStr"/>
-      <c r="M747" t="inlineStr"/>
-      <c r="N747" t="inlineStr">
-        <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
-        </is>
-      </c>
-      <c r="O747" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B748" t="n">
-        <v>212</v>
-      </c>
-      <c r="C748" t="n">
-        <v>20</v>
-      </c>
-      <c r="D748" t="inlineStr">
-        <is>
-          <t>L. Chr[is]t[ia]n[s]</t>
-        </is>
-      </c>
-      <c r="E748" t="inlineStr">
-        <is>
-          <t>L. Christians</t>
-        </is>
-      </c>
-      <c r="F748" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G748" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H748" t="inlineStr"/>
-      <c r="I748" t="inlineStr">
-        <is>
-          <t>ambiguous(4)</t>
-        </is>
-      </c>
-      <c r="J748" t="n">
-        <v>26</v>
-      </c>
-      <c r="K748" t="inlineStr">
-        <is>
-          <t>5101377;5101407;5101520;5101592</t>
-        </is>
-      </c>
-      <c r="L748" t="inlineStr">
-        <is>
-          <t>5101407</t>
-        </is>
-      </c>
-      <c r="M748" t="inlineStr">
-        <is>
-          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410; of this line's 4 candidates exactly one, 5101407, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
-      <c r="N748" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O748" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B749" t="n">
-        <v>212</v>
-      </c>
-      <c r="C749" t="n">
-        <v>21</v>
-      </c>
-      <c r="D749" t="inlineStr">
-        <is>
-          <t>Geo. C. Mo[r]e</t>
-        </is>
-      </c>
-      <c r="E749" t="inlineStr">
-        <is>
-          <t>George C. More</t>
-        </is>
-      </c>
-      <c r="F749" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G749" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H749" t="inlineStr"/>
-      <c r="I749" t="inlineStr">
-        <is>
-          <t>ambiguous(3)</t>
-        </is>
-      </c>
-      <c r="J749" t="n">
-        <v>26</v>
-      </c>
-      <c r="K749" t="inlineStr">
-        <is>
-          <t>5101408;5101409;5101459</t>
-        </is>
-      </c>
-      <c r="L749" t="inlineStr"/>
-      <c r="M749" t="inlineStr">
-        <is>
-          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
-        </is>
-      </c>
-      <c r="N749" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O749" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B750" t="n">
-        <v>212</v>
-      </c>
-      <c r="C750" t="n">
-        <v>22</v>
-      </c>
-      <c r="D750" t="inlineStr">
-        <is>
-          <t>[J]. Kir[t]la[n]d</t>
-        </is>
-      </c>
-      <c r="E750" t="inlineStr">
-        <is>
-          <t>J. Kirtland</t>
-        </is>
-      </c>
-      <c r="F750" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G750" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H750" t="inlineStr"/>
-      <c r="I750" t="inlineStr">
-        <is>
-          <t>ambiguous(3)</t>
-        </is>
-      </c>
-      <c r="J750" t="n">
-        <v>26</v>
-      </c>
-      <c r="K750" t="inlineStr">
-        <is>
-          <t>5101408;5101409;5101459</t>
-        </is>
-      </c>
-      <c r="L750" t="inlineStr"/>
-      <c r="M750" t="inlineStr">
-        <is>
-          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
-        </is>
-      </c>
-      <c r="N750" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O750" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B751" t="n">
-        <v>212</v>
-      </c>
-      <c r="C751" t="n">
-        <v>23</v>
-      </c>
-      <c r="D751" t="inlineStr">
-        <is>
-          <t>Jas. Edmu[n]ds</t>
-        </is>
-      </c>
-      <c r="E751" t="inlineStr">
-        <is>
-          <t>James Edmunds</t>
-        </is>
-      </c>
-      <c r="F751" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G751" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H751" t="inlineStr">
-        <is>
-          <t>5101410</t>
-        </is>
-      </c>
-      <c r="I751" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J751" t="n">
-        <v>26</v>
-      </c>
-      <c r="K751" t="inlineStr"/>
-      <c r="L751" t="inlineStr"/>
-      <c r="M751" t="inlineStr"/>
-      <c r="N751" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O751" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B752" t="n">
-        <v>212</v>
-      </c>
-      <c r="C752" t="n">
-        <v>24</v>
-      </c>
-      <c r="D752" t="inlineStr">
-        <is>
-          <t>John P[e]irc[e]</t>
-        </is>
-      </c>
-      <c r="E752" t="inlineStr">
-        <is>
-          <t>John Peirce</t>
-        </is>
-      </c>
-      <c r="F752" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G752" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H752" t="inlineStr"/>
-      <c r="I752" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="J752" t="n">
-        <v>26</v>
-      </c>
-      <c r="K752" t="inlineStr"/>
-      <c r="L752" t="inlineStr"/>
-      <c r="M752" t="inlineStr"/>
-      <c r="N752" t="inlineStr">
-        <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
-        </is>
-      </c>
-      <c r="O752" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B753" t="n">
-        <v>212</v>
-      </c>
-      <c r="C753" t="n">
-        <v>25</v>
-      </c>
-      <c r="D753" t="inlineStr">
-        <is>
-          <t>[P]. Lawrence</t>
-        </is>
-      </c>
-      <c r="E753" t="inlineStr">
-        <is>
-          <t>P. Lawrence</t>
-        </is>
-      </c>
-      <c r="F753" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G753" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H753" t="inlineStr">
-        <is>
-          <t>5101412</t>
-        </is>
-      </c>
-      <c r="I753" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J753" t="n">
-        <v>26</v>
-      </c>
-      <c r="K753" t="inlineStr"/>
-      <c r="L753" t="inlineStr"/>
-      <c r="M753" t="inlineStr"/>
-      <c r="N753" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O753" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B754" t="n">
-        <v>212</v>
-      </c>
-      <c r="C754" t="n">
-        <v>26</v>
-      </c>
-      <c r="D754" t="inlineStr">
-        <is>
-          <t>[J]. [C]. Walker</t>
-        </is>
-      </c>
-      <c r="E754" t="inlineStr">
-        <is>
-          <t>J. C. Walker</t>
-        </is>
-      </c>
-      <c r="F754" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G754" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H754" t="inlineStr"/>
-      <c r="I754" t="inlineStr">
-        <is>
-          <t>ambiguous(10)</t>
-        </is>
-      </c>
-      <c r="J754" t="n">
-        <v>26</v>
-      </c>
-      <c r="K754" t="inlineStr">
-        <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
-        </is>
-      </c>
-      <c r="L754" t="inlineStr">
-        <is>
-          <t>5101413</t>
-        </is>
-      </c>
-      <c r="M754" t="inlineStr">
-        <is>
-          <t>lines 25 and 27 resolve uniquely to serials 5101412 and 5101414; of this line's 10 candidates exactly one, 5101413, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
-      <c r="N754" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O754" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B755" t="n">
-        <v>212</v>
-      </c>
-      <c r="C755" t="n">
-        <v>27</v>
-      </c>
-      <c r="D755" t="inlineStr">
-        <is>
-          <t>[W]m. Williams</t>
-        </is>
-      </c>
-      <c r="E755" t="inlineStr">
-        <is>
-          <t>William Williams</t>
-        </is>
-      </c>
-      <c r="F755" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G755" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H755" t="inlineStr">
-        <is>
-          <t>5101414</t>
-        </is>
-      </c>
-      <c r="I755" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J755" t="n">
-        <v>26</v>
-      </c>
-      <c r="K755" t="inlineStr"/>
-      <c r="L755" t="inlineStr"/>
-      <c r="M755" t="inlineStr"/>
-      <c r="N755" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O755" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B756" t="n">
-        <v>212</v>
-      </c>
-      <c r="C756" t="n">
-        <v>28</v>
-      </c>
-      <c r="D756" t="inlineStr">
-        <is>
-          <t>W. Nelson</t>
-        </is>
-      </c>
-      <c r="E756" t="inlineStr">
-        <is>
-          <t>W. Nelson</t>
-        </is>
-      </c>
-      <c r="F756" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G756" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H756" t="inlineStr">
-        <is>
-          <t>5101415</t>
-        </is>
-      </c>
-      <c r="I756" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J756" t="n">
-        <v>26</v>
-      </c>
-      <c r="K756" t="inlineStr"/>
-      <c r="L756" t="inlineStr"/>
-      <c r="M756" t="inlineStr"/>
-      <c r="N756" t="inlineStr">
-        <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
-        </is>
-      </c>
-      <c r="O756" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B757" t="n">
-        <v>212</v>
-      </c>
-      <c r="C757" t="n">
-        <v>29</v>
-      </c>
-      <c r="D757" t="inlineStr">
-        <is>
-          <t>Geo. Merrill</t>
-        </is>
-      </c>
-      <c r="E757" t="inlineStr">
-        <is>
-          <t>George Merrill</t>
-        </is>
-      </c>
-      <c r="F757" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G757" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H757" t="inlineStr"/>
-      <c r="I757" t="inlineStr">
-        <is>
-          <t>ambiguous(6)</t>
-        </is>
-      </c>
-      <c r="J757" t="n">
-        <v>26</v>
-      </c>
-      <c r="K757" t="inlineStr">
-        <is>
-          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
-        </is>
-      </c>
-      <c r="L757" t="inlineStr"/>
-      <c r="M757" t="inlineStr"/>
-      <c r="N757" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O757" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B758" t="n">
-        <v>212</v>
-      </c>
-      <c r="C758" t="n">
-        <v>30</v>
-      </c>
-      <c r="D758" t="inlineStr">
-        <is>
-          <t>J. W. Salisbury</t>
-        </is>
-      </c>
-      <c r="E758" t="inlineStr">
-        <is>
-          <t>J. W. Salisbury</t>
-        </is>
-      </c>
-      <c r="F758" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G758" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H758" t="inlineStr"/>
-      <c r="I758" t="inlineStr">
-        <is>
-          <t>ambiguous(10)</t>
-        </is>
-      </c>
-      <c r="J758" t="n">
-        <v>26</v>
-      </c>
-      <c r="K758" t="inlineStr">
-        <is>
-          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
-        </is>
-      </c>
-      <c r="L758" t="inlineStr"/>
-      <c r="M758" t="inlineStr"/>
-      <c r="N758" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O758" t="inlineStr">
-        <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>33SQ-GYYJ-RY</t>
-        </is>
-      </c>
-      <c r="B759" t="n">
-        <v>212</v>
-      </c>
-      <c r="C759" t="n">
-        <v>31</v>
-      </c>
-      <c r="D759" t="inlineStr">
-        <is>
-          <t>John Parkin</t>
-        </is>
-      </c>
-      <c r="E759" t="inlineStr">
-        <is>
-          <t>John Parkin</t>
-        </is>
-      </c>
-      <c r="F759" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G759" t="inlineStr">
-        <is>
-          <t>scan_verified</t>
-        </is>
-      </c>
-      <c r="H759" t="inlineStr"/>
-      <c r="I759" t="inlineStr">
-        <is>
-          <t>ambiguous(43)</t>
-        </is>
-      </c>
-      <c r="J759" t="n">
-        <v>26</v>
-      </c>
-      <c r="K759" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L759" t="inlineStr"/>
-      <c r="M759" t="inlineStr"/>
-      <c r="N759" t="inlineStr">
-        <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
-        </is>
-      </c>
-      <c r="O759" t="inlineStr">
         <is>
           <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>

--- a/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
+++ b/chicago/reference/census1840/validation/T-0504_1840_name_serial_crosswalk.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O698"/>
+  <dimension ref="A1:O753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38690,23 +38690,23 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B638" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C638" t="n">
         <v>1</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Casper [M]uller</t>
+          <t>[?]ssel Rose</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Casper Muller</t>
+          <t>[?]ssel Rose</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
@@ -38719,53 +38719,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H638" t="inlineStr"/>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>5102180</t>
+        </is>
+      </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J638" t="n">
         <v>26</v>
       </c>
-      <c r="K638" t="inlineStr">
-        <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
-        </is>
-      </c>
+      <c r="K638" t="inlineStr"/>
       <c r="L638" t="inlineStr"/>
       <c r="M638" t="inlineStr"/>
       <c r="N638" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O638" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B639" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C639" t="n">
         <v>2</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>W[m]. [?] Sh[e]n[e]r</t>
+          <t>Jo[?]n J. Osgood</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>William [?] Shener</t>
+          <t>John J. Osgood</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -38780,7 +38780,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>5101449</t>
+          <t>5102181</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -38801,30 +38801,30 @@
       </c>
       <c r="O639" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B640" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C640" t="n">
         <v>3</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>[D]. [B]. [F]ischo[f]</t>
+          <t>Sam[?]l. C. Sti[?]ling</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>D. B. Fischof</t>
+          <t>Samuel C. Sti[?]ling</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
@@ -38837,53 +38837,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H640" t="inlineStr"/>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>5102182</t>
+        </is>
+      </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>ambiguous(11)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J640" t="n">
         <v>26</v>
       </c>
-      <c r="K640" t="inlineStr">
-        <is>
-          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
-        </is>
-      </c>
+      <c r="K640" t="inlineStr"/>
       <c r="L640" t="inlineStr"/>
       <c r="M640" t="inlineStr"/>
       <c r="N640" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B641" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C641" t="n">
         <v>4</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>E[ph]e[a]n [?] Sha[i]l[s]</t>
+          <t>John [?]agery</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>[?] Shails</t>
+          <t>John [?]agery</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
@@ -38899,51 +38899,59 @@
       <c r="H641" t="inlineStr"/>
       <c r="I641" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J641" t="n">
         <v>26</v>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>5101747;5102183;5102184</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr"/>
-      <c r="M641" t="inlineStr"/>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>lines 3 and 6 resolve uniquely to serials 5102182 and 5102185, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
       <c r="N641" t="inlineStr">
         <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B642" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C642" t="n">
         <v>5</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Ch[s]. Raymond</t>
+          <t>N. Ma[?]kay</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Charles Raymond</t>
+          <t>N. Ma[?]kay</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -38954,7 +38962,7 @@
       <c r="H642" t="inlineStr"/>
       <c r="I642" t="inlineStr">
         <is>
-          <t>ambiguous(8)</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J642" t="n">
@@ -38962,42 +38970,46 @@
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+          <t>5101747;5102183;5102184</t>
         </is>
       </c>
       <c r="L642" t="inlineStr"/>
-      <c r="M642" t="inlineStr"/>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>lines 3 and 6 resolve uniquely to serials 5102182 and 5102185, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B643" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C643" t="n">
         <v>6</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>[N]. B. Ca[r]t[e]r</t>
+          <t>Mrs. Ma[?]y Feltman</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>N. B. Carter</t>
+          <t>Ma[?]y Feltman</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
@@ -39010,53 +39022,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H643" t="inlineStr"/>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>5102185</t>
+        </is>
+      </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>ambiguous(8)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J643" t="n">
         <v>26</v>
       </c>
-      <c r="K643" t="inlineStr">
-        <is>
-          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
-        </is>
-      </c>
+      <c r="K643" t="inlineStr"/>
       <c r="L643" t="inlineStr"/>
       <c r="M643" t="inlineStr"/>
       <c r="N643" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O643" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B644" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C644" t="n">
         <v>7</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Nath[a]n [E]. King</t>
+          <t>Francis Feltman</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Nathan E. King</t>
+          <t>Francis Feltman</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
@@ -39072,7 +39084,7 @@
       <c r="H644" t="inlineStr"/>
       <c r="I644" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(4)</t>
         </is>
       </c>
       <c r="J644" t="n">
@@ -39080,42 +39092,50 @@
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L644" t="inlineStr"/>
-      <c r="M644" t="inlineStr"/>
+          <t>5101901;5101962;5102128;5102186</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>5102186</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>lines 6 and 9 resolve uniquely to serials 5102185 and 5102188; of this line's 4 candidates exactly one, 5102186, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N644" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B645" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C645" t="n">
         <v>8</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>[Ch]ad[w]ell &amp; H. Vail</t>
+          <t>James Ki[?]by</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Chadwell &amp; H. Vail</t>
+          <t>James Ki[?]by</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
@@ -39131,7 +39151,7 @@
       <c r="H645" t="inlineStr"/>
       <c r="I645" t="inlineStr">
         <is>
-          <t>ambiguous(6)</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J645" t="n">
@@ -39139,42 +39159,50 @@
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
-        </is>
-      </c>
-      <c r="L645" t="inlineStr"/>
-      <c r="M645" t="inlineStr"/>
+          <t>5101813;5101946;5102187</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>5102187</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>lines 6 and 9 resolve uniquely to serials 5102185 and 5102188; of this line's 3 candidates exactly one, 5102187, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N645" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B646" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C646" t="n">
         <v>9</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>[S]. M. Wag[e]r</t>
+          <t>Wm. Butt[?]field</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>S. M. Wager</t>
+          <t>William Butt[?]field</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
@@ -39187,53 +39215,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H646" t="inlineStr"/>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>5102188</t>
+        </is>
+      </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J646" t="n">
         <v>26</v>
       </c>
-      <c r="K646" t="inlineStr">
-        <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
-        </is>
-      </c>
+      <c r="K646" t="inlineStr"/>
       <c r="L646" t="inlineStr"/>
       <c r="M646" t="inlineStr"/>
       <c r="N646" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B647" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C647" t="n">
         <v>10</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>[?] W[m]. C[l]on[e]</t>
+          <t>Jas. Steven[?]</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>[?] William Clone</t>
+          <t>James Steven[?]</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
@@ -39249,50 +39277,46 @@
       <c r="H647" t="inlineStr"/>
       <c r="I647" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J647" t="n">
         <v>26</v>
       </c>
-      <c r="K647" t="inlineStr">
-        <is>
-          <t>5101420;5101457;5101810</t>
-        </is>
-      </c>
+      <c r="K647" t="inlineStr"/>
       <c r="L647" t="inlineStr"/>
       <c r="M647" t="inlineStr"/>
       <c r="N647" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B648" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C648" t="n">
         <v>11</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>[A]. [N]. Dea[r]d[e]n</t>
+          <t>John [?]ilmer</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>A. N. Dearden</t>
+          <t>John [?]ilmer</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
@@ -39308,7 +39332,7 @@
       <c r="H648" t="inlineStr"/>
       <c r="I648" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(10)</t>
         </is>
       </c>
       <c r="J648" t="n">
@@ -39316,42 +39340,50 @@
       </c>
       <c r="K648" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L648" t="inlineStr"/>
-      <c r="M648" t="inlineStr"/>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>5102190</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>lines 9 and 12 resolve uniquely to serials 5102188 and 5102191; of this line's 10 candidates exactly one, 5102190, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N648" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O648" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B649" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C649" t="n">
         <v>12</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>[E]. [K]. [?]</t>
+          <t>Sander[?] [?]eltman</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>Sander[?] [?]eltman</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
@@ -39364,58 +39396,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H649" t="inlineStr"/>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>5102191</t>
+        </is>
+      </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J649" t="n">
         <v>26</v>
       </c>
-      <c r="K649" t="inlineStr">
-        <is>
-          <t>5101408;5101409;5101459</t>
-        </is>
-      </c>
+      <c r="K649" t="inlineStr"/>
       <c r="L649" t="inlineStr"/>
       <c r="M649" t="inlineStr"/>
       <c r="N649" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O649" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B650" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C650" t="n">
         <v>13</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>[H]. [H]. Ryan</t>
+          <t>Benj. Emerson</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>H. H. Ryan</t>
+          <t>Benjamin Emerson</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -39426,7 +39458,7 @@
       <c r="H650" t="inlineStr"/>
       <c r="I650" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J650" t="n">
@@ -39434,42 +39466,50 @@
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L650" t="inlineStr"/>
-      <c r="M650" t="inlineStr"/>
+          <t>5101683;5101692;5102192</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>5102192</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>lines 12 and 16 resolve uniquely to serials 5102191 and 5102195; of this line's 3 candidates exactly one, 5102192, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N650" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B651" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C651" t="n">
         <v>14</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Chaunc[y] [S]hell</t>
+          <t>J[?]hn Leary</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Chauncy Shell</t>
+          <t>John Leary</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
@@ -39493,11 +39533,19 @@
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>5101451;5101461</t>
-        </is>
-      </c>
-      <c r="L651" t="inlineStr"/>
-      <c r="M651" t="inlineStr"/>
+          <t>5101815;5102193</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>5102193</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>lines 12 and 16 resolve uniquely to serials 5102191 and 5102195; of this line's 2 candidates exactly one, 5102193, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N651" t="inlineStr">
         <is>
           <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
@@ -39505,30 +39553,30 @@
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B652" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C652" t="n">
         <v>15</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>[Jos]. Pat[h]</t>
+          <t>James [?]otley</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Jos. Path</t>
+          <t>James [?]otley</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
@@ -39544,50 +39592,46 @@
       <c r="H652" t="inlineStr"/>
       <c r="I652" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J652" t="n">
         <v>26</v>
       </c>
-      <c r="K652" t="inlineStr">
-        <is>
-          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
-        </is>
-      </c>
+      <c r="K652" t="inlineStr"/>
       <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr"/>
       <c r="N652" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B653" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C653" t="n">
         <v>16</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>[?]. [B]. Ba[?]</t>
+          <t>Conrad Sn[?]er</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>[?]</t>
+          <t>Conrad Sn[?]er</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
@@ -39600,53 +39644,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H653" t="inlineStr"/>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>5102195</t>
+        </is>
+      </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J653" t="n">
         <v>26</v>
       </c>
-      <c r="K653" t="inlineStr">
-        <is>
-          <t>5101290;5101463;5102140</t>
-        </is>
-      </c>
+      <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr"/>
       <c r="N653" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B654" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C654" t="n">
         <v>17</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>Robert [F]ol[g]an</t>
+          <t>Henry K[?]inig Sr.</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>Robert Folgan</t>
+          <t>Henry K[?]inig Sr.</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
@@ -39659,58 +39703,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H654" t="inlineStr"/>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>5102169</t>
+        </is>
+      </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J654" t="n">
         <v>26</v>
       </c>
-      <c r="K654" t="inlineStr">
-        <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
+      <c r="K654" t="inlineStr"/>
       <c r="L654" t="inlineStr"/>
       <c r="M654" t="inlineStr"/>
       <c r="N654" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O654" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B655" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C655" t="n">
         <v>18</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>[W]m. Ra[n]kin</t>
+          <t>William Cain</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>William Rankin</t>
+          <t>William Cain</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -39720,7 +39764,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>5101435</t>
+          <t>5102170</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -39741,30 +39785,30 @@
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B656" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C656" t="n">
         <v>19</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>[?] A[b]e[l]e[s]</t>
+          <t>Jacob [?]elleman</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>[?] Abeles</t>
+          <t>Jacob [?]elleman</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
@@ -39777,53 +39821,61 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H656" t="inlineStr">
-        <is>
-          <t>5101436</t>
-        </is>
-      </c>
+      <c r="H656" t="inlineStr"/>
       <c r="I656" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(2)</t>
         </is>
       </c>
       <c r="J656" t="n">
         <v>26</v>
       </c>
-      <c r="K656" t="inlineStr"/>
-      <c r="L656" t="inlineStr"/>
-      <c r="M656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>5101326;5102171</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>5102171</t>
+        </is>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>lines 18 and 20 resolve uniquely to serials 5102170 and 5102172; of this line's 2 candidates exactly one, 5102171, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N656" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B657" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C657" t="n">
         <v>20</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>[W]. [H]o[d]son</t>
+          <t>Moses C. [?]ader</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>W. Hodson</t>
+          <t>Moses C. [?]ader</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -39838,7 +39890,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>5101437</t>
+          <t>5102172</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -39859,30 +39911,30 @@
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B658" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C658" t="n">
         <v>21</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>[H]. [Sp]a[rk]e[r]</t>
+          <t>John Boul[?]en</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>H. Sparker</t>
+          <t>John Boul[?]en</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
@@ -39895,53 +39947,57 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H658" t="inlineStr">
-        <is>
-          <t>5101438</t>
-        </is>
-      </c>
+      <c r="H658" t="inlineStr"/>
       <c r="I658" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J658" t="n">
         <v>26</v>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr"/>
-      <c r="M658" t="inlineStr"/>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>lines 20 and 23 resolve uniquely to serials 5102172 and 5102175, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
       <c r="N658" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B659" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C659" t="n">
         <v>22</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>John H[e]in[i]ck</t>
+          <t>M[?] Dal[?]er</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>John Heinick</t>
+          <t>M[?] Dal[?]er</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
@@ -39954,53 +40010,57 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H659" t="inlineStr">
-        <is>
-          <t>5101439</t>
-        </is>
-      </c>
+      <c r="H659" t="inlineStr"/>
       <c r="I659" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J659" t="n">
         <v>26</v>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr"/>
-      <c r="M659" t="inlineStr"/>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>lines 20 and 23 resolve uniquely to serials 5102172 and 5102175, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
       <c r="N659" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B660" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C660" t="n">
         <v>23</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>[Jos]. Whit[a]k[e]r</t>
+          <t>[?]n[?] Chapman</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Jos. Whitaker</t>
+          <t>[?]n[?] Chapman</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
@@ -40013,66 +40073,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H660" t="inlineStr"/>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>5102175</t>
+        </is>
+      </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>ambiguous(6)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J660" t="n">
         <v>26</v>
       </c>
-      <c r="K660" t="inlineStr">
-        <is>
-          <t>5101440;5101728;5101852;5102005;5102094;5102157</t>
-        </is>
-      </c>
-      <c r="L660" t="inlineStr">
-        <is>
-          <t>5101440</t>
-        </is>
-      </c>
-      <c r="M660" t="inlineStr">
-        <is>
-          <t>lines 22 and 24 resolve uniquely to serials 5101439 and 5101441; of this line's 6 candidates exactly one, 5101440, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K660" t="inlineStr"/>
+      <c r="L660" t="inlineStr"/>
+      <c r="M660" t="inlineStr"/>
       <c r="N660" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O660" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B661" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C661" t="n">
         <v>24</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>John Rogan</t>
+          <t>T. M. Monta[?]on</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>John Rogan</t>
+          <t>T. M. Monta[?]on</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -40080,58 +40132,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H661" t="inlineStr">
-        <is>
-          <t>5101441</t>
-        </is>
-      </c>
+      <c r="H661" t="inlineStr"/>
       <c r="I661" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(3)</t>
         </is>
       </c>
       <c r="J661" t="n">
         <v>26</v>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr"/>
       <c r="M661" t="inlineStr"/>
       <c r="N661" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B662" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C662" t="n">
         <v>25</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>A. [S]. Benne[t]</t>
+          <t>T. M. Ma[?]kh[?]m</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>A. S. Bennet</t>
+          <t>T. M. Ma[?]kh[?]m</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -40142,7 +40194,7 @@
       <c r="H662" t="inlineStr"/>
       <c r="I662" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>ambiguous(12)</t>
         </is>
       </c>
       <c r="J662" t="n">
@@ -40150,50 +40202,42 @@
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>5101442;5102092</t>
-        </is>
-      </c>
-      <c r="L662" t="inlineStr">
-        <is>
-          <t>5101442</t>
-        </is>
-      </c>
-      <c r="M662" t="inlineStr">
-        <is>
-          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 2 candidates exactly one, 5101442, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="inlineStr"/>
       <c r="N662" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B663" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C663" t="n">
         <v>26</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Th[os]. P[ag]e</t>
+          <t>J. H. [?]ain</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Thomas Page</t>
+          <t>J. H. [?]ain</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
@@ -40209,7 +40253,7 @@
       <c r="H663" t="inlineStr"/>
       <c r="I663" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(12)</t>
         </is>
       </c>
       <c r="J663" t="n">
@@ -40217,50 +40261,42 @@
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
-      <c r="L663" t="inlineStr">
-        <is>
-          <t>5101443</t>
-        </is>
-      </c>
-      <c r="M663" t="inlineStr">
-        <is>
-          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 43 candidates exactly one, 5101443, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr"/>
+      <c r="M663" t="inlineStr"/>
       <c r="N663" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O663" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-CK</t>
         </is>
       </c>
       <c r="B664" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C664" t="n">
         <v>27</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>[Ja]s. M[c]Lea[n]</t>
+          <t>John Davi[?]</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>James McLean</t>
+          <t>John Davi[?]</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
@@ -40273,58 +40309,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H664" t="inlineStr">
-        <is>
-          <t>5101444</t>
-        </is>
-      </c>
+      <c r="H664" t="inlineStr"/>
       <c r="I664" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(6)</t>
         </is>
       </c>
       <c r="J664" t="n">
         <v>26</v>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr"/>
       <c r="M664" t="inlineStr"/>
       <c r="N664" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-CK.jpg</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B665" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C665" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>[L]. [A]. [R]a[ll]s[t]one</t>
+          <t>James Davidson</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>L. A. Rallstone</t>
+          <t>James Davidson</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -40332,66 +40368,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H665" t="inlineStr"/>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>5101752</t>
+        </is>
+      </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>ambiguous(6)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J665" t="n">
         <v>26</v>
       </c>
-      <c r="K665" t="inlineStr">
-        <is>
-          <t>5101283;5101392;5101445;5101559;5101696;5101863</t>
-        </is>
-      </c>
-      <c r="L665" t="inlineStr">
-        <is>
-          <t>5101445</t>
-        </is>
-      </c>
-      <c r="M665" t="inlineStr">
-        <is>
-          <t>lines 27 and 30 resolve uniquely to serials 5101444 and 5101448; of this line's 6 candidates exactly one, 5101445, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K665" t="inlineStr"/>
+      <c r="L665" t="inlineStr"/>
+      <c r="M665" t="inlineStr"/>
       <c r="N665" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O665" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C666" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>M. [H]. Magi[e]</t>
+          <t>Robert Hamilton</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>M. H. Magie</t>
+          <t>Robert Hamilton</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -40399,10 +40427,14 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H666" t="inlineStr"/>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>5101753</t>
+        </is>
+      </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J666" t="n">
@@ -40413,40 +40445,40 @@
       <c r="M666" t="inlineStr"/>
       <c r="N666" t="inlineStr">
         <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O666" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RK</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B667" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C667" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>[F]. C. Sherman</t>
+          <t>Michael Bu[?]rk</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>F. C. Sherman</t>
+          <t>Michael Burk</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -40456,7 +40488,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>5101448</t>
+          <t>5101754</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -40477,30 +40509,30 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B668" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C668" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>[?] Sawyer</t>
+          <t>Dennis [?]ordan</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>[?] Sawyer</t>
+          <t>Dennis [?]ordan</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
@@ -40513,53 +40545,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H668" t="inlineStr"/>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>5101755</t>
+        </is>
+      </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>ambiguous(8)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J668" t="n">
         <v>26</v>
       </c>
-      <c r="K668" t="inlineStr">
-        <is>
-          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
-        </is>
-      </c>
+      <c r="K668" t="inlineStr"/>
       <c r="L668" t="inlineStr"/>
       <c r="M668" t="inlineStr"/>
       <c r="N668" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B669" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C669" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Joseph Shields</t>
+          <t>Patrick McHugh</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>Joseph Shields</t>
+          <t>Patrick McHugh</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
@@ -40572,53 +40604,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H669" t="inlineStr"/>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>5101756</t>
+        </is>
+      </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J669" t="n">
         <v>26</v>
       </c>
-      <c r="K669" t="inlineStr">
-        <is>
-          <t>5101420;5101457;5101810</t>
-        </is>
-      </c>
+      <c r="K669" t="inlineStr"/>
       <c r="L669" t="inlineStr"/>
       <c r="M669" t="inlineStr"/>
       <c r="N669" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B670" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C670" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>And[e]rson [L]. Co[x]</t>
+          <t>Susannah [?] Briggs</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>Anderson L. Cox</t>
+          <t>Susannah Briggs</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
@@ -40634,7 +40666,7 @@
       <c r="H670" t="inlineStr"/>
       <c r="I670" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(6)</t>
         </is>
       </c>
       <c r="J670" t="n">
@@ -40642,42 +40674,50 @@
       </c>
       <c r="K670" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L670" t="inlineStr"/>
-      <c r="M670" t="inlineStr"/>
+          <t>5101354;5101370;5101379;5101732;5101757;5102016</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>5101757</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>lines 5 and 7 resolve uniquely to serials 5101756 and 5101758; of this line's 6 candidates exactly one, 5101757, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N670" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B671" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C671" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Robert Ba[d]y</t>
+          <t>James Kelay</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Robert Bady</t>
+          <t>James Kelay</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
@@ -40692,7 +40732,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>5101422</t>
+          <t>5101758</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -40713,35 +40753,35 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B672" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C672" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>D. H. [?]anda[c]k</t>
+          <t>S. M. Merritt</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>D. H. [?]</t>
+          <t>S. M. Merritt</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -40752,7 +40792,7 @@
       <c r="H672" t="inlineStr"/>
       <c r="I672" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J672" t="n">
@@ -40760,50 +40800,50 @@
       </c>
       <c r="K672" t="inlineStr">
         <is>
-          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
         </is>
       </c>
       <c r="L672" t="inlineStr">
         <is>
-          <t>5101423</t>
+          <t>5101759</t>
         </is>
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>lines 4 and 6 resolve uniquely to serials 5101422 and 5101424; of this line's 10 candidates exactly one, 5101423, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 7 and 9 resolve uniquely to serials 5101758 and 5101760; of this line's 43 candidates exactly one, 5101759, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N672" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B673" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C673" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Marg[u]erite M[e]rra[r]d</t>
+          <t>Joseph D Winchell</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Marguerite Merrard</t>
+          <t>Joseph D Winchell</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
@@ -40818,7 +40858,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>5101424</t>
+          <t>5101760</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -40839,35 +40879,35 @@
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B674" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C674" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>David Bra[m]elin</t>
+          <t>Chas. C. Dow</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>David Bramelin</t>
+          <t>Charles C. Dow</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -40875,61 +40915,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H674" t="inlineStr"/>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>5101761</t>
+        </is>
+      </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>ambiguous(2)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J674" t="n">
         <v>26</v>
       </c>
-      <c r="K674" t="inlineStr">
-        <is>
-          <t>5101425;5101910</t>
-        </is>
-      </c>
-      <c r="L674" t="inlineStr">
-        <is>
-          <t>5101425</t>
-        </is>
-      </c>
-      <c r="M674" t="inlineStr">
-        <is>
-          <t>lines 6 and 8 resolve uniquely to serials 5101424 and 5101426; of this line's 2 candidates exactly one, 5101425, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K674" t="inlineStr"/>
+      <c r="L674" t="inlineStr"/>
+      <c r="M674" t="inlineStr"/>
       <c r="N674" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B675" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C675" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Robt. Watts</t>
+          <t>Thos. McDonall</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Robert Watts</t>
+          <t>Thomas McDonall</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
@@ -40944,7 +40976,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>5101426</t>
+          <t>5101762</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -40965,35 +40997,35 @@
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C676" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Wm. Raymond</t>
+          <t>Andrew Ba[?]an</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>William Raymond</t>
+          <t>Andrew Ba[?]an</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -41001,66 +41033,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H676" t="inlineStr"/>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>5101763</t>
+        </is>
+      </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>ambiguous(18)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J676" t="n">
         <v>26</v>
       </c>
-      <c r="K676" t="inlineStr">
-        <is>
-          <t>5101427;5101555;5101557;5101653;5101682;5101722;5101827;5101864;5101869;5101890;5101905;5101939;5101973;5102000;5102011;5102052;5102105;5102144</t>
-        </is>
-      </c>
-      <c r="L676" t="inlineStr">
-        <is>
-          <t>5101427</t>
-        </is>
-      </c>
-      <c r="M676" t="inlineStr">
-        <is>
-          <t>lines 8 and 10 resolve uniquely to serials 5101426 and 5101428; of this line's 18 candidates exactly one, 5101427, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="K676" t="inlineStr"/>
+      <c r="L676" t="inlineStr"/>
+      <c r="M676" t="inlineStr"/>
       <c r="N676" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 18 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O676" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B677" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C677" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>W[m]. [W]arner</t>
+          <t>William Wilson</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>William Warner</t>
+          <t>William Wilson</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
@@ -41068,58 +41092,66 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H677" t="inlineStr">
-        <is>
-          <t>5101428</t>
-        </is>
-      </c>
+      <c r="H677" t="inlineStr"/>
       <c r="I677" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(27)</t>
         </is>
       </c>
       <c r="J677" t="n">
         <v>26</v>
       </c>
-      <c r="K677" t="inlineStr"/>
-      <c r="L677" t="inlineStr"/>
-      <c r="M677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>5101279;5101385;5101465;5101540;5101684;5101685;5101689;5101708;5101710;5101723;5101726;5101744;5101764;5101779;5101780;5101784;5101792;5101842;5101898;5101935;5101980;5101986;5101994;5102009;5102055;5102077;5102090</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>5101764</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>lines 12 and 15 resolve uniquely to serials 5101763 and 5101766; of this line's 27 candidates exactly one, 5101764, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N677" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 27 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B678" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C678" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Ja[s]. C. [?]</t>
+          <t>Edward Ryan</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Jas. C. [?]</t>
+          <t>Edward Ryan</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
@@ -41127,58 +41159,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H678" t="inlineStr">
-        <is>
-          <t>5101429</t>
-        </is>
-      </c>
+      <c r="H678" t="inlineStr"/>
       <c r="I678" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(5)</t>
         </is>
       </c>
       <c r="J678" t="n">
         <v>26</v>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>5101589;5101609;5101663;5101794;5102113</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr"/>
       <c r="M678" t="inlineStr"/>
       <c r="N678" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 5 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O678" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B679" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C679" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>[?] H. Sherm[an]</t>
+          <t>P. Coughlin</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>[?] H. Sherman</t>
+          <t>P. Coughlin</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -41188,7 +41220,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>5101430</t>
+          <t>5101766</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41209,35 +41241,35 @@
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B680" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C680" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>[?]. [K]. Bul[l]</t>
+          <t>John Casey</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>[?] K. Bull</t>
+          <t>John Casey</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -41245,53 +41277,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H680" t="inlineStr"/>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>5101767</t>
+        </is>
+      </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>ambiguous(12)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J680" t="n">
         <v>26</v>
       </c>
-      <c r="K680" t="inlineStr">
-        <is>
-          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
-        </is>
-      </c>
+      <c r="K680" t="inlineStr"/>
       <c r="L680" t="inlineStr"/>
       <c r="M680" t="inlineStr"/>
       <c r="N680" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O680" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B681" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C681" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>John Davis</t>
+          <t>Barney Anderson</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>John Davis</t>
+          <t>Barney Anderson</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
@@ -41307,50 +41339,46 @@
       <c r="H681" t="inlineStr"/>
       <c r="I681" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J681" t="n">
         <v>26</v>
       </c>
-      <c r="K681" t="inlineStr">
-        <is>
-          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
-        </is>
-      </c>
+      <c r="K681" t="inlineStr"/>
       <c r="L681" t="inlineStr"/>
       <c r="M681" t="inlineStr"/>
       <c r="N681" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B682" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C682" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Isaac [?] W[il]mo[t]h</t>
+          <t>John McGl[?]flin</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Isaac [?] Wilmoth</t>
+          <t>John McGl[?]flin</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
@@ -41363,58 +41391,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H682" t="inlineStr"/>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>5101741</t>
+        </is>
+      </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J682" t="n">
         <v>26</v>
       </c>
-      <c r="K682" t="inlineStr">
-        <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
+      <c r="K682" t="inlineStr"/>
       <c r="L682" t="inlineStr"/>
       <c r="M682" t="inlineStr"/>
       <c r="N682" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B683" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C683" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Mary Willard</t>
+          <t>Mrs. Nan[?]y H. Jackson</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Mary Willard</t>
+          <t>Nan[?]y H. Jackson</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -41425,7 +41453,7 @@
       <c r="H683" t="inlineStr"/>
       <c r="I683" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(12)</t>
         </is>
       </c>
       <c r="J683" t="n">
@@ -41433,42 +41461,50 @@
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
-        </is>
-      </c>
-      <c r="L683" t="inlineStr"/>
-      <c r="M683" t="inlineStr"/>
+          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>5101742</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>lines 18 and 22 resolve uniquely to serials 5101741 and 5101745; of this line's 12 candidates exactly one, 5101742, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N683" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B684" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C684" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Martin Stewart</t>
+          <t>Alexr. Ford</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Martin Stewart</t>
+          <t>Alexander Ford</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
@@ -41481,53 +41517,61 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H684" t="inlineStr">
-        <is>
-          <t>5101404</t>
-        </is>
-      </c>
+      <c r="H684" t="inlineStr"/>
       <c r="I684" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J684" t="n">
         <v>26</v>
       </c>
-      <c r="K684" t="inlineStr"/>
-      <c r="L684" t="inlineStr"/>
-      <c r="M684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>5101743</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>lines 18 and 22 resolve uniquely to serials 5101741 and 5101745; of this line's 43 candidates exactly one, 5101743, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N684" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B685" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C685" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>F[r]. Ka[l]bfl[ei]sch</t>
+          <t>Alexr. Se[?]g[?]e</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>[?] Kalbfleisch</t>
+          <t>Alexander Se[?]g[?]e</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
@@ -41540,53 +41584,61 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H685" t="inlineStr">
-        <is>
-          <t>5101405</t>
-        </is>
-      </c>
+      <c r="H685" t="inlineStr"/>
       <c r="I685" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(27)</t>
         </is>
       </c>
       <c r="J685" t="n">
         <v>26</v>
       </c>
-      <c r="K685" t="inlineStr"/>
-      <c r="L685" t="inlineStr"/>
-      <c r="M685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>5101279;5101385;5101465;5101540;5101684;5101685;5101689;5101708;5101710;5101723;5101726;5101744;5101764;5101779;5101780;5101784;5101792;5101842;5101898;5101935;5101980;5101986;5101994;5102009;5102055;5102077;5102090</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>5101744</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>lines 18 and 22 resolve uniquely to serials 5101741 and 5101745; of this line's 27 candidates exactly one, 5101744, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
       <c r="N685" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 27 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B686" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C686" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Jam[e]s [?] Morrison</t>
+          <t>Michael Carthe[?]</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>James Morrison</t>
+          <t>Michael Carthe[?]</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
@@ -41599,10 +41651,14 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H686" t="inlineStr"/>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>5101745</t>
+        </is>
+      </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J686" t="n">
@@ -41613,35 +41669,35 @@
       <c r="M686" t="inlineStr"/>
       <c r="N686" t="inlineStr">
         <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B687" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C687" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>L. Chr[is]t[ia]n[s]</t>
+          <t>Wm. Mo[?]den</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>L. Christians</t>
+          <t>William Mo[?]den</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
@@ -41657,7 +41713,7 @@
       <c r="H687" t="inlineStr"/>
       <c r="I687" t="inlineStr">
         <is>
-          <t>ambiguous(4)</t>
+          <t>ambiguous(43)</t>
         </is>
       </c>
       <c r="J687" t="n">
@@ -41665,50 +41721,50 @@
       </c>
       <c r="K687" t="inlineStr">
         <is>
-          <t>5101377;5101407;5101520;5101592</t>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
         </is>
       </c>
       <c r="L687" t="inlineStr">
         <is>
-          <t>5101407</t>
+          <t>5101746</t>
         </is>
       </c>
       <c r="M687" t="inlineStr">
         <is>
-          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410; of this line's 4 candidates exactly one, 5101407, lies in that run at exactly the position an unbroken run would put it</t>
+          <t>lines 22 and 26 resolve uniquely to serials 5101745 and 5101749; of this line's 43 candidates exactly one, 5101746, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B688" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C688" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Geo. C. Mo[r]e</t>
+          <t>Sylvester L[?]id</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>George C. More</t>
+          <t>Sylvester L[?]id</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
@@ -41732,13 +41788,17 @@
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>5101408;5101409;5101459</t>
-        </is>
-      </c>
-      <c r="L688" t="inlineStr"/>
+          <t>5101747;5102183;5102184</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>5101747</t>
+        </is>
+      </c>
       <c r="M688" t="inlineStr">
         <is>
-          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+          <t>lines 22 and 26 resolve uniquely to serials 5101745 and 5101749; of this line's 3 candidates exactly one, 5101747, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N688" t="inlineStr">
@@ -41748,35 +41808,35 @@
       </c>
       <c r="O688" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B689" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C689" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>[J]. Kir[t]la[n]d</t>
+          <t>Nicholas Sadler</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>J. Kirtland</t>
+          <t>Nicholas Sadler</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -41787,7 +41847,7 @@
       <c r="H689" t="inlineStr"/>
       <c r="I689" t="inlineStr">
         <is>
-          <t>ambiguous(3)</t>
+          <t>ambiguous(11)</t>
         </is>
       </c>
       <c r="J689" t="n">
@@ -41795,51 +41855,55 @@
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>5101408;5101409;5101459</t>
-        </is>
-      </c>
-      <c r="L689" t="inlineStr"/>
+          <t>5101363;5101483;5101491;5101519;5101721;5101748;5101819;5102023;5102132;5102194;5102211</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>5101748</t>
+        </is>
+      </c>
       <c r="M689" t="inlineStr">
         <is>
-          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+          <t>lines 22 and 26 resolve uniquely to serials 5101745 and 5101749; of this line's 11 candidates exactly one, 5101748, lies in that run at exactly the position an unbroken run would put it</t>
         </is>
       </c>
       <c r="N689" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B690" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C690" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Jas. Edmu[n]ds</t>
+          <t>Benjamin M[?]ldon</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>James Edmunds</t>
+          <t>Benjamin M[?]ldon</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -41849,7 +41913,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>5101410</t>
+          <t>5101749</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -41870,35 +41934,35 @@
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B691" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C691" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>John P[e]irc[e]</t>
+          <t>Phillip [?]railman</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>John Peirce</t>
+          <t>Phillip [?]railman</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -41906,10 +41970,14 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H691" t="inlineStr"/>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>5101750</t>
+        </is>
+      </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J691" t="n">
@@ -41920,40 +41988,40 @@
       <c r="M691" t="inlineStr"/>
       <c r="N691" t="inlineStr">
         <is>
-          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
         </is>
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-LV</t>
         </is>
       </c>
       <c r="B692" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C692" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>[P]. Lawrence</t>
+          <t>E. Ryan</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>P. Lawrence</t>
+          <t>E. Ryan</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -41961,53 +42029,53 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H692" t="inlineStr">
-        <is>
-          <t>5101412</t>
-        </is>
-      </c>
+      <c r="H692" t="inlineStr"/>
       <c r="I692" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(10)</t>
         </is>
       </c>
       <c r="J692" t="n">
         <v>26</v>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr"/>
       <c r="M692" t="inlineStr"/>
       <c r="N692" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-LV.jpg</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B693" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C693" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>[J]. [C]. Walker</t>
+          <t>Casper [M]uller</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>J. C. Walker</t>
+          <t>Casper Muller</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
@@ -42034,16 +42102,8 @@
           <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
         </is>
       </c>
-      <c r="L693" t="inlineStr">
-        <is>
-          <t>5101413</t>
-        </is>
-      </c>
-      <c r="M693" t="inlineStr">
-        <is>
-          <t>lines 25 and 27 resolve uniquely to serials 5101412 and 5101414; of this line's 10 candidates exactly one, 5101413, lies in that run at exactly the position an unbroken run would put it</t>
-        </is>
-      </c>
+      <c r="L693" t="inlineStr"/>
+      <c r="M693" t="inlineStr"/>
       <c r="N693" t="inlineStr">
         <is>
           <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
@@ -42051,30 +42111,30 @@
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B694" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C694" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>[W]m. Williams</t>
+          <t>W[m]. [?] Sh[e]n[e]r</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>William Williams</t>
+          <t>William [?] Shener</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
@@ -42089,7 +42149,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>5101414</t>
+          <t>5101449</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42110,35 +42170,35 @@
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B695" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C695" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>W. Nelson</t>
+          <t>[D]. [B]. [F]ischo[f]</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>W. Nelson</t>
+          <t>D. B. Fischof</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
@@ -42146,58 +42206,58 @@
           <t>scan_verified</t>
         </is>
       </c>
-      <c r="H695" t="inlineStr">
-        <is>
-          <t>5101415</t>
-        </is>
-      </c>
+      <c r="H695" t="inlineStr"/>
       <c r="I695" t="inlineStr">
         <is>
-          <t>unique</t>
+          <t>ambiguous(11)</t>
         </is>
       </c>
       <c r="J695" t="n">
         <v>26</v>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>5101362;5101450;5101516;5101580;5101650;5101654;5101655;5101776;5101783;5101857;5101969</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr"/>
       <c r="M695" t="inlineStr"/>
       <c r="N695" t="inlineStr">
         <is>
-          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+          <t>the fingerprint over 26 columns matches 11 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B696" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C696" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Geo. Merrill</t>
+          <t>E[ph]e[a]n [?] Sha[i]l[s]</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>George Merrill</t>
+          <t>[?] Shails</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -42208,50 +42268,46 @@
       <c r="H696" t="inlineStr"/>
       <c r="I696" t="inlineStr">
         <is>
-          <t>ambiguous(6)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J696" t="n">
         <v>26</v>
       </c>
-      <c r="K696" t="inlineStr">
-        <is>
-          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
-        </is>
-      </c>
+      <c r="K696" t="inlineStr"/>
       <c r="L696" t="inlineStr"/>
       <c r="M696" t="inlineStr"/>
       <c r="N696" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
         </is>
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B697" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C697" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>J. W. Salisbury</t>
+          <t>Ch[s]. Raymond</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>J. W. Salisbury</t>
+          <t>Charles Raymond</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
@@ -42267,7 +42323,7 @@
       <c r="H697" t="inlineStr"/>
       <c r="I697" t="inlineStr">
         <is>
-          <t>ambiguous(10)</t>
+          <t>ambiguous(8)</t>
         </is>
       </c>
       <c r="J697" t="n">
@@ -42275,42 +42331,42 @@
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
         </is>
       </c>
       <c r="L697" t="inlineStr"/>
       <c r="M697" t="inlineStr"/>
       <c r="N697" t="inlineStr">
         <is>
-          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>33SQ-GYYJ-RY</t>
+          <t>33SQ-GYYJ-RK</t>
         </is>
       </c>
       <c r="B698" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C698" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>John Parkin</t>
+          <t>[N]. B. Ca[r]t[e]r</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>John Parkin</t>
+          <t>N. B. Carter</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
@@ -42326,7 +42382,7 @@
       <c r="H698" t="inlineStr"/>
       <c r="I698" t="inlineStr">
         <is>
-          <t>ambiguous(43)</t>
+          <t>ambiguous(8)</t>
         </is>
       </c>
       <c r="J698" t="n">
@@ -42334,17 +42390,3330 @@
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
         </is>
       </c>
       <c r="L698" t="inlineStr"/>
       <c r="M698" t="inlineStr"/>
       <c r="N698" t="inlineStr">
         <is>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>213</v>
+      </c>
+      <c r="C699" t="n">
+        <v>7</v>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Nath[a]n [E]. King</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Nathan E. King</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J699" t="n">
+        <v>26</v>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr"/>
+      <c r="M699" t="inlineStr"/>
+      <c r="N699" t="inlineStr">
+        <is>
           <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
         </is>
       </c>
-      <c r="O698" t="inlineStr">
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>213</v>
+      </c>
+      <c r="C700" t="n">
+        <v>8</v>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>[Ch]ad[w]ell &amp; H. Vail</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Chadwell &amp; H. Vail</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr"/>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J700" t="n">
+        <v>26</v>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr"/>
+      <c r="M700" t="inlineStr"/>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>213</v>
+      </c>
+      <c r="C701" t="n">
+        <v>9</v>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>[S]. M. Wag[e]r</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>S. M. Wager</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr"/>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J701" t="n">
+        <v>26</v>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr"/>
+      <c r="M701" t="inlineStr"/>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>213</v>
+      </c>
+      <c r="C702" t="n">
+        <v>10</v>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>[?] W[m]. C[l]on[e]</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>[?] William Clone</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr"/>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J702" t="n">
+        <v>26</v>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>5101420;5101457;5101810</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr"/>
+      <c r="M702" t="inlineStr"/>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>213</v>
+      </c>
+      <c r="C703" t="n">
+        <v>11</v>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>[A]. [N]. Dea[r]d[e]n</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>A. N. Dearden</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr"/>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J703" t="n">
+        <v>26</v>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr"/>
+      <c r="M703" t="inlineStr"/>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>213</v>
+      </c>
+      <c r="C704" t="n">
+        <v>12</v>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>[E]. [K]. [?]</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J704" t="n">
+        <v>26</v>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr"/>
+      <c r="M704" t="inlineStr"/>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>213</v>
+      </c>
+      <c r="C705" t="n">
+        <v>13</v>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>[H]. [H]. Ryan</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>H. H. Ryan</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr"/>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J705" t="n">
+        <v>26</v>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr"/>
+      <c r="M705" t="inlineStr"/>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>213</v>
+      </c>
+      <c r="C706" t="n">
+        <v>14</v>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Chaunc[y] [S]hell</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Chauncy Shell</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J706" t="n">
+        <v>26</v>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>5101451;5101461</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr"/>
+      <c r="M706" t="inlineStr"/>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>213</v>
+      </c>
+      <c r="C707" t="n">
+        <v>15</v>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>[Jos]. Pat[h]</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Jos. Path</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J707" t="n">
+        <v>26</v>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr"/>
+      <c r="M707" t="inlineStr"/>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>213</v>
+      </c>
+      <c r="C708" t="n">
+        <v>16</v>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>[?]. [B]. Ba[?]</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>[?]</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr"/>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J708" t="n">
+        <v>26</v>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>5101290;5101463;5102140</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr"/>
+      <c r="M708" t="inlineStr"/>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>213</v>
+      </c>
+      <c r="C709" t="n">
+        <v>17</v>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Robert [F]ol[g]an</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Robert Folgan</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J709" t="n">
+        <v>26</v>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr"/>
+      <c r="M709" t="inlineStr"/>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>213</v>
+      </c>
+      <c r="C710" t="n">
+        <v>18</v>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>[W]m. Ra[n]kin</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>William Rankin</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>5101435</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J710" t="n">
+        <v>26</v>
+      </c>
+      <c r="K710" t="inlineStr"/>
+      <c r="L710" t="inlineStr"/>
+      <c r="M710" t="inlineStr"/>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>213</v>
+      </c>
+      <c r="C711" t="n">
+        <v>19</v>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>[?] A[b]e[l]e[s]</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>[?] Abeles</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>5101436</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J711" t="n">
+        <v>26</v>
+      </c>
+      <c r="K711" t="inlineStr"/>
+      <c r="L711" t="inlineStr"/>
+      <c r="M711" t="inlineStr"/>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>213</v>
+      </c>
+      <c r="C712" t="n">
+        <v>20</v>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>[W]. [H]o[d]son</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>W. Hodson</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>5101437</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J712" t="n">
+        <v>26</v>
+      </c>
+      <c r="K712" t="inlineStr"/>
+      <c r="L712" t="inlineStr"/>
+      <c r="M712" t="inlineStr"/>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>213</v>
+      </c>
+      <c r="C713" t="n">
+        <v>21</v>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>[H]. [Sp]a[rk]e[r]</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>H. Sparker</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>5101438</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J713" t="n">
+        <v>26</v>
+      </c>
+      <c r="K713" t="inlineStr"/>
+      <c r="L713" t="inlineStr"/>
+      <c r="M713" t="inlineStr"/>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>213</v>
+      </c>
+      <c r="C714" t="n">
+        <v>22</v>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>John H[e]in[i]ck</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>John Heinick</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>5101439</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J714" t="n">
+        <v>26</v>
+      </c>
+      <c r="K714" t="inlineStr"/>
+      <c r="L714" t="inlineStr"/>
+      <c r="M714" t="inlineStr"/>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>213</v>
+      </c>
+      <c r="C715" t="n">
+        <v>23</v>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>[Jos]. Whit[a]k[e]r</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Jos. Whitaker</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr"/>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J715" t="n">
+        <v>26</v>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>5101440;5101728;5101852;5102005;5102094;5102157</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>5101440</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>lines 22 and 24 resolve uniquely to serials 5101439 and 5101441; of this line's 6 candidates exactly one, 5101440, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>213</v>
+      </c>
+      <c r="C716" t="n">
+        <v>24</v>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>John Rogan</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>John Rogan</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>5101441</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J716" t="n">
+        <v>26</v>
+      </c>
+      <c r="K716" t="inlineStr"/>
+      <c r="L716" t="inlineStr"/>
+      <c r="M716" t="inlineStr"/>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>213</v>
+      </c>
+      <c r="C717" t="n">
+        <v>25</v>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>A. [S]. Benne[t]</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>A. S. Bennet</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr"/>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J717" t="n">
+        <v>26</v>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>5101442;5102092</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>5101442</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 2 candidates exactly one, 5101442, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>213</v>
+      </c>
+      <c r="C718" t="n">
+        <v>26</v>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Th[os]. P[ag]e</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Thomas Page</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr"/>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J718" t="n">
+        <v>26</v>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>5101443</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>lines 24 and 27 resolve uniquely to serials 5101441 and 5101444; of this line's 43 candidates exactly one, 5101443, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>213</v>
+      </c>
+      <c r="C719" t="n">
+        <v>27</v>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>[Ja]s. M[c]Lea[n]</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>James McLean</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>5101444</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J719" t="n">
+        <v>26</v>
+      </c>
+      <c r="K719" t="inlineStr"/>
+      <c r="L719" t="inlineStr"/>
+      <c r="M719" t="inlineStr"/>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>213</v>
+      </c>
+      <c r="C720" t="n">
+        <v>28</v>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>[L]. [A]. [R]a[ll]s[t]one</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>L. A. Rallstone</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J720" t="n">
+        <v>26</v>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>5101283;5101392;5101445;5101559;5101696;5101863</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>5101445</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>lines 27 and 30 resolve uniquely to serials 5101444 and 5101448; of this line's 6 candidates exactly one, 5101445, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>213</v>
+      </c>
+      <c r="C721" t="n">
+        <v>29</v>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>M. [H]. Magi[e]</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>M. H. Magie</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J721" t="n">
+        <v>26</v>
+      </c>
+      <c r="K721" t="inlineStr"/>
+      <c r="L721" t="inlineStr"/>
+      <c r="M721" t="inlineStr"/>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RK</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>213</v>
+      </c>
+      <c r="C722" t="n">
+        <v>30</v>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>[F]. C. Sherman</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>F. C. Sherman</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>5101448</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J722" t="n">
+        <v>26</v>
+      </c>
+      <c r="K722" t="inlineStr"/>
+      <c r="L722" t="inlineStr"/>
+      <c r="M722" t="inlineStr"/>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>212</v>
+      </c>
+      <c r="C723" t="n">
+        <v>1</v>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>[?] Sawyer</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>[?] Sawyer</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>ambiguous(8)</t>
+        </is>
+      </c>
+      <c r="J723" t="n">
+        <v>26</v>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>5101416;5101452;5101453;5101498;5101959;5101979;5102032;5102051</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr"/>
+      <c r="M723" t="inlineStr"/>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 8 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>212</v>
+      </c>
+      <c r="C724" t="n">
+        <v>2</v>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Joseph Shields</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Joseph Shields</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J724" t="n">
+        <v>26</v>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>5101420;5101457;5101810</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr"/>
+      <c r="M724" t="inlineStr"/>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>212</v>
+      </c>
+      <c r="C725" t="n">
+        <v>3</v>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>And[e]rson [L]. Co[x]</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Anderson L. Cox</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr"/>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J725" t="n">
+        <v>26</v>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr"/>
+      <c r="M725" t="inlineStr"/>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>212</v>
+      </c>
+      <c r="C726" t="n">
+        <v>4</v>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Robert Ba[d]y</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Robert Bady</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>5101422</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J726" t="n">
+        <v>26</v>
+      </c>
+      <c r="K726" t="inlineStr"/>
+      <c r="L726" t="inlineStr"/>
+      <c r="M726" t="inlineStr"/>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>212</v>
+      </c>
+      <c r="C727" t="n">
+        <v>5</v>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>D. H. [?]anda[c]k</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>D. H. [?]</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr"/>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J727" t="n">
+        <v>26</v>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>5101423</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>lines 4 and 6 resolve uniquely to serials 5101422 and 5101424; of this line's 10 candidates exactly one, 5101423, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>212</v>
+      </c>
+      <c r="C728" t="n">
+        <v>6</v>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Marg[u]erite M[e]rra[r]d</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Marguerite Merrard</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>5101424</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J728" t="n">
+        <v>26</v>
+      </c>
+      <c r="K728" t="inlineStr"/>
+      <c r="L728" t="inlineStr"/>
+      <c r="M728" t="inlineStr"/>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>212</v>
+      </c>
+      <c r="C729" t="n">
+        <v>7</v>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>David Bra[m]elin</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>David Bramelin</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>ambiguous(2)</t>
+        </is>
+      </c>
+      <c r="J729" t="n">
+        <v>26</v>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>5101425;5101910</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>5101425</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>lines 6 and 8 resolve uniquely to serials 5101424 and 5101426; of this line's 2 candidates exactly one, 5101425, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 2 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>212</v>
+      </c>
+      <c r="C730" t="n">
+        <v>8</v>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Robt. Watts</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Robert Watts</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>5101426</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J730" t="n">
+        <v>26</v>
+      </c>
+      <c r="K730" t="inlineStr"/>
+      <c r="L730" t="inlineStr"/>
+      <c r="M730" t="inlineStr"/>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>212</v>
+      </c>
+      <c r="C731" t="n">
+        <v>9</v>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Wm. Raymond</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>William Raymond</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>ambiguous(18)</t>
+        </is>
+      </c>
+      <c r="J731" t="n">
+        <v>26</v>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>5101427;5101555;5101557;5101653;5101682;5101722;5101827;5101864;5101869;5101890;5101905;5101939;5101973;5102000;5102011;5102052;5102105;5102144</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>5101427</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>lines 8 and 10 resolve uniquely to serials 5101426 and 5101428; of this line's 18 candidates exactly one, 5101427, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 18 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>212</v>
+      </c>
+      <c r="C732" t="n">
+        <v>10</v>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>W[m]. [W]arner</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>William Warner</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>5101428</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J732" t="n">
+        <v>26</v>
+      </c>
+      <c r="K732" t="inlineStr"/>
+      <c r="L732" t="inlineStr"/>
+      <c r="M732" t="inlineStr"/>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>212</v>
+      </c>
+      <c r="C733" t="n">
+        <v>11</v>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Ja[s]. C. [?]</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Jas. C. [?]</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>5101429</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J733" t="n">
+        <v>26</v>
+      </c>
+      <c r="K733" t="inlineStr"/>
+      <c r="L733" t="inlineStr"/>
+      <c r="M733" t="inlineStr"/>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>212</v>
+      </c>
+      <c r="C734" t="n">
+        <v>12</v>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>[?] H. Sherm[an]</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>[?] H. Sherman</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>5101430</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J734" t="n">
+        <v>26</v>
+      </c>
+      <c r="K734" t="inlineStr"/>
+      <c r="L734" t="inlineStr"/>
+      <c r="M734" t="inlineStr"/>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>212</v>
+      </c>
+      <c r="C735" t="n">
+        <v>13</v>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>[?]. [K]. Bul[l]</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>[?] K. Bull</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>ambiguous(12)</t>
+        </is>
+      </c>
+      <c r="J735" t="n">
+        <v>26</v>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>5101396;5101397;5101431;5101507;5101548;5101625;5101706;5101724;5101742;5101938;5102036;5102074</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr"/>
+      <c r="M735" t="inlineStr"/>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 12 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>212</v>
+      </c>
+      <c r="C736" t="n">
+        <v>14</v>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>John Davis</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>John Davis</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr"/>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J736" t="n">
+        <v>26</v>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>5101273;5101291;5101294;5101321;5101324;5101337;5101432;5101434;5101443;5101464;5101476;5101479;5101485;5101551;5101552;5101606;5101631;5101656;5101678;5101739;5101743;5101759;5101765;5101812;5101820;5101822;5101853;5101880;5101882;5101883;5101906;5101918;5101928;5101947;5101954;5101956;5101985;5101990;5102050;5102155;5102156;5102159;5102168</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr"/>
+      <c r="M736" t="inlineStr"/>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>212</v>
+      </c>
+      <c r="C737" t="n">
+        <v>15</v>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Isaac [?] W[il]mo[t]h</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Isaac [?] Wilmoth</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J737" t="n">
+        <v>26</v>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr"/>
+      <c r="M737" t="inlineStr"/>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>212</v>
+      </c>
+      <c r="C738" t="n">
+        <v>16</v>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Mary Willard</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Mary Willard</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J738" t="n">
+        <v>26</v>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr"/>
+      <c r="M738" t="inlineStr"/>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>212</v>
+      </c>
+      <c r="C739" t="n">
+        <v>17</v>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Martin Stewart</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Martin Stewart</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>5101404</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J739" t="n">
+        <v>26</v>
+      </c>
+      <c r="K739" t="inlineStr"/>
+      <c r="L739" t="inlineStr"/>
+      <c r="M739" t="inlineStr"/>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>212</v>
+      </c>
+      <c r="C740" t="n">
+        <v>18</v>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>F[r]. Ka[l]bfl[ei]sch</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>[?] Kalbfleisch</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>5101405</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J740" t="n">
+        <v>26</v>
+      </c>
+      <c r="K740" t="inlineStr"/>
+      <c r="L740" t="inlineStr"/>
+      <c r="M740" t="inlineStr"/>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>212</v>
+      </c>
+      <c r="C741" t="n">
+        <v>19</v>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Jam[e]s [?] Morrison</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>James Morrison</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J741" t="n">
+        <v>26</v>
+      </c>
+      <c r="K741" t="inlineStr"/>
+      <c r="L741" t="inlineStr"/>
+      <c r="M741" t="inlineStr"/>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>212</v>
+      </c>
+      <c r="C742" t="n">
+        <v>20</v>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>L. Chr[is]t[ia]n[s]</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>L. Christians</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>ambiguous(4)</t>
+        </is>
+      </c>
+      <c r="J742" t="n">
+        <v>26</v>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>5101377;5101407;5101520;5101592</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>5101407</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410; of this line's 4 candidates exactly one, 5101407, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 4 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>212</v>
+      </c>
+      <c r="C743" t="n">
+        <v>21</v>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Geo. C. Mo[r]e</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>George C. More</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J743" t="n">
+        <v>26</v>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr"/>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>212</v>
+      </c>
+      <c r="C744" t="n">
+        <v>22</v>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>[J]. Kir[t]la[n]d</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>J. Kirtland</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>ambiguous(3)</t>
+        </is>
+      </c>
+      <c r="J744" t="n">
+        <v>26</v>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>5101408;5101409;5101459</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr"/>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>lines 18 and 23 resolve uniquely to serials 5101405 and 5101410, and 2 of this line's candidates fall between them, so continuity narrows and does not settle it</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 3 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>212</v>
+      </c>
+      <c r="C745" t="n">
+        <v>23</v>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Jas. Edmu[n]ds</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>James Edmunds</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>5101410</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J745" t="n">
+        <v>26</v>
+      </c>
+      <c r="K745" t="inlineStr"/>
+      <c r="L745" t="inlineStr"/>
+      <c r="M745" t="inlineStr"/>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>212</v>
+      </c>
+      <c r="C746" t="n">
+        <v>24</v>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>John P[e]irc[e]</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>John Peirce</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J746" t="n">
+        <v>26</v>
+      </c>
+      <c r="K746" t="inlineStr"/>
+      <c r="L746" t="inlineStr"/>
+      <c r="M746" t="inlineStr"/>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>no IPUMS household carries this pattern over the 26 compared columns — either the household is outside the extract or the reading of one cell is wrong, and this tool cannot tell those apart</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>212</v>
+      </c>
+      <c r="C747" t="n">
+        <v>25</v>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>[P]. Lawrence</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>P. Lawrence</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>5101412</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J747" t="n">
+        <v>26</v>
+      </c>
+      <c r="K747" t="inlineStr"/>
+      <c r="L747" t="inlineStr"/>
+      <c r="M747" t="inlineStr"/>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>212</v>
+      </c>
+      <c r="C748" t="n">
+        <v>26</v>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>[J]. [C]. Walker</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>J. C. Walker</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J748" t="n">
+        <v>26</v>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>5101381;5101393;5101398;5101413;5101423;5101446;5101456;5101594;5101595;5101596</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>5101413</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>lines 25 and 27 resolve uniquely to serials 5101412 and 5101414; of this line's 10 candidates exactly one, 5101413, lies in that run at exactly the position an unbroken run would put it</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>212</v>
+      </c>
+      <c r="C749" t="n">
+        <v>27</v>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>[W]m. Williams</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>William Williams</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>5101414</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J749" t="n">
+        <v>26</v>
+      </c>
+      <c r="K749" t="inlineStr"/>
+      <c r="L749" t="inlineStr"/>
+      <c r="M749" t="inlineStr"/>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>212</v>
+      </c>
+      <c r="C750" t="n">
+        <v>28</v>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>W. Nelson</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>W. Nelson</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>5101415</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J750" t="n">
+        <v>26</v>
+      </c>
+      <c r="K750" t="inlineStr"/>
+      <c r="L750" t="inlineStr"/>
+      <c r="M750" t="inlineStr"/>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>free-white age-band fingerprint over 26 of the schedule's 26 columns matches exactly one of the 964 IPUMS households</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>212</v>
+      </c>
+      <c r="C751" t="n">
+        <v>29</v>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Geo. Merrill</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>George Merrill</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>ambiguous(6)</t>
+        </is>
+      </c>
+      <c r="J751" t="n">
+        <v>26</v>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>5101417;5101455;5101610;5102008;5102024;5102179</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr"/>
+      <c r="M751" t="inlineStr"/>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 6 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>212</v>
+      </c>
+      <c r="C752" t="n">
+        <v>30</v>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>J. W. Salisbury</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>J. W. Salisbury</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>ambiguous(10)</t>
+        </is>
+      </c>
+      <c r="J752" t="n">
+        <v>26</v>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>5101266;5101418;5101462;5101512;5101640;5101645;5101664;5101751;5101960;5102190</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr"/>
+      <c r="M752" t="inlineStr"/>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 10 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>33SQ-GYYJ-RY</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>212</v>
+      </c>
+      <c r="C753" t="n">
+        <v>31</v>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>John Parkin</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>John Parkin</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>scan_verified</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>ambiguous(43)</t>
+        </is>
+      </c>
+      <c r="J753" t="n">
+        <v>26</v>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>5101373;5101374;5101375;5101376;5101378;5101401;5101402;5101403;5101406;5101419;5101421;5101433;5101454;5101458;5101460;5101469;5101494;5101499;5101500;5101501;5101508;5101511;5101513;5101518;5101523;5101524;5101558;5101587;5101590;5101598;5101600;5101612;5101613;5101622;5101623;5101633;5101637;5101646;5101676;5101746;5102034;5102173;5102174</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr"/>
+      <c r="M753" t="inlineStr"/>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>the fingerprint over 26 columns matches 43 IPUMS households and does not distinguish them; no serial is attached</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
         <is>
           <t>chicago/reference/census1840/33SQ-GYYJ-RY.jpg</t>
         </is>
